--- a/database/event/8250/event_8250_evp_summary.xlsx
+++ b/database/event/8250/event_8250_evp_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EVP_Summary_8250" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVP_Summary_8250" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,7 +502,7 @@
         <v>2.9413</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8124</v>
+        <v>3.1783</v>
       </c>
       <c r="E2" t="n">
         <v>8.910500000000001</v>
@@ -548,7 +548,7 @@
         <v>2.117</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8884</v>
+        <v>2.1695</v>
       </c>
       <c r="E3" t="n">
         <v>6.4133</v>
@@ -594,7 +594,7 @@
         <v>1.9338</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6831</v>
+        <v>1.9453</v>
       </c>
       <c r="E4" t="n">
         <v>5.8583</v>
@@ -640,7 +640,7 @@
         <v>1.879</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6216</v>
+        <v>1.8782</v>
       </c>
       <c r="E5" t="n">
         <v>5.6923</v>
@@ -686,7 +686,7 @@
         <v>1.8305</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5673</v>
+        <v>1.8189</v>
       </c>
       <c r="E6" t="n">
         <v>5.5455</v>
@@ -732,7 +732,7 @@
         <v>1.7348</v>
       </c>
       <c r="D7" t="n">
-        <v>1.46</v>
+        <v>1.7017</v>
       </c>
       <c r="E7" t="n">
         <v>5.2555</v>
@@ -778,7 +778,7 @@
         <v>1.1312</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7834</v>
+        <v>0.963</v>
       </c>
       <c r="E8" t="n">
         <v>3.4268</v>
@@ -824,7 +824,7 @@
         <v>1.0106</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6483</v>
+        <v>0.8155</v>
       </c>
       <c r="E9" t="n">
         <v>3.0616</v>
@@ -870,7 +870,7 @@
         <v>0.9989</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6351</v>
+        <v>0.8011</v>
       </c>
       <c r="E10" t="n">
         <v>3.0261</v>
@@ -916,7 +916,7 @@
         <v>0.9458</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5756</v>
+        <v>0.7362</v>
       </c>
       <c r="E11" t="n">
         <v>2.8653</v>
@@ -962,7 +962,7 @@
         <v>0.8336</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4498</v>
+        <v>0.5988</v>
       </c>
       <c r="E12" t="n">
         <v>2.5252</v>
@@ -1008,7 +1008,7 @@
         <v>0.7235</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3265</v>
+        <v>0.4641</v>
       </c>
       <c r="E13" t="n">
         <v>2.1918</v>
@@ -1054,7 +1054,7 @@
         <v>0.7093</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3105</v>
+        <v>0.4467</v>
       </c>
       <c r="E14" t="n">
         <v>2.1488</v>
@@ -1100,7 +1100,7 @@
         <v>0.6853</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2837</v>
+        <v>0.4174</v>
       </c>
       <c r="E15" t="n">
         <v>2.0762</v>
@@ -1146,7 +1146,7 @@
         <v>0.4764</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0494</v>
+        <v>0.1616</v>
       </c>
       <c r="E16" t="n">
         <v>1.4431</v>
@@ -1192,7 +1192,7 @@
         <v>0.3955</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0413</v>
+        <v>0.0626</v>
       </c>
       <c r="E17" t="n">
         <v>1.198</v>
@@ -1238,7 +1238,7 @@
         <v>0.348</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0945</v>
+        <v>0.0045</v>
       </c>
       <c r="E18" t="n">
         <v>1.0541</v>
@@ -1284,7 +1284,7 @@
         <v>0.3358</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1081</v>
+        <v>-0.0104</v>
       </c>
       <c r="E19" t="n">
         <v>1.0173</v>
@@ -1330,7 +1330,7 @@
         <v>0.33</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1147</v>
+        <v>-0.0175</v>
       </c>
       <c r="E20" t="n">
         <v>0.9996</v>
@@ -1376,7 +1376,7 @@
         <v>0.2941</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1548</v>
+        <v>-0.0614</v>
       </c>
       <c r="E21" t="n">
         <v>0.8911</v>
@@ -1422,7 +1422,7 @@
         <v>0.2905</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1588</v>
+        <v>-0.0658</v>
       </c>
       <c r="E22" t="n">
         <v>0.8802</v>
@@ -1468,7 +1468,7 @@
         <v>0.2901</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1593</v>
+        <v>-0.0663</v>
       </c>
       <c r="E23" t="n">
         <v>0.8789</v>
@@ -1514,7 +1514,7 @@
         <v>0.2111</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2479</v>
+        <v>-0.163</v>
       </c>
       <c r="E24" t="n">
         <v>0.6395999999999999</v>
@@ -1560,7 +1560,7 @@
         <v>0.1991</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2613</v>
+        <v>-0.1776</v>
       </c>
       <c r="E25" t="n">
         <v>0.6032999999999999</v>
@@ -1606,7 +1606,7 @@
         <v>0.172</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2917</v>
+        <v>-0.2109</v>
       </c>
       <c r="E26" t="n">
         <v>0.521</v>
@@ -1652,7 +1652,7 @@
         <v>0.1151</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3555</v>
+        <v>-0.2805</v>
       </c>
       <c r="E27" t="n">
         <v>0.3488</v>
@@ -1698,7 +1698,7 @@
         <v>0.0629</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.414</v>
+        <v>-0.3444</v>
       </c>
       <c r="E28" t="n">
         <v>0.1906</v>
@@ -1744,7 +1744,7 @@
         <v>0.0496</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4289</v>
+        <v>-0.3607</v>
       </c>
       <c r="E29" t="n">
         <v>0.1502</v>
@@ -1790,7 +1790,7 @@
         <v>0.0249</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4567</v>
+        <v>-0.3909</v>
       </c>
       <c r="E30" t="n">
         <v>0.07530000000000001</v>
@@ -1836,7 +1836,7 @@
         <v>0.0021</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4821</v>
+        <v>-0.4187</v>
       </c>
       <c r="E31" t="n">
         <v>0.0065</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0299</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.518</v>
+        <v>-0.4579</v>
       </c>
       <c r="E32" t="n">
         <v>-0.0905</v>
@@ -1928,7 +1928,7 @@
         <v>-0.098</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.5413</v>
       </c>
       <c r="E33" t="n">
         <v>-0.2968</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1812</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6876</v>
+        <v>-0.6431</v>
       </c>
       <c r="E34" t="n">
         <v>-0.5488</v>
@@ -2020,7 +2020,7 @@
         <v>-0.4368</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9741</v>
+        <v>-0.9559</v>
       </c>
       <c r="E35" t="n">
         <v>-1.3232</v>
@@ -2066,7 +2066,7 @@
         <v>-0.4574</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9973</v>
+        <v>-0.9812</v>
       </c>
       <c r="E36" t="n">
         <v>-1.3858</v>
@@ -2112,7 +2112,7 @@
         <v>-0.4987</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0435</v>
+        <v>-1.0317</v>
       </c>
       <c r="E37" t="n">
         <v>-1.5107</v>
@@ -2158,7 +2158,7 @@
         <v>-0.4996</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0446</v>
+        <v>-1.0328</v>
       </c>
       <c r="E38" t="n">
         <v>-1.5136</v>
@@ -2204,7 +2204,7 @@
         <v>-0.5485</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0993</v>
+        <v>-1.0926</v>
       </c>
       <c r="E39" t="n">
         <v>-1.6616</v>
@@ -2250,7 +2250,7 @@
         <v>-0.5663</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1193</v>
+        <v>-1.1144</v>
       </c>
       <c r="E40" t="n">
         <v>-1.7156</v>
@@ -2296,7 +2296,7 @@
         <v>-0.5807</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1354</v>
+        <v>-1.132</v>
       </c>
       <c r="E41" t="n">
         <v>-1.7591</v>

--- a/database/event/8250/event_8250_evp_summary.xlsx
+++ b/database/event/8250/event_8250_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.9413</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1783</v>
+        <v>3.106</v>
       </c>
       <c r="E2" t="n">
         <v>8.910500000000001</v>
@@ -548,7 +548,7 @@
         <v>2.117</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1695</v>
+        <v>2.1111</v>
       </c>
       <c r="E3" t="n">
         <v>6.4133</v>
@@ -594,7 +594,7 @@
         <v>1.9338</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9453</v>
+        <v>1.89</v>
       </c>
       <c r="E4" t="n">
         <v>5.8583</v>
@@ -640,7 +640,7 @@
         <v>1.879</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8782</v>
+        <v>1.8239</v>
       </c>
       <c r="E5" t="n">
         <v>5.6923</v>
@@ -686,7 +686,7 @@
         <v>1.8305</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8189</v>
+        <v>1.7654</v>
       </c>
       <c r="E6" t="n">
         <v>5.5455</v>
@@ -732,7 +732,7 @@
         <v>1.7348</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7017</v>
+        <v>1.6499</v>
       </c>
       <c r="E7" t="n">
         <v>5.2555</v>
@@ -778,7 +778,7 @@
         <v>1.1312</v>
       </c>
       <c r="D8" t="n">
-        <v>0.963</v>
+        <v>0.9213</v>
       </c>
       <c r="E8" t="n">
         <v>3.4268</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0616</v>
+        <v>3.0524</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0106</v>
+        <v>1.0076</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8155</v>
+        <v>0.7722</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0616</v>
+        <v>3.0524</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4689</v>
+        <v>2.4597</v>
       </c>
       <c r="G9" t="n">
         <v>0.5927</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4689</v>
+        <v>2.4597</v>
       </c>
       <c r="I9" t="n">
         <v>2.4804</v>
@@ -870,7 +870,7 @@
         <v>0.9989</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8011</v>
+        <v>0.7617</v>
       </c>
       <c r="E10" t="n">
         <v>3.0261</v>
@@ -916,7 +916,7 @@
         <v>0.9458</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7362</v>
+        <v>0.6976</v>
       </c>
       <c r="E11" t="n">
         <v>2.8653</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5252</v>
+        <v>2.5168</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8336</v>
+        <v>0.8308</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5988</v>
+        <v>0.5588</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5252</v>
+        <v>2.5168</v>
       </c>
       <c r="F12" t="n">
-        <v>2.251</v>
+        <v>2.2426</v>
       </c>
       <c r="G12" t="n">
         <v>0.2742</v>
       </c>
       <c r="H12" t="n">
-        <v>2.251</v>
+        <v>2.2426</v>
       </c>
       <c r="I12" t="n">
         <v>2.2615</v>
@@ -1008,7 +1008,7 @@
         <v>0.7235</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4641</v>
+        <v>0.4293</v>
       </c>
       <c r="E13" t="n">
         <v>2.1918</v>
@@ -1054,7 +1054,7 @@
         <v>0.7093</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4467</v>
+        <v>0.4122</v>
       </c>
       <c r="E14" t="n">
         <v>2.1488</v>
@@ -1100,7 +1100,7 @@
         <v>0.6853</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4174</v>
+        <v>0.3832</v>
       </c>
       <c r="E15" t="n">
         <v>2.0762</v>
@@ -1146,7 +1146,7 @@
         <v>0.4764</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1616</v>
+        <v>0.131</v>
       </c>
       <c r="E16" t="n">
         <v>1.4431</v>
@@ -1192,7 +1192,7 @@
         <v>0.3955</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0626</v>
+        <v>0.0334</v>
       </c>
       <c r="E17" t="n">
         <v>1.198</v>
@@ -1238,7 +1238,7 @@
         <v>0.348</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0045</v>
+        <v>-0.024</v>
       </c>
       <c r="E18" t="n">
         <v>1.0541</v>
@@ -1284,7 +1284,7 @@
         <v>0.3358</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0104</v>
+        <v>-0.0386</v>
       </c>
       <c r="E19" t="n">
         <v>1.0173</v>
@@ -1330,7 +1330,7 @@
         <v>0.33</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0175</v>
+        <v>-0.0457</v>
       </c>
       <c r="E20" t="n">
         <v>0.9996</v>
@@ -1376,7 +1376,7 @@
         <v>0.2941</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0614</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="E21" t="n">
         <v>0.8911</v>
@@ -1422,7 +1422,7 @@
         <v>0.2905</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0658</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="E22" t="n">
         <v>0.8802</v>
@@ -1468,7 +1468,7 @@
         <v>0.2901</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0663</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="E23" t="n">
         <v>0.8789</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.6388</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2111</v>
+        <v>0.2109</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.163</v>
+        <v>-0.1894</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.6388</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2132</v>
+        <v>0.2124</v>
       </c>
       <c r="G24" t="n">
         <v>0.4264</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2132</v>
+        <v>0.2124</v>
       </c>
       <c r="I24" t="n">
         <v>0.2142</v>
@@ -1560,7 +1560,7 @@
         <v>0.1991</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1776</v>
+        <v>-0.2036</v>
       </c>
       <c r="E25" t="n">
         <v>0.6032999999999999</v>
@@ -1606,7 +1606,7 @@
         <v>0.172</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2109</v>
+        <v>-0.2363</v>
       </c>
       <c r="E26" t="n">
         <v>0.521</v>
@@ -1652,7 +1652,7 @@
         <v>0.1151</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2805</v>
+        <v>-0.3049</v>
       </c>
       <c r="E27" t="n">
         <v>0.3488</v>
@@ -1698,7 +1698,7 @@
         <v>0.0629</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3444</v>
+        <v>-0.368</v>
       </c>
       <c r="E28" t="n">
         <v>0.1906</v>
@@ -1744,7 +1744,7 @@
         <v>0.0496</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3607</v>
+        <v>-0.3841</v>
       </c>
       <c r="E29" t="n">
         <v>0.1502</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0759</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0249</v>
+        <v>0.0251</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3909</v>
+        <v>-0.4137</v>
       </c>
       <c r="E30" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0759</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1564</v>
+        <v>-0.1558</v>
       </c>
       <c r="G30" t="n">
         <v>0.2317</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1564</v>
+        <v>-0.1558</v>
       </c>
       <c r="I30" t="n">
         <v>-0.1571</v>
@@ -1836,7 +1836,7 @@
         <v>0.0021</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4187</v>
+        <v>-0.4413</v>
       </c>
       <c r="E31" t="n">
         <v>0.0065</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0299</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4579</v>
+        <v>-0.48</v>
       </c>
       <c r="E32" t="n">
         <v>-0.0905</v>
@@ -1928,7 +1928,7 @@
         <v>-0.098</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5413</v>
+        <v>-0.5622</v>
       </c>
       <c r="E33" t="n">
         <v>-0.2968</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1812</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6431</v>
+        <v>-0.6626</v>
       </c>
       <c r="E34" t="n">
         <v>-0.5488</v>
@@ -2020,7 +2020,7 @@
         <v>-0.4368</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9559</v>
+        <v>-0.9711</v>
       </c>
       <c r="E35" t="n">
         <v>-1.3232</v>
@@ -2066,7 +2066,7 @@
         <v>-0.4574</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9812</v>
+        <v>-0.996</v>
       </c>
       <c r="E36" t="n">
         <v>-1.3858</v>
@@ -2112,7 +2112,7 @@
         <v>-0.4987</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0317</v>
+        <v>-1.0458</v>
       </c>
       <c r="E37" t="n">
         <v>-1.5107</v>
@@ -2158,7 +2158,7 @@
         <v>-0.4996</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0328</v>
+        <v>-1.0469</v>
       </c>
       <c r="E38" t="n">
         <v>-1.5136</v>
@@ -2204,7 +2204,7 @@
         <v>-0.5485</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0926</v>
+        <v>-1.1059</v>
       </c>
       <c r="E39" t="n">
         <v>-1.6616</v>
@@ -2250,7 +2250,7 @@
         <v>-0.5663</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1144</v>
+        <v>-1.1274</v>
       </c>
       <c r="E40" t="n">
         <v>-1.7156</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.7591</v>
+        <v>-1.7562</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5807</v>
+        <v>-0.5797</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.132</v>
+        <v>-1.1436</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.7591</v>
+        <v>-1.7562</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.7591</v>
+        <v>-0.7562</v>
       </c>
       <c r="G41" t="n">
         <v>-1</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.7591</v>
+        <v>-0.7562</v>
       </c>
       <c r="I41" t="n">
         <v>-0.7625999999999999</v>

--- a/database/event/8250/event_8250_evp_summary.xlsx
+++ b/database/event/8250/event_8250_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.910500000000001</v>
+        <v>7.8821</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9413</v>
+        <v>2.6018</v>
       </c>
       <c r="D2" t="n">
-        <v>3.106</v>
+        <v>2.9204</v>
       </c>
       <c r="E2" t="n">
-        <v>8.910500000000001</v>
+        <v>7.8821</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3012</v>
+        <v>3.8088</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6093</v>
+        <v>4.0733</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7442</v>
+        <v>7.9336</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8453</v>
+        <v>4.1251</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6093</v>
+        <v>4.0733</v>
       </c>
       <c r="K2" t="n">
         <v>136</v>
@@ -529,7 +529,7 @@
         <v>112</v>
       </c>
       <c r="M2" t="n">
-        <v>8.454599999999999</v>
+        <v>8.198399999999999</v>
       </c>
       <c r="N2" t="n">
         <v>248</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4133</v>
+        <v>6.4993</v>
       </c>
       <c r="C3" t="n">
-        <v>2.117</v>
+        <v>2.1454</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1111</v>
+        <v>2.2961</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4133</v>
+        <v>6.4993</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1622</v>
+        <v>2.7313</v>
       </c>
       <c r="G3" t="n">
-        <v>4.251</v>
+        <v>3.768</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1622</v>
+        <v>4.1371</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7526</v>
+        <v>2.1511</v>
       </c>
       <c r="J3" t="n">
-        <v>4.251</v>
+        <v>3.768</v>
       </c>
       <c r="K3" t="n">
         <v>136</v>
@@ -575,7 +575,7 @@
         <v>112</v>
       </c>
       <c r="M3" t="n">
-        <v>6.0036</v>
+        <v>5.9191</v>
       </c>
       <c r="N3" t="n">
         <v>248</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.8583</v>
+        <v>6.0005</v>
       </c>
       <c r="C4" t="n">
-        <v>1.9338</v>
+        <v>1.9807</v>
       </c>
       <c r="D4" t="n">
-        <v>1.89</v>
+        <v>2.0709</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8583</v>
+        <v>6.0005</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4761</v>
+        <v>1.2522</v>
       </c>
       <c r="G4" t="n">
-        <v>5.3822</v>
+        <v>4.7483</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4761</v>
+        <v>1.2522</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3859</v>
+        <v>0.6511</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3822</v>
+        <v>4.7483</v>
       </c>
       <c r="K4" t="n">
         <v>136</v>
@@ -621,7 +621,7 @@
         <v>112</v>
       </c>
       <c r="M4" t="n">
-        <v>5.7681</v>
+        <v>5.3994</v>
       </c>
       <c r="N4" t="n">
         <v>248</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6923</v>
+        <v>5.4444</v>
       </c>
       <c r="C5" t="n">
-        <v>1.879</v>
+        <v>1.7972</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8239</v>
+        <v>1.8199</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6923</v>
+        <v>5.4444</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6311</v>
+        <v>3.9188</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0612</v>
+        <v>1.5256</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6311</v>
+        <v>8.321099999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9431</v>
+        <v>4.3266</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0612</v>
+        <v>1.5256</v>
       </c>
       <c r="K5" t="n">
         <v>84</v>
@@ -667,7 +667,7 @@
         <v>110</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0043</v>
+        <v>5.8522</v>
       </c>
       <c r="N5" t="n">
         <v>194</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.5455</v>
+        <v>5.3561</v>
       </c>
       <c r="C6" t="n">
-        <v>1.8305</v>
+        <v>1.768</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7654</v>
+        <v>1.78</v>
       </c>
       <c r="E6" t="n">
-        <v>5.5455</v>
+        <v>5.3561</v>
       </c>
       <c r="F6" t="n">
-        <v>4.334</v>
+        <v>2.5324</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2115</v>
+        <v>2.8237</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8763</v>
+        <v>3.4363</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9524</v>
+        <v>1.7867</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2115</v>
+        <v>2.8237</v>
       </c>
       <c r="K6" t="n">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="L6" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M6" t="n">
-        <v>5.1639</v>
+        <v>4.6104</v>
       </c>
       <c r="N6" t="n">
-        <v>194</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.2555</v>
+        <v>5.3361</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7348</v>
+        <v>1.7614</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6499</v>
+        <v>1.771</v>
       </c>
       <c r="E7" t="n">
-        <v>5.2555</v>
+        <v>5.3361</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2995</v>
+        <v>3.5129</v>
       </c>
       <c r="G7" t="n">
-        <v>2.956</v>
+        <v>1.8232</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2995</v>
+        <v>6.891</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8638</v>
+        <v>3.583</v>
       </c>
       <c r="J7" t="n">
-        <v>2.956</v>
+        <v>1.8232</v>
       </c>
       <c r="K7" t="n">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="L7" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M7" t="n">
-        <v>4.8198</v>
+        <v>5.4062</v>
       </c>
       <c r="N7" t="n">
-        <v>248</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4268</v>
+        <v>4.1283</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1312</v>
+        <v>1.3627</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9213</v>
+        <v>1.2257</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4268</v>
+        <v>4.1283</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8192</v>
+        <v>2.4918</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6076</v>
+        <v>1.6365</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8192</v>
+        <v>3.2934</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4745</v>
+        <v>1.7124</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6076</v>
+        <v>1.6365</v>
       </c>
       <c r="K8" t="n">
         <v>84</v>
@@ -805,7 +805,7 @@
         <v>110</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0821</v>
+        <v>3.3489</v>
       </c>
       <c r="N8" t="n">
         <v>194</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0524</v>
+        <v>3.4615</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0076</v>
+        <v>1.1426</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7722</v>
+        <v>0.9247</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0524</v>
+        <v>3.4615</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4597</v>
+        <v>2.8297</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5927</v>
+        <v>0.6318</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4597</v>
+        <v>2.8537</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4804</v>
+        <v>2.9711</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5927</v>
+        <v>0.6318</v>
       </c>
       <c r="K9" t="n">
         <v>109</v>
@@ -851,7 +851,7 @@
         <v>75</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0731</v>
+        <v>3.6029</v>
       </c>
       <c r="N9" t="n">
         <v>184</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0261</v>
+        <v>3.2786</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9989</v>
+        <v>1.0822</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7617</v>
+        <v>0.8421</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0261</v>
+        <v>3.2786</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2556</v>
+        <v>2.9869</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7705</v>
+        <v>0.2917</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2556</v>
+        <v>3.199</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2556</v>
+        <v>3.199</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7705</v>
+        <v>0.2917</v>
       </c>
       <c r="K10" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L10" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0261</v>
+        <v>3.4907</v>
       </c>
       <c r="N10" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8653</v>
+        <v>3.1598</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9458</v>
+        <v>1.043</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6976</v>
+        <v>0.7885</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8653</v>
+        <v>3.1598</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3482</v>
+        <v>2.494</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5171</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3482</v>
+        <v>3.3011</v>
       </c>
       <c r="I11" t="n">
-        <v>2.3482</v>
+        <v>1.7164</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5171</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="L11" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8653</v>
+        <v>2.3822</v>
       </c>
       <c r="N11" t="n">
-        <v>214</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5168</v>
+        <v>3.0833</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8308</v>
+        <v>1.0178</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5588</v>
+        <v>0.7539</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5168</v>
+        <v>3.0833</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2426</v>
+        <v>2.6293</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2742</v>
+        <v>0.454</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2426</v>
+        <v>2.6293</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2615</v>
+        <v>2.7374</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2742</v>
+        <v>0.454</v>
       </c>
       <c r="K12" t="n">
         <v>109</v>
@@ -989,7 +989,7 @@
         <v>75</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5357</v>
+        <v>3.1914</v>
       </c>
       <c r="N12" t="n">
         <v>184</v>
@@ -998,44 +998,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1918</v>
+        <v>2.6397</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7235</v>
+        <v>0.8714</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4293</v>
+        <v>0.5537</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1918</v>
+        <v>2.6397</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9146</v>
+        <v>1.3282</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2772</v>
+        <v>1.3115</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9146</v>
+        <v>1.3282</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5518</v>
+        <v>1.3282</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2772</v>
+        <v>1.3115</v>
       </c>
       <c r="K13" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="L13" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="M13" t="n">
-        <v>1.829</v>
+        <v>2.6397</v>
       </c>
       <c r="N13" t="n">
         <v>194</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1488</v>
+        <v>2.51</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7093</v>
+        <v>0.8285</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4122</v>
+        <v>0.4951</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1488</v>
+        <v>2.51</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8504</v>
+        <v>3.0705</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7016</v>
+        <v>-0.5605</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8504</v>
+        <v>5.3322</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3103</v>
+        <v>2.7725</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7016</v>
+        <v>-0.5605</v>
       </c>
       <c r="K14" t="n">
         <v>136</v>
@@ -1081,7 +1081,7 @@
         <v>112</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6087</v>
+        <v>2.212</v>
       </c>
       <c r="N14" t="n">
         <v>248</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0762</v>
+        <v>2.0898</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6853</v>
+        <v>0.6898</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3832</v>
+        <v>0.3054</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0762</v>
+        <v>2.0898</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0338</v>
+        <v>1.4049</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0424</v>
+        <v>0.6849</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0338</v>
+        <v>1.4049</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0338</v>
+        <v>1.4049</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0424</v>
+        <v>0.6849</v>
       </c>
       <c r="K15" t="n">
         <v>99</v>
@@ -1127,7 +1127,7 @@
         <v>95</v>
       </c>
       <c r="M15" t="n">
-        <v>2.0762</v>
+        <v>2.0898</v>
       </c>
       <c r="N15" t="n">
         <v>194</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4431</v>
+        <v>1.8177</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4764</v>
+        <v>0.6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.131</v>
+        <v>0.1826</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4431</v>
+        <v>1.8177</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8556</v>
+        <v>1.165</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5875</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8556</v>
+        <v>1.165</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8556</v>
+        <v>1.165</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5875</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>81</v>
@@ -1173,7 +1173,7 @@
         <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4431</v>
+        <v>1.8177</v>
       </c>
       <c r="N16" t="n">
         <v>132</v>
@@ -1182,81 +1182,81 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.198</v>
+        <v>1.6595</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3955</v>
+        <v>0.5478</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0334</v>
+        <v>0.1112</v>
       </c>
       <c r="E17" t="n">
-        <v>1.198</v>
+        <v>1.6595</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2652</v>
+        <v>1.5717</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0672</v>
+        <v>0.0878</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2652</v>
+        <v>1.5717</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2652</v>
+        <v>1.5717</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0672</v>
+        <v>0.0878</v>
       </c>
       <c r="K17" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="L17" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="M17" t="n">
-        <v>1.198</v>
+        <v>1.6595</v>
       </c>
       <c r="N17" t="n">
-        <v>132</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0541</v>
+        <v>1.6248</v>
       </c>
       <c r="C18" t="n">
-        <v>0.348</v>
+        <v>0.5363</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.024</v>
+        <v>0.0955</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0541</v>
+        <v>1.6248</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9031</v>
+        <v>1.5218</v>
       </c>
       <c r="G18" t="n">
-        <v>0.151</v>
+        <v>0.103</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9031</v>
+        <v>1.5218</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9031</v>
+        <v>1.5218</v>
       </c>
       <c r="J18" t="n">
-        <v>0.151</v>
+        <v>0.103</v>
       </c>
       <c r="K18" t="n">
         <v>81</v>
@@ -1265,7 +1265,7 @@
         <v>51</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0541</v>
+        <v>1.6248</v>
       </c>
       <c r="N18" t="n">
         <v>132</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0173</v>
+        <v>1.5783</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3358</v>
+        <v>0.521</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0386</v>
+        <v>0.0745</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0173</v>
+        <v>1.5783</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0173</v>
+        <v>1.5783</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0173</v>
+        <v>1.5783</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0173</v>
+        <v>1.5783</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0173</v>
+        <v>1.5783</v>
       </c>
       <c r="N19" t="n">
         <v>108</v>
@@ -1320,35 +1320,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9996</v>
+        <v>1.4644</v>
       </c>
       <c r="C20" t="n">
-        <v>0.33</v>
+        <v>0.4834</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0457</v>
+        <v>0.0231</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9996</v>
+        <v>1.4644</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8178</v>
+        <v>1.1828</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8182</v>
+        <v>0.2816</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8178</v>
+        <v>1.1828</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8178</v>
+        <v>1.1828</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8182</v>
+        <v>0.2816</v>
       </c>
       <c r="K20" t="n">
         <v>81</v>
@@ -1357,7 +1357,7 @@
         <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9996</v>
+        <v>1.4644</v>
       </c>
       <c r="N20" t="n">
         <v>132</v>
@@ -1366,139 +1366,139 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Krabeni</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8911</v>
+        <v>1.351</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2941</v>
+        <v>0.446</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.0281</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8911</v>
+        <v>1.351</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8911</v>
+        <v>1.8795</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.5285</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8911</v>
+        <v>1.8795</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8911</v>
+        <v>1.8795</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.5285</v>
       </c>
       <c r="K21" t="n">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8911</v>
+        <v>1.351</v>
       </c>
       <c r="N21" t="n">
-        <v>108</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>Neityu</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8802</v>
+        <v>1.3019</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2905</v>
+        <v>0.4298</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.0503</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8802</v>
+        <v>1.3019</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8802</v>
+        <v>1.603</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8802</v>
+        <v>1.603</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8802</v>
+        <v>1.603</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="K22" t="n">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8802</v>
+        <v>1.3019</v>
       </c>
       <c r="N22" t="n">
-        <v>112</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8789</v>
+        <v>1.2638</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2901</v>
+        <v>0.4172</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0675</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8789</v>
+        <v>1.2638</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9929</v>
+        <v>1.2638</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.114</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9929</v>
+        <v>1.2638</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9929</v>
+        <v>1.2638</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.114</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="L23" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8789</v>
+        <v>1.2638</v>
       </c>
       <c r="N23" t="n">
-        <v>214</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24">
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6388</v>
+        <v>1.1416</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2109</v>
+        <v>0.3768</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1894</v>
+        <v>-0.1226</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6388</v>
+        <v>1.1416</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2124</v>
+        <v>0.6894</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4264</v>
+        <v>0.4522</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2124</v>
+        <v>0.6894</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2142</v>
+        <v>0.7178</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4264</v>
+        <v>0.4522</v>
       </c>
       <c r="K24" t="n">
         <v>109</v>
@@ -1541,7 +1541,7 @@
         <v>75</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6406000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="N24" t="n">
         <v>184</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>Krabeni</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6032999999999999</v>
+        <v>1.1077</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1991</v>
+        <v>0.3656</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2036</v>
+        <v>-0.1379</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6032999999999999</v>
+        <v>1.1077</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6032999999999999</v>
+        <v>1.1077</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6032999999999999</v>
+        <v>1.1077</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6032999999999999</v>
+        <v>1.1077</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6032999999999999</v>
+        <v>1.1077</v>
       </c>
       <c r="N25" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Neityu</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.521</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.172</v>
+        <v>0.3301</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2363</v>
+        <v>-0.1866</v>
       </c>
       <c r="E26" t="n">
-        <v>0.521</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1734</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6524</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.1734</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>1.1734</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6524</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="L26" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.521</v>
+        <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>214</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27">
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3488</v>
+        <v>0.6827</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1151</v>
+        <v>0.2254</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3049</v>
+        <v>-0.3298</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3488</v>
+        <v>0.6827</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8472</v>
+        <v>1.2284</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4984</v>
+        <v>-0.5457</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8472</v>
+        <v>1.2284</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8472</v>
+        <v>1.2284</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4984</v>
+        <v>-0.5457</v>
       </c>
       <c r="K27" t="n">
         <v>97</v>
@@ -1679,7 +1679,7 @@
         <v>117</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3487999999999999</v>
+        <v>0.6827</v>
       </c>
       <c r="N27" t="n">
         <v>214</v>
@@ -1688,139 +1688,139 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1906</v>
+        <v>0.6433</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0629</v>
+        <v>0.2123</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.368</v>
+        <v>-0.3476</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1906</v>
+        <v>0.6433</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.1601</v>
+        <v>-0.005</v>
       </c>
       <c r="G28" t="n">
-        <v>1.3507</v>
+        <v>0.6483</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.1601</v>
+        <v>-0.005</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.1601</v>
+        <v>-0.005</v>
       </c>
       <c r="J28" t="n">
-        <v>1.3507</v>
+        <v>0.6483</v>
       </c>
       <c r="K28" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L28" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1906000000000001</v>
+        <v>0.6433</v>
       </c>
       <c r="N28" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1502</v>
+        <v>0.546</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0496</v>
+        <v>0.1802</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3841</v>
+        <v>-0.3915</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1502</v>
+        <v>0.546</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5553</v>
+        <v>0.546</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7055</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5553</v>
+        <v>0.546</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5553</v>
+        <v>0.546</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7055</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="L29" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1502</v>
+        <v>0.546</v>
       </c>
       <c r="N29" t="n">
-        <v>214</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0759</v>
+        <v>0.5054</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0251</v>
+        <v>0.1668</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4137</v>
+        <v>-0.4099</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0759</v>
+        <v>0.5054</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1558</v>
+        <v>-0.7133</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2317</v>
+        <v>1.2187</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1558</v>
+        <v>-0.7133</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1571</v>
+        <v>-0.7133</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2317</v>
+        <v>1.2187</v>
       </c>
       <c r="K30" t="n">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="L30" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0746</v>
+        <v>0.5053999999999998</v>
       </c>
       <c r="N30" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0065</v>
+        <v>0.3176</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0021</v>
+        <v>0.1048</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4413</v>
+        <v>-0.4946</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0065</v>
+        <v>0.3176</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0065</v>
+        <v>0.3176</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0065</v>
+        <v>0.3176</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0065</v>
+        <v>0.3176</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0065</v>
+        <v>0.3176</v>
       </c>
       <c r="N31" t="n">
         <v>108</v>
@@ -1872,47 +1872,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0905</v>
+        <v>0.1646</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0299</v>
+        <v>0.0543</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.48</v>
+        <v>-0.5637</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0905</v>
+        <v>0.1646</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0905</v>
+        <v>-0.0562</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.2208</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0905</v>
+        <v>-0.0562</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0905</v>
+        <v>-0.0585</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.2208</v>
       </c>
       <c r="K32" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0905</v>
+        <v>0.1623</v>
       </c>
       <c r="N32" t="n">
-        <v>112</v>
+        <v>184</v>
       </c>
     </row>
     <row r="33">
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2968</v>
+        <v>0.0684</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.098</v>
+        <v>0.0226</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5622</v>
+        <v>-0.6071</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2968</v>
+        <v>0.0684</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3102</v>
+        <v>1.4975</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.607</v>
+        <v>-1.4291</v>
       </c>
       <c r="H33" t="n">
-        <v>1.3102</v>
+        <v>1.4975</v>
       </c>
       <c r="I33" t="n">
-        <v>1.3102</v>
+        <v>1.4975</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.607</v>
+        <v>-1.4291</v>
       </c>
       <c r="K33" t="n">
         <v>99</v>
@@ -1955,7 +1955,7 @@
         <v>95</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2968</v>
+        <v>0.06840000000000002</v>
       </c>
       <c r="N33" t="n">
         <v>194</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5488</v>
+        <v>-0.3636</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1812</v>
+        <v>-0.12</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6626</v>
+        <v>-0.8022</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5488</v>
+        <v>-0.3636</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9909</v>
+        <v>-0.8407</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4421</v>
+        <v>0.4771</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9909</v>
+        <v>-0.8407</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9909</v>
+        <v>-0.8407</v>
       </c>
       <c r="J34" t="n">
-        <v>0.4421</v>
+        <v>0.4771</v>
       </c>
       <c r="K34" t="n">
         <v>81</v>
@@ -2001,7 +2001,7 @@
         <v>51</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5488</v>
+        <v>-0.3636</v>
       </c>
       <c r="N34" t="n">
         <v>132</v>
@@ -2010,216 +2010,216 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>hypex</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.3232</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4368</v>
+        <v>-0.3179</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9711</v>
+        <v>-1.0729</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.3232</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.3232</v>
+        <v>0.2579</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.3232</v>
+        <v>0.2579</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.3232</v>
+        <v>0.2579</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
       <c r="K35" t="n">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.3232</v>
+        <v>-0.9632000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>112</v>
+        <v>194</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>coolio</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3858</v>
+        <v>-0.9798</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4574</v>
+        <v>-0.3234</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.996</v>
+        <v>-1.0803</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3858</v>
+        <v>-0.9798</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.3858</v>
+        <v>-0.3168</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.663</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.3858</v>
+        <v>-0.3168</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.3858</v>
+        <v>-0.3298</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.663</v>
       </c>
       <c r="K36" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.3858</v>
+        <v>-0.9928</v>
       </c>
       <c r="N36" t="n">
-        <v>108</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>cmtry</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.5107</v>
+        <v>-0.9997</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4987</v>
+        <v>-0.33</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0458</v>
+        <v>-1.0893</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.5107</v>
+        <v>-0.9997</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0587</v>
+        <v>-0.9997</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.452</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0587</v>
+        <v>-0.9997</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8581</v>
+        <v>-0.9997</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.452</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="L37" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.3101</v>
+        <v>-0.9997</v>
       </c>
       <c r="N37" t="n">
-        <v>194</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>hypex</t>
+          <t>coolio</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.5136</v>
+        <v>-1.0672</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4996</v>
+        <v>-0.3523</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0469</v>
+        <v>-1.1198</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.5136</v>
+        <v>-1.0672</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.0469</v>
+        <v>-1.0672</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.4667</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.0469</v>
+        <v>-1.0672</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0469</v>
+        <v>-1.0672</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.4667</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="L38" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.5136</v>
+        <v>-1.0672</v>
       </c>
       <c r="N38" t="n">
-        <v>194</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6616</v>
+        <v>-1.0851</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5485</v>
+        <v>-0.3582</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1059</v>
+        <v>-1.1279</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6616</v>
+        <v>-1.0851</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.6616</v>
+        <v>-1.0851</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.6616</v>
+        <v>-1.0851</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.6616</v>
+        <v>-1.0851</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.6616</v>
+        <v>-1.0851</v>
       </c>
       <c r="N39" t="n">
         <v>112</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cmtry</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7156</v>
+        <v>-1.1556</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5663</v>
+        <v>-0.3815</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1274</v>
+        <v>-1.1597</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7156</v>
+        <v>-1.1556</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.7156</v>
+        <v>-1.1556</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.7156</v>
+        <v>-1.1556</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7156</v>
+        <v>-1.1556</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7156</v>
+        <v>-1.1556</v>
       </c>
       <c r="N40" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.7562</v>
+        <v>-1.7013</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5797</v>
+        <v>-0.5616</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1436</v>
+        <v>-1.4061</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.7562</v>
+        <v>-1.7013</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.7562</v>
+        <v>-1.0776</v>
       </c>
       <c r="G41" t="n">
-        <v>-1</v>
+        <v>-0.6237</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.7562</v>
+        <v>-1.0776</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7625999999999999</v>
+        <v>-0.5603</v>
       </c>
       <c r="J41" t="n">
-        <v>-1</v>
+        <v>-0.6237</v>
       </c>
       <c r="K41" t="n">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="L41" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.7626</v>
+        <v>-1.184</v>
       </c>
       <c r="N41" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.25</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4731</v>
+        <v>0.5507</v>
       </c>
       <c r="J2" t="n">
-        <v>13.2468</v>
+        <v>15.4196</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2492</v>
+        <v>0.2622</v>
       </c>
       <c r="J3" t="n">
-        <v>6.9776</v>
+        <v>7.3416</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.059</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.1112</v>
+        <v>-1.652</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3544</v>
+        <v>-0.2223</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.9232</v>
+        <v>-6.2244</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.6</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6372</v>
+        <v>-0.4232</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.8416</v>
+        <v>-11.8496</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1851</v>
+        <v>1.1245</v>
       </c>
       <c r="J7" t="n">
-        <v>33.1828</v>
+        <v>31.486</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.38</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9318</v>
+        <v>0.9495</v>
       </c>
       <c r="J8" t="n">
-        <v>26.0904</v>
+        <v>26.586</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.23</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.6187</v>
       </c>
       <c r="J9" t="n">
-        <v>15.2572</v>
+        <v>17.3236</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.468</v>
+        <v>0.5466</v>
       </c>
       <c r="J10" t="n">
-        <v>13.104</v>
+        <v>15.3048</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.07</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1167</v>
+        <v>0.1967</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2676</v>
+        <v>5.5076</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.67</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9254</v>
+        <v>1.1078</v>
       </c>
       <c r="J12" t="n">
-        <v>22.2096</v>
+        <v>26.5872</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.27</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4541</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>10.8984</v>
+        <v>12.9312</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.11</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2118</v>
+        <v>0.2498</v>
       </c>
       <c r="J14" t="n">
-        <v>5.0832</v>
+        <v>5.9952</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.84</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3427</v>
+        <v>-0.2073</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.2248</v>
+        <v>-4.9752</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.51</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7607</v>
+        <v>-0.5174</v>
       </c>
       <c r="J16" t="n">
-        <v>-18.2568</v>
+        <v>-12.4176</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.69</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6287</v>
+        <v>1.4098</v>
       </c>
       <c r="J17" t="n">
-        <v>39.0888</v>
+        <v>33.8352</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4899</v>
+        <v>0.4778</v>
       </c>
       <c r="J18" t="n">
-        <v>11.7576</v>
+        <v>11.4672</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.09</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2589</v>
+        <v>0.2933</v>
       </c>
       <c r="J19" t="n">
-        <v>6.2136</v>
+        <v>7.0392</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.98</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1891</v>
+        <v>-0.1224</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.5384</v>
+        <v>-2.9376</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.65</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0445</v>
+        <v>-1.0251</v>
       </c>
       <c r="J21" t="n">
-        <v>-25.068</v>
+        <v>-24.6024</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.35</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6571</v>
+        <v>0.8119</v>
       </c>
       <c r="J22" t="n">
-        <v>10.5136</v>
+        <v>12.9904</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.79</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3296</v>
+        <v>-0.2254</v>
       </c>
       <c r="J23" t="n">
-        <v>-5.2736</v>
+        <v>-3.6064</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.75</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3965</v>
+        <v>-0.2637</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.344</v>
+        <v>-4.2192</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.66</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5285</v>
+        <v>-0.3493</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.456</v>
+        <v>-5.5888</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.48</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.76</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.16</v>
+        <v>-8.265599999999999</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>2.18</v>
       </c>
       <c r="I27" t="n">
-        <v>2.139</v>
+        <v>1.8681</v>
       </c>
       <c r="J27" t="n">
-        <v>34.224</v>
+        <v>29.8896</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.93</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8891</v>
+        <v>1.5942</v>
       </c>
       <c r="J28" t="n">
-        <v>30.2256</v>
+        <v>25.5072</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.25</v>
       </c>
       <c r="I29" t="n">
-        <v>0.514</v>
+        <v>0.6287</v>
       </c>
       <c r="J29" t="n">
-        <v>8.224</v>
+        <v>10.0592</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.13</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2268</v>
+        <v>0.3274</v>
       </c>
       <c r="J30" t="n">
-        <v>3.6288</v>
+        <v>5.2384</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.8</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7793</v>
+        <v>-0.7276</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.4688</v>
+        <v>-11.6416</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>2.12</v>
       </c>
       <c r="I32" t="n">
-        <v>1.9454</v>
+        <v>1.4866</v>
       </c>
       <c r="J32" t="n">
-        <v>27.2356</v>
+        <v>20.8124</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.96</v>
       </c>
       <c r="I33" t="n">
-        <v>1.8009</v>
+        <v>1.3152</v>
       </c>
       <c r="J33" t="n">
-        <v>25.2126</v>
+        <v>18.4128</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.7</v>
       </c>
       <c r="I34" t="n">
-        <v>1.3947</v>
+        <v>1.032</v>
       </c>
       <c r="J34" t="n">
-        <v>19.5258</v>
+        <v>14.448</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.36</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6923</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>9.6922</v>
+        <v>8.8424</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.17</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2792</v>
+        <v>0.3689</v>
       </c>
       <c r="J36" t="n">
-        <v>3.9088</v>
+        <v>5.1646</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.72</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2459</v>
+        <v>-0.2171</v>
       </c>
       <c r="J37" t="n">
-        <v>-3.4426</v>
+        <v>-3.0394</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.64</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3677</v>
+        <v>-0.3065</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.1478</v>
+        <v>-4.291</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.44</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.7158</v>
+        <v>-0.4998</v>
       </c>
       <c r="J39" t="n">
-        <v>-10.0212</v>
+        <v>-6.9972</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.41</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7619</v>
+        <v>-0.5286</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.6666</v>
+        <v>-7.4004</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.27</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9560999999999999</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.3854</v>
+        <v>-9.3492</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.23</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6774</v>
+        <v>0.5231</v>
       </c>
       <c r="J42" t="n">
-        <v>20.322</v>
+        <v>15.693</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.21</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6272</v>
+        <v>0.494</v>
       </c>
       <c r="J43" t="n">
-        <v>18.816</v>
+        <v>14.82</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.09</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2641</v>
+        <v>0.2944</v>
       </c>
       <c r="J44" t="n">
-        <v>7.923</v>
+        <v>8.832000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.02</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0192</v>
+        <v>0.0706</v>
       </c>
       <c r="J45" t="n">
-        <v>0.576</v>
+        <v>2.118</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.99</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1434</v>
+        <v>-0.0798</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.302</v>
+        <v>-2.394</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.26</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4564</v>
+        <v>0.453</v>
       </c>
       <c r="J47" t="n">
-        <v>13.692</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.12</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2491</v>
+        <v>0.2787</v>
       </c>
       <c r="J48" t="n">
-        <v>7.473</v>
+        <v>8.361000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.09</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1975</v>
+        <v>0.2188</v>
       </c>
       <c r="J49" t="n">
-        <v>5.925</v>
+        <v>6.564</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.87</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2861</v>
+        <v>-0.1705</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.583</v>
+        <v>-5.115</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.82</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3619</v>
+        <v>-0.2225</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.857</v>
+        <v>-6.675</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.79</v>
       </c>
       <c r="I52" t="n">
-        <v>1.7126</v>
+        <v>1.2017</v>
       </c>
       <c r="J52" t="n">
-        <v>30.8268</v>
+        <v>21.6306</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.4</v>
       </c>
       <c r="I53" t="n">
-        <v>0.9695</v>
+        <v>0.7222</v>
       </c>
       <c r="J53" t="n">
-        <v>17.451</v>
+        <v>12.9996</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.15</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3337</v>
+        <v>0.3834</v>
       </c>
       <c r="J54" t="n">
-        <v>6.0066</v>
+        <v>6.9012</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3074</v>
+        <v>0.3679</v>
       </c>
       <c r="J55" t="n">
-        <v>5.5332</v>
+        <v>6.6222</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3223</v>
+        <v>-0.2383</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.8014</v>
+        <v>-4.2894</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.99</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0867</v>
+        <v>0.0459</v>
       </c>
       <c r="J57" t="n">
-        <v>1.5606</v>
+        <v>0.8262</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.83</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2111</v>
+        <v>-0.1768</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.7998</v>
+        <v>-3.1824</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.8</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2606</v>
+        <v>-0.2079</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.6908</v>
+        <v>-3.7422</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5904</v>
+        <v>-0.3957</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.6272</v>
+        <v>-7.1226</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.48</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7471</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>-13.4478</v>
+        <v>-9.136799999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.45</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1175</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>26.82</v>
+        <v>19.2456</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.4</v>
       </c>
       <c r="I63" t="n">
-        <v>1.0124</v>
+        <v>0.7368</v>
       </c>
       <c r="J63" t="n">
-        <v>24.2976</v>
+        <v>17.6832</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.24</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6395</v>
+        <v>0.5218</v>
       </c>
       <c r="J64" t="n">
-        <v>15.348</v>
+        <v>12.5232</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.02</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0251</v>
+        <v>0.0459</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.6024</v>
+        <v>1.1016</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.92</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4215</v>
+        <v>-0.3459</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.116</v>
+        <v>-8.301600000000001</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.36</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6082</v>
+        <v>0.5704</v>
       </c>
       <c r="J67" t="n">
-        <v>14.5968</v>
+        <v>13.6896</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.09</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2238</v>
+        <v>0.2347</v>
       </c>
       <c r="J68" t="n">
-        <v>5.3712</v>
+        <v>5.6328</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0232</v>
+        <v>0.005</v>
       </c>
       <c r="J69" t="n">
-        <v>0.5568</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.8</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3753</v>
+        <v>-0.235</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.007199999999999</v>
+        <v>-5.64</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.58</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6651</v>
+        <v>-0.4439</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.9624</v>
+        <v>-10.6536</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.85</v>
       </c>
       <c r="I72" t="n">
-        <v>1.8013</v>
+        <v>1.299</v>
       </c>
       <c r="J72" t="n">
-        <v>37.8273</v>
+        <v>27.279</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.49</v>
       </c>
       <c r="I73" t="n">
-        <v>1.1982</v>
+        <v>0.853</v>
       </c>
       <c r="J73" t="n">
-        <v>25.1622</v>
+        <v>17.913</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.16</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4007</v>
+        <v>0.4089</v>
       </c>
       <c r="J74" t="n">
-        <v>8.4147</v>
+        <v>8.5869</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.82</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.625</v>
       </c>
       <c r="J75" t="n">
-        <v>-14.364</v>
+        <v>-13.125</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.72</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.9135</v>
+        <v>-0.8776</v>
       </c>
       <c r="J76" t="n">
-        <v>-19.1835</v>
+        <v>-18.4296</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.34</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5783</v>
+        <v>0.5464</v>
       </c>
       <c r="J77" t="n">
-        <v>12.1443</v>
+        <v>11.4744</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.14</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3007</v>
+        <v>0.3286</v>
       </c>
       <c r="J78" t="n">
-        <v>6.3147</v>
+        <v>6.9006</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.13</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2849</v>
+        <v>0.3114</v>
       </c>
       <c r="J79" t="n">
-        <v>5.9829</v>
+        <v>6.5394</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.74</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4631</v>
+        <v>-0.2957</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.725099999999999</v>
+        <v>-6.2097</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.55</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.703</v>
+        <v>-0.4726</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.763</v>
+        <v>-9.9246</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.5</v>
       </c>
       <c r="I82" t="n">
-        <v>1.2555</v>
+        <v>0.8854</v>
       </c>
       <c r="J82" t="n">
-        <v>37.665</v>
+        <v>26.562</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.47</v>
       </c>
       <c r="I83" t="n">
-        <v>1.1951</v>
+        <v>0.8461</v>
       </c>
       <c r="J83" t="n">
-        <v>35.853</v>
+        <v>25.383</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.11</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3065</v>
+        <v>0.3388</v>
       </c>
       <c r="J84" t="n">
-        <v>9.195</v>
+        <v>10.164</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.85</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5887</v>
+        <v>-0.5264</v>
       </c>
       <c r="J85" t="n">
-        <v>-17.661</v>
+        <v>-15.792</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.74</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-0.8109</v>
       </c>
       <c r="J86" t="n">
-        <v>-25.569</v>
+        <v>-24.327</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.39</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6141</v>
+        <v>0.5773</v>
       </c>
       <c r="J87" t="n">
-        <v>18.423</v>
+        <v>17.319</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.16</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3026</v>
+        <v>0.3413</v>
       </c>
       <c r="J88" t="n">
-        <v>9.077999999999999</v>
+        <v>10.239</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.97</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1152</v>
+        <v>-0.0559</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.456</v>
+        <v>-1.677</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.96</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1362</v>
+        <v>-0.0693</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.086</v>
+        <v>-2.079</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.82</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3679</v>
+        <v>-0.2256</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.037</v>
+        <v>-6.768</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.76</v>
       </c>
       <c r="I92" t="n">
-        <v>1.017</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="J92" t="n">
-        <v>24.408</v>
+        <v>21.9072</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.99</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0766</v>
+        <v>-0.0287</v>
       </c>
       <c r="J93" t="n">
-        <v>-1.8384</v>
+        <v>-0.6888</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.96</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1443</v>
+        <v>-0.0722</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.4632</v>
+        <v>-1.7328</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.88</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2836</v>
+        <v>-0.1659</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.8064</v>
+        <v>-3.9816</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.85</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3295</v>
+        <v>-0.1978</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.908</v>
+        <v>-4.7472</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.28</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8351</v>
+        <v>0.6107</v>
       </c>
       <c r="J97" t="n">
-        <v>20.0424</v>
+        <v>14.6568</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.11</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3973</v>
+        <v>0.3514</v>
       </c>
       <c r="J98" t="n">
-        <v>9.5352</v>
+        <v>8.4336</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.03</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1066</v>
+        <v>0.1224</v>
       </c>
       <c r="J99" t="n">
-        <v>2.5584</v>
+        <v>2.9376</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.92</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3582</v>
+        <v>-0.302</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.5968</v>
+        <v>-7.248</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.87</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5022</v>
+        <v>-0.4459</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.0528</v>
+        <v>-10.7016</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.51</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.5228</v>
       </c>
       <c r="J102" t="n">
-        <v>16.2448</v>
+        <v>11.5016</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.3</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4824</v>
+        <v>0.3805</v>
       </c>
       <c r="J103" t="n">
-        <v>10.6128</v>
+        <v>8.371</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.04</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0519</v>
+        <v>0.0704</v>
       </c>
       <c r="J104" t="n">
-        <v>1.1418</v>
+        <v>1.5488</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.9</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2577</v>
+        <v>-0.1468</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.6694</v>
+        <v>-3.2296</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3642</v>
+        <v>-0.2214</v>
       </c>
       <c r="J106" t="n">
-        <v>-8.0124</v>
+        <v>-4.8708</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.15</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3397</v>
+        <v>0.2856</v>
       </c>
       <c r="J107" t="n">
-        <v>7.4734</v>
+        <v>6.2832</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0424</v>
       </c>
       <c r="J108" t="n">
-        <v>1.7842</v>
+        <v>0.9328</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.97</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0381</v>
+        <v>-0.0426</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.8381999999999999</v>
+        <v>-0.9372</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.91</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.172</v>
+        <v>-0.1147</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.784</v>
+        <v>-2.5234</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.54</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7058</v>
+        <v>-0.4749</v>
       </c>
       <c r="J111" t="n">
-        <v>-15.5276</v>
+        <v>-10.4478</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.42</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6851</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="J112" t="n">
-        <v>19.8679</v>
+        <v>18.3744</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.09</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2276</v>
+        <v>0.2376</v>
       </c>
       <c r="J113" t="n">
-        <v>6.6004</v>
+        <v>6.8904</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.79</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3872</v>
+        <v>-0.2438</v>
       </c>
       <c r="J114" t="n">
-        <v>-11.2288</v>
+        <v>-7.0702</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.76</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4301</v>
+        <v>-0.2733</v>
       </c>
       <c r="J115" t="n">
-        <v>-12.4729</v>
+        <v>-7.9257</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.72</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4851</v>
+        <v>-0.312</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.0679</v>
+        <v>-9.048</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.63</v>
       </c>
       <c r="I117" t="n">
-        <v>1.4998</v>
+        <v>1.0481</v>
       </c>
       <c r="J117" t="n">
-        <v>43.4942</v>
+        <v>30.3949</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2655</v>
+        <v>0.3137</v>
       </c>
       <c r="J118" t="n">
-        <v>7.6995</v>
+        <v>9.097300000000001</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.08</v>
       </c>
       <c r="I119" t="n">
-        <v>0.204</v>
+        <v>0.2572</v>
       </c>
       <c r="J119" t="n">
-        <v>5.916</v>
+        <v>7.4588</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.99</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1615</v>
+        <v>-0.0902</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.6835</v>
+        <v>-2.6158</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.342</v>
+        <v>-0.2693</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.917999999999999</v>
+        <v>-7.8097</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>2.13</v>
       </c>
       <c r="I122" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J122" t="n">
-        <v>47.3639</v>
+        <v>42.1774</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.49</v>
       </c>
       <c r="I123" t="n">
-        <v>1.1717</v>
+        <v>1.1149</v>
       </c>
       <c r="J123" t="n">
-        <v>26.9491</v>
+        <v>25.6427</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.97</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2807</v>
+        <v>-0.1972</v>
       </c>
       <c r="J124" t="n">
-        <v>-6.4561</v>
+        <v>-4.5356</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5306</v>
       </c>
       <c r="J125" t="n">
-        <v>-13.7609</v>
+        <v>-12.2038</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5306</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.7609</v>
+        <v>-12.2038</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.23</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4478</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="J127" t="n">
-        <v>10.2994</v>
+        <v>11.8818</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.11</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2682</v>
+        <v>0.2848</v>
       </c>
       <c r="J128" t="n">
-        <v>6.1686</v>
+        <v>6.5504</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1182</v>
+        <v>-0.0828</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.7186</v>
+        <v>-1.9044</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.79</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3824</v>
+        <v>-0.2416</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.795199999999999</v>
+        <v>-5.5568</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.62</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6113</v>
+        <v>-0.404</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.0599</v>
+        <v>-9.292</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.78</v>
       </c>
       <c r="I132" t="n">
-        <v>1.6258</v>
+        <v>1.4206</v>
       </c>
       <c r="J132" t="n">
-        <v>27.6386</v>
+        <v>24.1502</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.51</v>
       </c>
       <c r="I133" t="n">
-        <v>1.1029</v>
+        <v>1.1074</v>
       </c>
       <c r="J133" t="n">
-        <v>18.7493</v>
+        <v>18.8258</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.43</v>
       </c>
       <c r="I134" t="n">
-        <v>0.9056999999999999</v>
+        <v>1.0073</v>
       </c>
       <c r="J134" t="n">
-        <v>15.3969</v>
+        <v>17.1241</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.36</v>
       </c>
       <c r="I135" t="n">
-        <v>0.7518</v>
+        <v>0.8742</v>
       </c>
       <c r="J135" t="n">
-        <v>12.7806</v>
+        <v>14.8614</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.3</v>
       </c>
       <c r="I136" t="n">
-        <v>0.6201</v>
+        <v>0.7409</v>
       </c>
       <c r="J136" t="n">
-        <v>10.5417</v>
+        <v>12.5953</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.09</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3206</v>
+        <v>0.3432</v>
       </c>
       <c r="J137" t="n">
-        <v>5.4502</v>
+        <v>5.8344</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.87</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1389</v>
+        <v>-0.1304</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.3613</v>
+        <v>-2.2168</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.77</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.3037</v>
+        <v>-0.2359</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.1629</v>
+        <v>-4.0103</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.49</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.7318</v>
+        <v>-0.4965</v>
       </c>
       <c r="J140" t="n">
-        <v>-12.4406</v>
+        <v>-8.4405</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.42</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.8186</v>
+        <v>-0.5615</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.9162</v>
+        <v>-9.545500000000001</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.57</v>
       </c>
       <c r="I142" t="n">
-        <v>1.3188</v>
+        <v>1.2096</v>
       </c>
       <c r="J142" t="n">
-        <v>22.4196</v>
+        <v>20.5632</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.48</v>
       </c>
       <c r="I143" t="n">
-        <v>1.1396</v>
+        <v>1.0976</v>
       </c>
       <c r="J143" t="n">
-        <v>19.3732</v>
+        <v>18.6592</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.14</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3082</v>
+        <v>0.3918</v>
       </c>
       <c r="J144" t="n">
-        <v>5.2394</v>
+        <v>6.6606</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.14</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3082</v>
+        <v>0.3918</v>
       </c>
       <c r="J145" t="n">
-        <v>5.2394</v>
+        <v>6.6606</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.1</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1998</v>
+        <v>0.2823</v>
       </c>
       <c r="J146" t="n">
-        <v>3.3966</v>
+        <v>4.7991</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.29</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5578</v>
+        <v>0.6657</v>
       </c>
       <c r="J147" t="n">
-        <v>9.4826</v>
+        <v>11.3169</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.06</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2113</v>
+        <v>0.204</v>
       </c>
       <c r="J148" t="n">
-        <v>3.5921</v>
+        <v>3.468</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.74</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.432</v>
+        <v>-0.2805</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.344</v>
+        <v>-4.7685</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.65</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5566</v>
+        <v>-0.3662</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.462199999999999</v>
+        <v>-6.2254</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.4499</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.4223</v>
+        <v>-7.6483</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.32</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6007</v>
+        <v>0.5561</v>
       </c>
       <c r="J152" t="n">
-        <v>12.014</v>
+        <v>11.122</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.3198</v>
+        <v>-0.2109</v>
       </c>
       <c r="J153" t="n">
-        <v>-6.396</v>
+        <v>-4.218</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.77</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3837</v>
+        <v>-0.2501</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.674</v>
+        <v>-5.002</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.75</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4139</v>
+        <v>-0.2695</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.278</v>
+        <v>-5.39</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.6</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6194</v>
+        <v>-0.4116</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.388</v>
+        <v>-8.231999999999999</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.96</v>
       </c>
       <c r="I157" t="n">
-        <v>1.1742</v>
+        <v>1.0571</v>
       </c>
       <c r="J157" t="n">
-        <v>23.484</v>
+        <v>21.142</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.33</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4853</v>
+        <v>0.4293</v>
       </c>
       <c r="J158" t="n">
-        <v>9.706</v>
+        <v>8.586</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.06</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0593</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="J159" t="n">
-        <v>1.186</v>
+        <v>1.778</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.96</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1755</v>
+        <v>-0.0864</v>
       </c>
       <c r="J160" t="n">
-        <v>-3.51</v>
+        <v>-1.728</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.84</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3681</v>
+        <v>-0.2221</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.362</v>
+        <v>-4.442</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.94</v>
       </c>
       <c r="I162" t="n">
-        <v>1.8955</v>
+        <v>1.6015</v>
       </c>
       <c r="J162" t="n">
-        <v>30.328</v>
+        <v>25.624</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.59</v>
       </c>
       <c r="I163" t="n">
-        <v>1.2697</v>
+        <v>1.2011</v>
       </c>
       <c r="J163" t="n">
-        <v>20.3152</v>
+        <v>19.2176</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.53</v>
       </c>
       <c r="I164" t="n">
-        <v>1.1464</v>
+        <v>1.1308</v>
       </c>
       <c r="J164" t="n">
-        <v>18.3424</v>
+        <v>18.0928</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.36</v>
       </c>
       <c r="I165" t="n">
-        <v>0.7518</v>
+        <v>0.8742</v>
       </c>
       <c r="J165" t="n">
-        <v>12.0288</v>
+        <v>13.9872</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.96</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3652</v>
+        <v>-0.278</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.8432</v>
+        <v>-4.448</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.77</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.2539</v>
+        <v>-0.2164</v>
       </c>
       <c r="J167" t="n">
-        <v>-4.0624</v>
+        <v>-3.4624</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.72</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.3322</v>
+        <v>-0.268</v>
       </c>
       <c r="J168" t="n">
-        <v>-5.3152</v>
+        <v>-4.288</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.61</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.5302</v>
+        <v>-0.3699</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.4832</v>
+        <v>-5.9184</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.55</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.6227</v>
+        <v>-0.4252</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.963200000000001</v>
+        <v>-6.8032</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.54</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6371</v>
+        <v>-0.4345</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.1936</v>
+        <v>-6.952</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.51</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2642</v>
+        <v>1.1658</v>
       </c>
       <c r="J172" t="n">
-        <v>36.6618</v>
+        <v>33.8082</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.32</v>
       </c>
       <c r="I173" t="n">
-        <v>0.8629</v>
+        <v>0.8534</v>
       </c>
       <c r="J173" t="n">
-        <v>25.0241</v>
+        <v>24.7486</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.6223</v>
+        <v>0.6166</v>
       </c>
       <c r="J174" t="n">
-        <v>18.0467</v>
+        <v>17.8814</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.92</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4053</v>
+        <v>-0.3331</v>
       </c>
       <c r="J175" t="n">
-        <v>-11.7537</v>
+        <v>-9.6599</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6946</v>
+        <v>-0.6384</v>
       </c>
       <c r="J176" t="n">
-        <v>-20.1434</v>
+        <v>-18.5136</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.51</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7948</v>
+        <v>0.99</v>
       </c>
       <c r="J177" t="n">
-        <v>23.0492</v>
+        <v>28.71</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.98</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0281</v>
+        <v>-0.0316</v>
       </c>
       <c r="J178" t="n">
-        <v>-0.8149</v>
+        <v>-0.9164</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.95</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.0988</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.8652</v>
+        <v>-2.0706</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.71</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4959</v>
+        <v>-0.3202</v>
       </c>
       <c r="J180" t="n">
-        <v>-14.3811</v>
+        <v>-9.2858</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.57</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-0.4507</v>
       </c>
       <c r="J181" t="n">
-        <v>-19.5431</v>
+        <v>-13.0703</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.21</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4191</v>
+        <v>0.3663</v>
       </c>
       <c r="J182" t="n">
-        <v>10.0584</v>
+        <v>8.7912</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.16</v>
       </c>
       <c r="I183" t="n">
-        <v>0.346</v>
+        <v>0.2936</v>
       </c>
       <c r="J183" t="n">
-        <v>8.304</v>
+        <v>7.0464</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.95</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0958</v>
+        <v>-0.0711</v>
       </c>
       <c r="J184" t="n">
-        <v>-2.2992</v>
+        <v>-1.7064</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.87</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.258</v>
+        <v>-0.16</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.192</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.51</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7448</v>
+        <v>-0.5046</v>
       </c>
       <c r="J186" t="n">
-        <v>-17.8752</v>
+        <v>-12.1104</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.33</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5322</v>
+        <v>0.4556</v>
       </c>
       <c r="J187" t="n">
-        <v>12.7728</v>
+        <v>10.9344</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.31</v>
       </c>
       <c r="I188" t="n">
-        <v>0.5064</v>
+        <v>0.4317</v>
       </c>
       <c r="J188" t="n">
-        <v>12.1536</v>
+        <v>10.3608</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.18</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3252</v>
+        <v>0.2706</v>
       </c>
       <c r="J189" t="n">
-        <v>7.8048</v>
+        <v>6.4944</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.85</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3283</v>
+        <v>-0.1971</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.8792</v>
+        <v>-4.7304</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.74</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4819</v>
+        <v>-0.3069</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.5656</v>
+        <v>-7.3656</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.96</v>
       </c>
       <c r="I192" t="n">
-        <v>1.9014</v>
+        <v>1.6096</v>
       </c>
       <c r="J192" t="n">
-        <v>30.4224</v>
+        <v>25.7536</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.65</v>
       </c>
       <c r="I193" t="n">
-        <v>1.3555</v>
+        <v>1.2618</v>
       </c>
       <c r="J193" t="n">
-        <v>21.688</v>
+        <v>20.1888</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.58</v>
       </c>
       <c r="I194" t="n">
-        <v>1.2133</v>
+        <v>1.182</v>
       </c>
       <c r="J194" t="n">
-        <v>19.4128</v>
+        <v>18.912</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.33</v>
       </c>
       <c r="I195" t="n">
-        <v>0.6629</v>
+        <v>0.7951</v>
       </c>
       <c r="J195" t="n">
-        <v>10.6064</v>
+        <v>12.7216</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.2</v>
       </c>
       <c r="I196" t="n">
-        <v>0.3749</v>
+        <v>0.4905</v>
       </c>
       <c r="J196" t="n">
-        <v>5.9984</v>
+        <v>7.848</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.19</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4912</v>
+        <v>0.5855</v>
       </c>
       <c r="J197" t="n">
-        <v>7.8592</v>
+        <v>9.368</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.03</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2223</v>
+        <v>0.2139</v>
       </c>
       <c r="J198" t="n">
-        <v>3.5568</v>
+        <v>3.4224</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.52</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.6852</v>
+        <v>-0.4637</v>
       </c>
       <c r="J199" t="n">
-        <v>-10.9632</v>
+        <v>-7.4192</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.47</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.7501</v>
+        <v>-0.5105</v>
       </c>
       <c r="J200" t="n">
-        <v>-12.0016</v>
+        <v>-8.167999999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.28</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.9794</v>
+        <v>-0.6876</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.6704</v>
+        <v>-11.0016</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.05</v>
       </c>
       <c r="I202" t="n">
-        <v>0.2086</v>
+        <v>0.1971</v>
       </c>
       <c r="J202" t="n">
-        <v>3.7548</v>
+        <v>3.5478</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.01</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1209</v>
+        <v>0.0883</v>
       </c>
       <c r="J203" t="n">
-        <v>2.1762</v>
+        <v>1.5894</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.71</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.4622</v>
+        <v>-0.3038</v>
       </c>
       <c r="J204" t="n">
-        <v>-8.319599999999999</v>
+        <v>-5.4684</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4909</v>
+        <v>-0.3229</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.8362</v>
+        <v>-5.8122</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.64</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5597</v>
+        <v>-0.3701</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.0746</v>
+        <v>-6.6618</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.79</v>
       </c>
       <c r="I207" t="n">
-        <v>1.6895</v>
+        <v>1.4552</v>
       </c>
       <c r="J207" t="n">
-        <v>30.411</v>
+        <v>26.1936</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.4</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9236</v>
+        <v>0.97</v>
       </c>
       <c r="J208" t="n">
-        <v>16.6248</v>
+        <v>17.46</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.29</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6428</v>
+        <v>0.74</v>
       </c>
       <c r="J209" t="n">
-        <v>11.5704</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.26</v>
       </c>
       <c r="I210" t="n">
-        <v>0.572</v>
+        <v>0.6711</v>
       </c>
       <c r="J210" t="n">
-        <v>10.296</v>
+        <v>12.0798</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.09</v>
       </c>
       <c r="I211" t="n">
-        <v>0.1455</v>
+        <v>0.2354</v>
       </c>
       <c r="J211" t="n">
-        <v>2.619</v>
+        <v>4.2372</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.34</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5763</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J212" t="n">
-        <v>13.2549</v>
+        <v>15.916</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.17</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3445</v>
+        <v>0.3873</v>
       </c>
       <c r="J213" t="n">
-        <v>7.9235</v>
+        <v>8.9079</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.96</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1079</v>
+        <v>-0.062</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.4817</v>
+        <v>-1.426</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.82</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3509</v>
+        <v>-0.2172</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.0707</v>
+        <v>-4.9956</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.64</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5944</v>
+        <v>-0.3909</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.6712</v>
+        <v>-8.9907</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.29</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8287</v>
+        <v>0.8056</v>
       </c>
       <c r="J217" t="n">
-        <v>19.0601</v>
+        <v>18.5288</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.2</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6103</v>
+        <v>0.585</v>
       </c>
       <c r="J218" t="n">
-        <v>14.0369</v>
+        <v>13.455</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.12</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3877</v>
+        <v>0.3777</v>
       </c>
       <c r="J219" t="n">
-        <v>8.9171</v>
+        <v>8.687099999999999</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.99</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1364</v>
+        <v>-0.0761</v>
       </c>
       <c r="J220" t="n">
-        <v>-3.1372</v>
+        <v>-1.7503</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.87</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5228</v>
+        <v>-0.4607</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.0244</v>
+        <v>-10.5961</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.89</v>
       </c>
       <c r="I222" t="n">
-        <v>1.0703</v>
+        <v>0.9819</v>
       </c>
       <c r="J222" t="n">
-        <v>19.2654</v>
+        <v>17.6742</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.77</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9500999999999999</v>
+        <v>0.8711</v>
       </c>
       <c r="J223" t="n">
-        <v>17.1018</v>
+        <v>15.6798</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.23</v>
       </c>
       <c r="I224" t="n">
-        <v>0.2873</v>
+        <v>0.3017</v>
       </c>
       <c r="J224" t="n">
-        <v>5.1714</v>
+        <v>5.4306</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.01</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.067</v>
+        <v>-0.0128</v>
       </c>
       <c r="J225" t="n">
-        <v>-1.206</v>
+        <v>-0.2304</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2328</v>
+        <v>-0.1237</v>
       </c>
       <c r="J226" t="n">
-        <v>-4.1904</v>
+        <v>-2.2266</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.22</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4725</v>
+        <v>0.419</v>
       </c>
       <c r="J227" t="n">
-        <v>8.505000000000001</v>
+        <v>7.542</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.96</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0239</v>
+        <v>-0.0439</v>
       </c>
       <c r="J228" t="n">
-        <v>-0.4302</v>
+        <v>-0.7902</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0639</v>
+        <v>-0.0699</v>
       </c>
       <c r="J229" t="n">
-        <v>-1.1502</v>
+        <v>-1.2582</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.61</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.6034</v>
+        <v>-0.4004</v>
       </c>
       <c r="J230" t="n">
-        <v>-10.8612</v>
+        <v>-7.2072</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.45</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.8007</v>
+        <v>-0.5476</v>
       </c>
       <c r="J231" t="n">
-        <v>-14.4126</v>
+        <v>-9.8568</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.03</v>
       </c>
       <c r="I232" t="n">
-        <v>0.21</v>
+        <v>0.1967</v>
       </c>
       <c r="J232" t="n">
-        <v>3.78</v>
+        <v>3.5406</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.79</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.2683</v>
+        <v>-0.2152</v>
       </c>
       <c r="J233" t="n">
-        <v>-4.8294</v>
+        <v>-3.8736</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.71</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.4167</v>
+        <v>-0.2908</v>
       </c>
       <c r="J234" t="n">
-        <v>-7.5006</v>
+        <v>-5.2344</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.55</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.653</v>
+        <v>-0.4399</v>
       </c>
       <c r="J235" t="n">
-        <v>-11.754</v>
+        <v>-7.9182</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.54</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6663</v>
+        <v>-0.4492</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.9934</v>
+        <v>-8.085599999999999</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.8</v>
       </c>
       <c r="I237" t="n">
-        <v>1.7123</v>
+        <v>1.4698</v>
       </c>
       <c r="J237" t="n">
-        <v>30.8214</v>
+        <v>26.4564</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.51</v>
       </c>
       <c r="I238" t="n">
-        <v>1.1677</v>
+        <v>1.123</v>
       </c>
       <c r="J238" t="n">
-        <v>21.0186</v>
+        <v>20.214</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.23</v>
       </c>
       <c r="I239" t="n">
-        <v>0.5057</v>
+        <v>0.6028</v>
       </c>
       <c r="J239" t="n">
-        <v>9.102600000000001</v>
+        <v>10.8504</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.17</v>
       </c>
       <c r="I240" t="n">
-        <v>0.3592</v>
+        <v>0.4546</v>
       </c>
       <c r="J240" t="n">
-        <v>6.4656</v>
+        <v>8.1828</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.06</v>
       </c>
       <c r="I241" t="n">
-        <v>0.0619</v>
+        <v>0.1478</v>
       </c>
       <c r="J241" t="n">
-        <v>1.1142</v>
+        <v>2.6604</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.36</v>
       </c>
       <c r="I242" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.7409</v>
       </c>
       <c r="J242" t="n">
-        <v>14.0852</v>
+        <v>17.0407</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.33</v>
       </c>
       <c r="I243" t="n">
-        <v>0.5747</v>
+        <v>0.6888</v>
       </c>
       <c r="J243" t="n">
-        <v>13.2181</v>
+        <v>15.8424</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.82</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3422</v>
+        <v>-0.2134</v>
       </c>
       <c r="J244" t="n">
-        <v>-7.8706</v>
+        <v>-4.9082</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.66</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5635</v>
+        <v>-0.3686</v>
       </c>
       <c r="J245" t="n">
-        <v>-12.9605</v>
+        <v>-8.4778</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.6</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6388</v>
+        <v>-0.4243</v>
       </c>
       <c r="J246" t="n">
-        <v>-14.6924</v>
+        <v>-9.758900000000001</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.78</v>
       </c>
       <c r="I247" t="n">
-        <v>1.7573</v>
+        <v>1.4977</v>
       </c>
       <c r="J247" t="n">
-        <v>40.4179</v>
+        <v>34.4471</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.21</v>
       </c>
       <c r="I248" t="n">
-        <v>0.5787</v>
+        <v>0.587</v>
       </c>
       <c r="J248" t="n">
-        <v>13.3101</v>
+        <v>13.501</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.03</v>
       </c>
       <c r="I249" t="n">
-        <v>0.0231</v>
+        <v>0.0895</v>
       </c>
       <c r="J249" t="n">
-        <v>0.5313</v>
+        <v>2.0585</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.97</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2539</v>
+        <v>-0.1769</v>
       </c>
       <c r="J250" t="n">
-        <v>-5.8397</v>
+        <v>-4.0687</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.91</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4421</v>
+        <v>-0.3692</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.1683</v>
+        <v>-8.4916</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.56</v>
       </c>
       <c r="I252" t="n">
-        <v>1.324</v>
+        <v>1.2091</v>
       </c>
       <c r="J252" t="n">
-        <v>26.48</v>
+        <v>24.182</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.25</v>
       </c>
       <c r="I253" t="n">
-        <v>0.6439</v>
+        <v>0.6708</v>
       </c>
       <c r="J253" t="n">
-        <v>12.878</v>
+        <v>13.416</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.22</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5486</v>
+        <v>0.6025</v>
       </c>
       <c r="J254" t="n">
-        <v>10.972</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.21</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5205</v>
+        <v>0.5789</v>
       </c>
       <c r="J255" t="n">
-        <v>10.41</v>
+        <v>11.578</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.93</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4006</v>
+        <v>-0.3223</v>
       </c>
       <c r="J256" t="n">
-        <v>-8.012</v>
+        <v>-6.446</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.15</v>
       </c>
       <c r="I257" t="n">
-        <v>0.3353</v>
+        <v>0.3686</v>
       </c>
       <c r="J257" t="n">
-        <v>6.706</v>
+        <v>7.372</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.1</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2553</v>
+        <v>0.2674</v>
       </c>
       <c r="J258" t="n">
-        <v>5.106</v>
+        <v>5.348</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.06</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1845</v>
+        <v>0.1803</v>
       </c>
       <c r="J259" t="n">
-        <v>3.69</v>
+        <v>3.606</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.71</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4923</v>
+        <v>-0.3182</v>
       </c>
       <c r="J260" t="n">
-        <v>-9.846</v>
+        <v>-6.364</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.62</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6095</v>
+        <v>-0.4028</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.19</v>
+        <v>-8.055999999999999</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.72</v>
       </c>
       <c r="I262" t="n">
-        <v>1.6638</v>
+        <v>1.4335</v>
       </c>
       <c r="J262" t="n">
-        <v>39.9312</v>
+        <v>34.404</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.35</v>
       </c>
       <c r="I263" t="n">
-        <v>0.9322</v>
+        <v>0.9232</v>
       </c>
       <c r="J263" t="n">
-        <v>22.3728</v>
+        <v>22.1568</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.97</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2433</v>
+        <v>-0.1697</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.8392</v>
+        <v>-4.0728</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3434</v>
+        <v>-0.2703</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.2416</v>
+        <v>-6.4872</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.78</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.7649</v>
+        <v>-0.7147</v>
       </c>
       <c r="J266" t="n">
-        <v>-18.3576</v>
+        <v>-17.1528</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.22</v>
       </c>
       <c r="I267" t="n">
-        <v>0.431</v>
+        <v>0.4949</v>
       </c>
       <c r="J267" t="n">
-        <v>10.344</v>
+        <v>11.8776</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.2</v>
       </c>
       <c r="I268" t="n">
-        <v>0.4027</v>
+        <v>0.4577</v>
       </c>
       <c r="J268" t="n">
-        <v>9.6648</v>
+        <v>10.9848</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.89</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2259</v>
+        <v>-0.1393</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.4216</v>
+        <v>-3.3432</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.88</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2433</v>
+        <v>-0.15</v>
       </c>
       <c r="J270" t="n">
-        <v>-5.8392</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.54</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.7102000000000001</v>
+        <v>-0.4782</v>
       </c>
       <c r="J271" t="n">
-        <v>-17.0448</v>
+        <v>-11.4768</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.17</v>
       </c>
       <c r="I272" t="n">
-        <v>0.412</v>
+        <v>0.4649</v>
       </c>
       <c r="J272" t="n">
-        <v>7.416</v>
+        <v>8.3682</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1</v>
       </c>
       <c r="I273" t="n">
-        <v>0.0915</v>
+        <v>0.0533</v>
       </c>
       <c r="J273" t="n">
-        <v>1.647</v>
+        <v>0.9594</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.96</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.0118</v>
+        <v>-0.0383</v>
       </c>
       <c r="J274" t="n">
-        <v>-0.2124</v>
+        <v>-0.6894</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.55</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-0.4523</v>
       </c>
       <c r="J275" t="n">
-        <v>-12.1302</v>
+        <v>-8.141400000000001</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.36</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.9012</v>
+        <v>-0.626</v>
       </c>
       <c r="J276" t="n">
-        <v>-16.2216</v>
+        <v>-11.268</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.56</v>
       </c>
       <c r="I277" t="n">
-        <v>1.2668</v>
+        <v>1.1836</v>
       </c>
       <c r="J277" t="n">
-        <v>22.8024</v>
+        <v>21.3048</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.48</v>
       </c>
       <c r="I278" t="n">
-        <v>1.1049</v>
+        <v>1.0859</v>
       </c>
       <c r="J278" t="n">
-        <v>19.8882</v>
+        <v>19.5462</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.39</v>
       </c>
       <c r="I279" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.9532</v>
       </c>
       <c r="J279" t="n">
-        <v>16.3224</v>
+        <v>17.1576</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.21</v>
       </c>
       <c r="I280" t="n">
-        <v>0.4567</v>
+        <v>0.554</v>
       </c>
       <c r="J280" t="n">
-        <v>8.220599999999999</v>
+        <v>9.972</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>1.14</v>
       </c>
       <c r="I281" t="n">
-        <v>0.2824</v>
+        <v>0.3761</v>
       </c>
       <c r="J281" t="n">
-        <v>5.0832</v>
+        <v>6.7698</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.22</v>
       </c>
       <c r="I282" t="n">
-        <v>0.4419</v>
+        <v>0.5075</v>
       </c>
       <c r="J282" t="n">
-        <v>9.7218</v>
+        <v>11.165</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.11</v>
       </c>
       <c r="I283" t="n">
-        <v>0.2764</v>
+        <v>0.2923</v>
       </c>
       <c r="J283" t="n">
-        <v>6.0808</v>
+        <v>6.4306</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.02</v>
       </c>
       <c r="I284" t="n">
-        <v>0.1064</v>
+        <v>0.0849</v>
       </c>
       <c r="J284" t="n">
-        <v>2.3408</v>
+        <v>1.8678</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.72</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4759</v>
+        <v>-0.3071</v>
       </c>
       <c r="J285" t="n">
-        <v>-10.4698</v>
+        <v>-6.7562</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.51</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.7415</v>
+        <v>-0.5021</v>
       </c>
       <c r="J286" t="n">
-        <v>-16.313</v>
+        <v>-11.0462</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.5</v>
       </c>
       <c r="I287" t="n">
-        <v>1.2382</v>
+        <v>1.1496</v>
       </c>
       <c r="J287" t="n">
-        <v>27.2404</v>
+        <v>25.2912</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.31</v>
       </c>
       <c r="I288" t="n">
-        <v>0.8334</v>
+        <v>0.8262</v>
       </c>
       <c r="J288" t="n">
-        <v>18.3348</v>
+        <v>18.1764</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.2</v>
       </c>
       <c r="I289" t="n">
-        <v>0.5605</v>
+        <v>0.5654</v>
       </c>
       <c r="J289" t="n">
-        <v>12.331</v>
+        <v>12.4388</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.93</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3797</v>
+        <v>-0.3058</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.353400000000001</v>
+        <v>-6.7276</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.9</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.4663</v>
+        <v>-0.3954</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.2586</v>
+        <v>-8.6988</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.81</v>
       </c>
       <c r="I292" t="n">
-        <v>1.7746</v>
+        <v>1.5094</v>
       </c>
       <c r="J292" t="n">
-        <v>33.7174</v>
+        <v>28.6786</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.26</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.6905</v>
       </c>
       <c r="J293" t="n">
-        <v>12.4013</v>
+        <v>13.1195</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.22</v>
       </c>
       <c r="I294" t="n">
-        <v>0.533</v>
+        <v>0.5991</v>
       </c>
       <c r="J294" t="n">
-        <v>10.127</v>
+        <v>11.3829</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.06</v>
       </c>
       <c r="I295" t="n">
-        <v>0.0941</v>
+        <v>0.171</v>
       </c>
       <c r="J295" t="n">
-        <v>1.7879</v>
+        <v>3.249</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.92</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4354</v>
+        <v>-0.3576</v>
       </c>
       <c r="J296" t="n">
-        <v>-8.272600000000001</v>
+        <v>-6.7944</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.7</v>
       </c>
       <c r="I297" t="n">
-        <v>1.0016</v>
+        <v>1.1806</v>
       </c>
       <c r="J297" t="n">
-        <v>19.0304</v>
+        <v>22.4314</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.86</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.2781</v>
+        <v>-0.1717</v>
       </c>
       <c r="J298" t="n">
-        <v>-5.2839</v>
+        <v>-3.2623</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.8</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.371</v>
+        <v>-0.2331</v>
       </c>
       <c r="J299" t="n">
-        <v>-7.049</v>
+        <v>-4.4289</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.74</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4565</v>
+        <v>-0.2921</v>
       </c>
       <c r="J300" t="n">
-        <v>-8.673500000000001</v>
+        <v>-5.5499</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.65</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5755</v>
+        <v>-0.3775</v>
       </c>
       <c r="J301" t="n">
-        <v>-10.9345</v>
+        <v>-7.1725</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.78</v>
       </c>
       <c r="I302" t="n">
-        <v>1.0545</v>
+        <v>1.0289</v>
       </c>
       <c r="J302" t="n">
-        <v>25.308</v>
+        <v>24.6936</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.91</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.2215</v>
+        <v>-0.127</v>
       </c>
       <c r="J303" t="n">
-        <v>-5.316</v>
+        <v>-3.048</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.85</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.3181</v>
+        <v>-0.1921</v>
       </c>
       <c r="J304" t="n">
-        <v>-7.6344</v>
+        <v>-4.6104</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.83</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3481</v>
+        <v>-0.2128</v>
       </c>
       <c r="J305" t="n">
-        <v>-8.3544</v>
+        <v>-5.1072</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3772</v>
+        <v>-0.2331</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.0528</v>
+        <v>-5.5944</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.4</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6169</v>
+        <v>0.5359</v>
       </c>
       <c r="J307" t="n">
-        <v>14.8056</v>
+        <v>12.8616</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.33</v>
       </c>
       <c r="I308" t="n">
-        <v>0.5296</v>
+        <v>0.4538</v>
       </c>
       <c r="J308" t="n">
-        <v>12.7104</v>
+        <v>10.8912</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.13</v>
       </c>
       <c r="I309" t="n">
-        <v>0.2421</v>
+        <v>0.2038</v>
       </c>
       <c r="J309" t="n">
-        <v>5.8104</v>
+        <v>4.8912</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.02</v>
       </c>
       <c r="I310" t="n">
-        <v>0.0169</v>
+        <v>0.0378</v>
       </c>
       <c r="J310" t="n">
-        <v>0.4056</v>
+        <v>0.9072</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.57</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6928</v>
+        <v>-0.4649</v>
       </c>
       <c r="J311" t="n">
-        <v>-16.6272</v>
+        <v>-11.1576</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.73</v>
       </c>
       <c r="I312" t="n">
-        <v>1.6658</v>
+        <v>1.4348</v>
       </c>
       <c r="J312" t="n">
-        <v>39.9792</v>
+        <v>34.4352</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.36</v>
       </c>
       <c r="I313" t="n">
-        <v>0.9371</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="J313" t="n">
-        <v>22.4904</v>
+        <v>22.416</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.1</v>
       </c>
       <c r="I314" t="n">
-        <v>0.2444</v>
+        <v>0.3062</v>
       </c>
       <c r="J314" t="n">
-        <v>5.8656</v>
+        <v>7.3488</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.9</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.4714</v>
+        <v>-0.3995</v>
       </c>
       <c r="J315" t="n">
-        <v>-11.3136</v>
+        <v>-9.587999999999999</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.83</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6534</v>
+        <v>-0.5928</v>
       </c>
       <c r="J316" t="n">
-        <v>-15.6816</v>
+        <v>-14.2272</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.16</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3381</v>
+        <v>0.376</v>
       </c>
       <c r="J317" t="n">
-        <v>8.1144</v>
+        <v>9.023999999999999</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.15</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3228</v>
+        <v>0.3567</v>
       </c>
       <c r="J318" t="n">
-        <v>7.7472</v>
+        <v>8.5608</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.12</v>
       </c>
       <c r="I319" t="n">
-        <v>0.2755</v>
+        <v>0.2974</v>
       </c>
       <c r="J319" t="n">
-        <v>6.612</v>
+        <v>7.1376</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.9</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2146</v>
+        <v>-0.1301</v>
       </c>
       <c r="J320" t="n">
-        <v>-5.1504</v>
+        <v>-3.1224</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.48</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.7824</v>
+        <v>-0.5337</v>
       </c>
       <c r="J321" t="n">
-        <v>-18.7776</v>
+        <v>-12.8088</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/8250/event_8250_evp_summary.xlsx
+++ b/database/event/8250/event_8250_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.8821</v>
+        <v>7.9367</v>
       </c>
       <c r="C2" t="n">
-        <v>2.6018</v>
+        <v>2.6199</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9204</v>
+        <v>2.9887</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8821</v>
+        <v>7.9367</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8088</v>
+        <v>3.7489</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0733</v>
+        <v>4.1878</v>
       </c>
       <c r="H2" t="n">
-        <v>7.9336</v>
+        <v>7.4749</v>
       </c>
       <c r="I2" t="n">
-        <v>4.1251</v>
+        <v>4.0364</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0733</v>
+        <v>4.1878</v>
       </c>
       <c r="K2" t="n">
         <v>136</v>
@@ -529,7 +529,7 @@
         <v>112</v>
       </c>
       <c r="M2" t="n">
-        <v>8.198399999999999</v>
+        <v>8.2242</v>
       </c>
       <c r="N2" t="n">
         <v>248</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4993</v>
+        <v>6.6104</v>
       </c>
       <c r="C3" t="n">
-        <v>2.1454</v>
+        <v>2.1821</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2961</v>
+        <v>2.385</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4993</v>
+        <v>6.6104</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7313</v>
+        <v>2.6538</v>
       </c>
       <c r="G3" t="n">
-        <v>3.768</v>
+        <v>3.9566</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1371</v>
+        <v>3.8615</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1511</v>
+        <v>2.0852</v>
       </c>
       <c r="J3" t="n">
-        <v>3.768</v>
+        <v>3.9566</v>
       </c>
       <c r="K3" t="n">
         <v>136</v>
@@ -575,7 +575,7 @@
         <v>112</v>
       </c>
       <c r="M3" t="n">
-        <v>5.9191</v>
+        <v>6.0418</v>
       </c>
       <c r="N3" t="n">
         <v>248</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0005</v>
+        <v>6.3069</v>
       </c>
       <c r="C4" t="n">
-        <v>1.9807</v>
+        <v>2.0819</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0709</v>
+        <v>2.2468</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0005</v>
+        <v>6.3069</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2522</v>
+        <v>1.2028</v>
       </c>
       <c r="G4" t="n">
-        <v>4.7483</v>
+        <v>5.1041</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2522</v>
+        <v>1.2028</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6511</v>
+        <v>0.6495</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7483</v>
+        <v>5.1041</v>
       </c>
       <c r="K4" t="n">
         <v>136</v>
@@ -621,7 +621,7 @@
         <v>112</v>
       </c>
       <c r="M4" t="n">
-        <v>5.3994</v>
+        <v>5.7536</v>
       </c>
       <c r="N4" t="n">
         <v>248</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.4444</v>
+        <v>5.4523</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7972</v>
+        <v>1.7998</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8199</v>
+        <v>1.8578</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4444</v>
+        <v>5.4523</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9188</v>
+        <v>3.848</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5256</v>
+        <v>1.6043</v>
       </c>
       <c r="H5" t="n">
-        <v>8.321099999999999</v>
+        <v>7.8018</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3266</v>
+        <v>4.2129</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5256</v>
+        <v>1.6043</v>
       </c>
       <c r="K5" t="n">
         <v>84</v>
@@ -667,7 +667,7 @@
         <v>110</v>
       </c>
       <c r="M5" t="n">
-        <v>5.8522</v>
+        <v>5.817200000000001</v>
       </c>
       <c r="N5" t="n">
         <v>194</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.3561</v>
+        <v>5.4497</v>
       </c>
       <c r="C6" t="n">
-        <v>1.768</v>
+        <v>1.7989</v>
       </c>
       <c r="D6" t="n">
-        <v>1.78</v>
+        <v>1.8566</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3561</v>
+        <v>5.4497</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5324</v>
+        <v>3.517</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8237</v>
+        <v>1.9327</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4363</v>
+        <v>6.7097</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7867</v>
+        <v>3.6232</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8237</v>
+        <v>1.9327</v>
       </c>
       <c r="K6" t="n">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="L6" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6104</v>
+        <v>5.5559</v>
       </c>
       <c r="N6" t="n">
-        <v>248</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.3361</v>
+        <v>5.3766</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7614</v>
+        <v>1.7748</v>
       </c>
       <c r="D7" t="n">
-        <v>1.771</v>
+        <v>1.8233</v>
       </c>
       <c r="E7" t="n">
-        <v>5.3361</v>
+        <v>5.3766</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5129</v>
+        <v>2.496</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8232</v>
+        <v>2.8806</v>
       </c>
       <c r="H7" t="n">
-        <v>6.891</v>
+        <v>3.341</v>
       </c>
       <c r="I7" t="n">
-        <v>3.583</v>
+        <v>1.8041</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8232</v>
+        <v>2.8806</v>
       </c>
       <c r="K7" t="n">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="L7" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M7" t="n">
-        <v>5.4062</v>
+        <v>4.684699999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>194</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.1283</v>
+        <v>4.1439</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3627</v>
+        <v>1.3679</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2257</v>
+        <v>1.2622</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1283</v>
+        <v>4.1439</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4918</v>
+        <v>2.4103</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6365</v>
+        <v>1.7336</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2934</v>
+        <v>3.0584</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7124</v>
+        <v>1.6515</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6365</v>
+        <v>1.7336</v>
       </c>
       <c r="K8" t="n">
         <v>84</v>
@@ -805,7 +805,7 @@
         <v>110</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3489</v>
+        <v>3.3851</v>
       </c>
       <c r="N8" t="n">
         <v>194</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4615</v>
+        <v>3.2355</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1426</v>
+        <v>1.068</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9247</v>
+        <v>0.8487</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4615</v>
+        <v>3.2355</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8297</v>
+        <v>2.5279</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6318</v>
+        <v>0.7076</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8537</v>
+        <v>2.8079</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9711</v>
+        <v>2.8803</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6318</v>
+        <v>0.7076</v>
       </c>
       <c r="K9" t="n">
         <v>109</v>
@@ -851,7 +851,7 @@
         <v>75</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6029</v>
+        <v>3.5879</v>
       </c>
       <c r="N9" t="n">
         <v>184</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2786</v>
+        <v>3.0777</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0822</v>
+        <v>1.0159</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8421</v>
+        <v>0.7768</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2786</v>
+        <v>3.0777</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9869</v>
+        <v>2.4192</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2917</v>
+        <v>0.6585</v>
       </c>
       <c r="H10" t="n">
-        <v>3.199</v>
+        <v>3.0876</v>
       </c>
       <c r="I10" t="n">
-        <v>3.199</v>
+        <v>1.6673</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2917</v>
+        <v>0.6585</v>
       </c>
       <c r="K10" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="L10" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4907</v>
+        <v>2.3258</v>
       </c>
       <c r="N10" t="n">
-        <v>214</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1598</v>
+        <v>3.0343</v>
       </c>
       <c r="C11" t="n">
-        <v>1.043</v>
+        <v>1.0016</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7885</v>
+        <v>0.7571</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1598</v>
+        <v>3.0343</v>
       </c>
       <c r="F11" t="n">
-        <v>2.494</v>
+        <v>2.6834</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.3509</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3011</v>
+        <v>3.1481</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7164</v>
+        <v>3.1481</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.3509</v>
       </c>
       <c r="K11" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="L11" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="M11" t="n">
-        <v>2.3822</v>
+        <v>3.499</v>
       </c>
       <c r="N11" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0833</v>
+        <v>2.932</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0178</v>
+        <v>0.9678</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7539</v>
+        <v>0.7105</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0833</v>
+        <v>2.932</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6293</v>
+        <v>2.3948</v>
       </c>
       <c r="G12" t="n">
-        <v>0.454</v>
+        <v>0.5372</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6293</v>
+        <v>2.5165</v>
       </c>
       <c r="I12" t="n">
-        <v>2.7374</v>
+        <v>2.5813</v>
       </c>
       <c r="J12" t="n">
-        <v>0.454</v>
+        <v>0.5372</v>
       </c>
       <c r="K12" t="n">
         <v>109</v>
@@ -989,7 +989,7 @@
         <v>75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1914</v>
+        <v>3.1185</v>
       </c>
       <c r="N12" t="n">
         <v>184</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6397</v>
+        <v>2.7391</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8714</v>
+        <v>0.9042</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5537</v>
+        <v>0.6227</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6397</v>
+        <v>2.7391</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3282</v>
+        <v>1.3013</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3115</v>
+        <v>1.4378</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3282</v>
+        <v>1.3013</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3282</v>
+        <v>1.3013</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3115</v>
+        <v>1.4378</v>
       </c>
       <c r="K13" t="n">
         <v>99</v>
@@ -1035,7 +1035,7 @@
         <v>95</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6397</v>
+        <v>2.7391</v>
       </c>
       <c r="N13" t="n">
         <v>194</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.51</v>
+        <v>2.4756</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8285</v>
+        <v>0.8172</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4951</v>
+        <v>0.5027</v>
       </c>
       <c r="E14" t="n">
-        <v>2.51</v>
+        <v>2.4756</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0705</v>
+        <v>2.9787</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5605</v>
+        <v>-0.5031</v>
       </c>
       <c r="H14" t="n">
-        <v>5.3322</v>
+        <v>4.9338</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7725</v>
+        <v>2.6642</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5605</v>
+        <v>-0.5031</v>
       </c>
       <c r="K14" t="n">
         <v>136</v>
@@ -1081,7 +1081,7 @@
         <v>112</v>
       </c>
       <c r="M14" t="n">
-        <v>2.212</v>
+        <v>2.1611</v>
       </c>
       <c r="N14" t="n">
         <v>248</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0898</v>
+        <v>2.1502</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6898</v>
+        <v>0.7098</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3054</v>
+        <v>0.3546</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0898</v>
+        <v>2.1502</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4049</v>
+        <v>1.3395</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6849</v>
+        <v>0.8107</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4049</v>
+        <v>1.3395</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4049</v>
+        <v>1.3395</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6849</v>
+        <v>0.8107</v>
       </c>
       <c r="K15" t="n">
         <v>99</v>
@@ -1127,7 +1127,7 @@
         <v>95</v>
       </c>
       <c r="M15" t="n">
-        <v>2.0898</v>
+        <v>2.1502</v>
       </c>
       <c r="N15" t="n">
         <v>194</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8177</v>
+        <v>1.7682</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6</v>
+        <v>0.5837</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1826</v>
+        <v>0.1807</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8177</v>
+        <v>1.7682</v>
       </c>
       <c r="F16" t="n">
-        <v>1.165</v>
+        <v>1.1018</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.6664</v>
       </c>
       <c r="H16" t="n">
-        <v>1.165</v>
+        <v>1.1018</v>
       </c>
       <c r="I16" t="n">
-        <v>1.165</v>
+        <v>1.1018</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.6664</v>
       </c>
       <c r="K16" t="n">
         <v>81</v>
@@ -1173,7 +1173,7 @@
         <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8177</v>
+        <v>1.7682</v>
       </c>
       <c r="N16" t="n">
         <v>132</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6595</v>
+        <v>1.5522</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5478</v>
+        <v>0.5124</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1112</v>
+        <v>0.0824</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6595</v>
+        <v>1.5522</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5717</v>
+        <v>1.4669</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0878</v>
+        <v>0.0853</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5717</v>
+        <v>1.4669</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5717</v>
+        <v>1.4669</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0878</v>
+        <v>0.0853</v>
       </c>
       <c r="K17" t="n">
         <v>97</v>
@@ -1219,7 +1219,7 @@
         <v>117</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6595</v>
+        <v>1.5522</v>
       </c>
       <c r="N17" t="n">
         <v>214</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>dem0n</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6248</v>
+        <v>1.5307</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5363</v>
+        <v>0.5053</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0955</v>
+        <v>0.0726</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6248</v>
+        <v>1.5307</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5218</v>
+        <v>1.5307</v>
       </c>
       <c r="G18" t="n">
-        <v>0.103</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5218</v>
+        <v>1.5307</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5218</v>
+        <v>1.5307</v>
       </c>
       <c r="J18" t="n">
-        <v>0.103</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="L18" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6248</v>
+        <v>1.5307</v>
       </c>
       <c r="N18" t="n">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dem0n</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5783</v>
+        <v>1.4887</v>
       </c>
       <c r="C19" t="n">
-        <v>0.521</v>
+        <v>0.4914</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0745</v>
+        <v>0.0535</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5783</v>
+        <v>1.4887</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5783</v>
+        <v>1.3941</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.0946</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5783</v>
+        <v>1.3941</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5783</v>
+        <v>1.3941</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.0946</v>
       </c>
       <c r="K19" t="n">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5783</v>
+        <v>1.4887</v>
       </c>
       <c r="N19" t="n">
-        <v>108</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4644</v>
+        <v>1.4829</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4834</v>
+        <v>0.4895</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0231</v>
+        <v>0.0508</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4644</v>
+        <v>1.4829</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1828</v>
+        <v>1.146</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2816</v>
+        <v>0.3369</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1828</v>
+        <v>1.146</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1828</v>
+        <v>1.146</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2816</v>
+        <v>0.3369</v>
       </c>
       <c r="K20" t="n">
         <v>81</v>
@@ -1357,7 +1357,7 @@
         <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4644</v>
+        <v>1.4829</v>
       </c>
       <c r="N20" t="n">
         <v>132</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.351</v>
+        <v>1.3117</v>
       </c>
       <c r="C21" t="n">
-        <v>0.446</v>
+        <v>0.433</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0281</v>
+        <v>-0.0271</v>
       </c>
       <c r="E21" t="n">
-        <v>1.351</v>
+        <v>1.3117</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8795</v>
+        <v>1.8533</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5285</v>
+        <v>-0.5416</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8795</v>
+        <v>1.8533</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8795</v>
+        <v>1.8533</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5285</v>
+        <v>-0.5416</v>
       </c>
       <c r="K21" t="n">
         <v>81</v>
@@ -1403,7 +1403,7 @@
         <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>1.351</v>
+        <v>1.3117</v>
       </c>
       <c r="N21" t="n">
         <v>132</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3019</v>
+        <v>1.3048</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4298</v>
+        <v>0.4307</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0503</v>
+        <v>-0.0302</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3019</v>
+        <v>1.3048</v>
       </c>
       <c r="F22" t="n">
-        <v>1.603</v>
+        <v>1.5451</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3011</v>
+        <v>-0.2403</v>
       </c>
       <c r="H22" t="n">
-        <v>1.603</v>
+        <v>1.5451</v>
       </c>
       <c r="I22" t="n">
-        <v>1.603</v>
+        <v>1.5451</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3011</v>
+        <v>-0.2403</v>
       </c>
       <c r="K22" t="n">
         <v>97</v>
@@ -1449,7 +1449,7 @@
         <v>117</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3019</v>
+        <v>1.3048</v>
       </c>
       <c r="N22" t="n">
         <v>214</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.2638</v>
+        <v>1.1798</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4172</v>
+        <v>0.3894</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0675</v>
+        <v>-0.0871</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2638</v>
+        <v>1.1798</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2638</v>
+        <v>1.1798</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2638</v>
+        <v>1.1798</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2638</v>
+        <v>1.1798</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2638</v>
+        <v>1.1798</v>
       </c>
       <c r="N23" t="n">
         <v>112</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1416</v>
+        <v>1.1005</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3768</v>
+        <v>0.3633</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1226</v>
+        <v>-0.1232</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1416</v>
+        <v>1.1005</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6894</v>
+        <v>0.6139</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4522</v>
+        <v>0.4866</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6894</v>
+        <v>0.6139</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7178</v>
+        <v>0.6297</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4522</v>
+        <v>0.4866</v>
       </c>
       <c r="K24" t="n">
         <v>109</v>
@@ -1541,7 +1541,7 @@
         <v>75</v>
       </c>
       <c r="M24" t="n">
-        <v>1.17</v>
+        <v>1.1163</v>
       </c>
       <c r="N24" t="n">
         <v>184</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.1077</v>
+        <v>1.0705</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3656</v>
+        <v>0.3534</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1379</v>
+        <v>-0.1369</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1077</v>
+        <v>1.0705</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1077</v>
+        <v>1.0705</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1077</v>
+        <v>1.0705</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1077</v>
+        <v>1.0705</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1077</v>
+        <v>1.0705</v>
       </c>
       <c r="N25" t="n">
         <v>108</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0.927</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3301</v>
+        <v>0.306</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1866</v>
+        <v>-0.2022</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0.927</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0.927</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0.927</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0.927</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0.927</v>
       </c>
       <c r="N26" t="n">
         <v>112</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6827</v>
+        <v>0.6675</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2254</v>
+        <v>0.2203</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3298</v>
+        <v>-0.3203</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6827</v>
+        <v>0.6675</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2284</v>
+        <v>1.1787</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.5457</v>
+        <v>-0.5112</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2284</v>
+        <v>1.1787</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2284</v>
+        <v>1.1787</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.5457</v>
+        <v>-0.5112</v>
       </c>
       <c r="K27" t="n">
         <v>97</v>
@@ -1679,7 +1679,7 @@
         <v>117</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6827</v>
+        <v>0.6675000000000001</v>
       </c>
       <c r="N27" t="n">
         <v>214</v>
@@ -1688,139 +1688,139 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6433</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2123</v>
+        <v>0.2158</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3476</v>
+        <v>-0.3266</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6433</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.005</v>
+        <v>-0.7294</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6483</v>
+        <v>1.3831</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.005</v>
+        <v>-0.7294</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.005</v>
+        <v>-0.7294</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6483</v>
+        <v>1.3831</v>
       </c>
       <c r="K28" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L28" t="n">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6433</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>214</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.546</v>
+        <v>0.6329</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1802</v>
+        <v>0.2089</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3915</v>
+        <v>-0.3361</v>
       </c>
       <c r="E29" t="n">
-        <v>0.546</v>
+        <v>0.6329</v>
       </c>
       <c r="F29" t="n">
-        <v>0.546</v>
+        <v>-0.0113</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.6442</v>
       </c>
       <c r="H29" t="n">
-        <v>0.546</v>
+        <v>-0.0113</v>
       </c>
       <c r="I29" t="n">
-        <v>0.546</v>
+        <v>-0.0113</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.6442</v>
       </c>
       <c r="K29" t="n">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M29" t="n">
-        <v>0.546</v>
+        <v>0.6329</v>
       </c>
       <c r="N29" t="n">
-        <v>112</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5054</v>
+        <v>0.4715</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1668</v>
+        <v>0.1556</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4099</v>
+        <v>-0.4096</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5054</v>
+        <v>0.4715</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7133</v>
+        <v>0.4715</v>
       </c>
       <c r="G30" t="n">
-        <v>1.2187</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7133</v>
+        <v>0.4715</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7133</v>
+        <v>0.4715</v>
       </c>
       <c r="J30" t="n">
-        <v>1.2187</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="L30" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.5053999999999998</v>
+        <v>0.4715</v>
       </c>
       <c r="N30" t="n">
-        <v>194</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3176</v>
+        <v>0.2733</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1048</v>
+        <v>0.0902</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4946</v>
+        <v>-0.4998</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3176</v>
+        <v>0.2733</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3176</v>
+        <v>0.2733</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3176</v>
+        <v>0.2733</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3176</v>
+        <v>0.2733</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.3176</v>
+        <v>0.2733</v>
       </c>
       <c r="N31" t="n">
         <v>108</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.1646</v>
+        <v>0.2126</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0543</v>
+        <v>0.0702</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5637</v>
+        <v>-0.5274</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1646</v>
+        <v>0.2126</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0562</v>
+        <v>-0.064</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2208</v>
+        <v>0.2766</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0562</v>
+        <v>-0.064</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0585</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2208</v>
+        <v>0.2766</v>
       </c>
       <c r="K32" t="n">
         <v>109</v>
@@ -1909,7 +1909,7 @@
         <v>75</v>
       </c>
       <c r="M32" t="n">
-        <v>0.1623</v>
+        <v>0.2109</v>
       </c>
       <c r="N32" t="n">
         <v>184</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0684</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0226</v>
+        <v>0.0303</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6071</v>
+        <v>-0.5824</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0684</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>1.4975</v>
+        <v>1.4544</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.4291</v>
+        <v>-1.3626</v>
       </c>
       <c r="H33" t="n">
-        <v>1.4975</v>
+        <v>1.4544</v>
       </c>
       <c r="I33" t="n">
-        <v>1.4975</v>
+        <v>1.4544</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.4291</v>
+        <v>-1.3626</v>
       </c>
       <c r="K33" t="n">
         <v>99</v>
@@ -1955,7 +1955,7 @@
         <v>95</v>
       </c>
       <c r="M33" t="n">
-        <v>0.06840000000000002</v>
+        <v>0.09179999999999988</v>
       </c>
       <c r="N33" t="n">
         <v>194</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3636</v>
+        <v>-0.2878</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.12</v>
+        <v>-0.095</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8022</v>
+        <v>-0.7552</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3636</v>
+        <v>-0.2878</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8407</v>
+        <v>-0.8174</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4771</v>
+        <v>0.5296</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8407</v>
+        <v>-0.8174</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8407</v>
+        <v>-0.8174</v>
       </c>
       <c r="J34" t="n">
-        <v>0.4771</v>
+        <v>0.5296</v>
       </c>
       <c r="K34" t="n">
         <v>81</v>
@@ -2001,7 +2001,7 @@
         <v>51</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3636</v>
+        <v>-0.2878000000000001</v>
       </c>
       <c r="N34" t="n">
         <v>132</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>hypex</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-1.0014</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3179</v>
+        <v>-0.3306</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0729</v>
+        <v>-1.0801</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-1.0014</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2579</v>
+        <v>-0.3019</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.2211</v>
+        <v>-0.6995</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2579</v>
+        <v>-0.3019</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2579</v>
+        <v>-0.3097</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.2211</v>
+        <v>-0.6995</v>
       </c>
       <c r="K35" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="L35" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.9632000000000001</v>
+        <v>-1.0092</v>
       </c>
       <c r="N35" t="n">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>hypex</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9798</v>
+        <v>-1.0277</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3234</v>
+        <v>-0.3392</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0803</v>
+        <v>-1.092</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9798</v>
+        <v>-1.0277</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3168</v>
+        <v>0.2029</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.663</v>
+        <v>-1.2306</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3168</v>
+        <v>0.2029</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3298</v>
+        <v>0.2029</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.663</v>
+        <v>-1.2306</v>
       </c>
       <c r="K36" t="n">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="L36" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9928</v>
+        <v>-1.0277</v>
       </c>
       <c r="N36" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9997</v>
+        <v>-1.047</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.33</v>
+        <v>-0.3456</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0893</v>
+        <v>-1.1008</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9997</v>
+        <v>-1.047</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9997</v>
+        <v>-1.047</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9997</v>
+        <v>-1.047</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9997</v>
+        <v>-1.047</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9997</v>
+        <v>-1.047</v>
       </c>
       <c r="N37" t="n">
         <v>108</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0672</v>
+        <v>-1.0886</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3523</v>
+        <v>-0.3593</v>
       </c>
       <c r="D38" t="n">
         <v>-1.1198</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0672</v>
+        <v>-1.0886</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0672</v>
+        <v>-1.0886</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0672</v>
+        <v>-1.0886</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0672</v>
+        <v>-1.0886</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0672</v>
+        <v>-1.0886</v>
       </c>
       <c r="N38" t="n">
         <v>108</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0851</v>
+        <v>-1.1414</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3582</v>
+        <v>-0.3768</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1279</v>
+        <v>-1.1438</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0851</v>
+        <v>-1.1414</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0851</v>
+        <v>-1.1414</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0851</v>
+        <v>-1.1414</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0851</v>
+        <v>-1.1414</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0851</v>
+        <v>-1.1414</v>
       </c>
       <c r="N39" t="n">
         <v>112</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1556</v>
+        <v>-1.2245</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3815</v>
+        <v>-0.4042</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1597</v>
+        <v>-1.1816</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1556</v>
+        <v>-1.2245</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.1556</v>
+        <v>-1.2245</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.1556</v>
+        <v>-1.2245</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1556</v>
+        <v>-1.2245</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.1556</v>
+        <v>-1.2245</v>
       </c>
       <c r="N40" t="n">
         <v>112</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.7013</v>
+        <v>-1.4442</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5616</v>
+        <v>-0.4767</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4061</v>
+        <v>-1.2816</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.7013</v>
+        <v>-1.4442</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.0776</v>
+        <v>-0.9208</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.6237</v>
+        <v>-0.5234</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.0776</v>
+        <v>-0.9208</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5603</v>
+        <v>-0.4972</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.6237</v>
+        <v>-0.5234</v>
       </c>
       <c r="K41" t="n">
         <v>84</v>
@@ -2323,7 +2323,7 @@
         <v>110</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.184</v>
+        <v>-1.0206</v>
       </c>
       <c r="N41" t="n">
         <v>194</v>
@@ -2429,10 +2429,10 @@
         <v>1.25</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5507</v>
+        <v>0.533</v>
       </c>
       <c r="J2" t="n">
-        <v>15.4196</v>
+        <v>14.924</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2622</v>
+        <v>0.2639</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3416</v>
+        <v>7.3892</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.059</v>
+        <v>-0.0693</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.652</v>
+        <v>-1.9404</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2223</v>
+        <v>-0.2372</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.2244</v>
+        <v>-6.6416</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.6</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4232</v>
+        <v>-0.4324</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.8496</v>
+        <v>-12.1072</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1245</v>
+        <v>1.1195</v>
       </c>
       <c r="J7" t="n">
-        <v>31.486</v>
+        <v>31.346</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.38</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9495</v>
+        <v>0.8958</v>
       </c>
       <c r="J8" t="n">
-        <v>26.586</v>
+        <v>25.0824</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.23</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6187</v>
+        <v>0.6006</v>
       </c>
       <c r="J9" t="n">
-        <v>17.3236</v>
+        <v>16.8168</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5466</v>
+        <v>0.536</v>
       </c>
       <c r="J10" t="n">
-        <v>15.3048</v>
+        <v>15.008</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.07</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1967</v>
+        <v>0.216</v>
       </c>
       <c r="J11" t="n">
-        <v>5.5076</v>
+        <v>6.048</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.67</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1078</v>
+        <v>1.1064</v>
       </c>
       <c r="J12" t="n">
-        <v>26.5872</v>
+        <v>26.5536</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.27</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.5306</v>
       </c>
       <c r="J13" t="n">
-        <v>12.9312</v>
+        <v>12.7344</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.11</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2498</v>
+        <v>0.2598</v>
       </c>
       <c r="J14" t="n">
-        <v>5.9952</v>
+        <v>6.2352</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.84</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2073</v>
+        <v>-0.2189</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.9752</v>
+        <v>-5.2536</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.51</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5174</v>
+        <v>-0.52</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.4176</v>
+        <v>-12.48</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.69</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4098</v>
+        <v>1.5116</v>
       </c>
       <c r="J17" t="n">
-        <v>33.8352</v>
+        <v>36.2784</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4778</v>
+        <v>0.4671</v>
       </c>
       <c r="J18" t="n">
-        <v>11.4672</v>
+        <v>11.2104</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.09</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2933</v>
+        <v>0.2971</v>
       </c>
       <c r="J19" t="n">
-        <v>7.0392</v>
+        <v>7.1304</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.98</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1224</v>
+        <v>-0.1193</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.9376</v>
+        <v>-2.8632</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.65</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0251</v>
+        <v>-0.9354</v>
       </c>
       <c r="J21" t="n">
-        <v>-24.6024</v>
+        <v>-22.4496</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.35</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8119</v>
+        <v>0.7558</v>
       </c>
       <c r="J22" t="n">
-        <v>12.9904</v>
+        <v>12.0928</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.79</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2254</v>
+        <v>-0.244</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.6064</v>
+        <v>-3.904</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.75</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2637</v>
+        <v>-0.2818</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.2192</v>
+        <v>-4.5088</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.66</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3493</v>
+        <v>-0.3648</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.5888</v>
+        <v>-5.8368</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.48</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.5234</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.265599999999999</v>
+        <v>-8.3744</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>2.18</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8681</v>
+        <v>1.8453</v>
       </c>
       <c r="J27" t="n">
-        <v>29.8896</v>
+        <v>29.5248</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.93</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5942</v>
+        <v>1.7347</v>
       </c>
       <c r="J28" t="n">
-        <v>25.5072</v>
+        <v>27.7552</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.25</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6287</v>
+        <v>0.6169</v>
       </c>
       <c r="J29" t="n">
-        <v>10.0592</v>
+        <v>9.8704</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.13</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3274</v>
+        <v>0.3459</v>
       </c>
       <c r="J30" t="n">
-        <v>5.2384</v>
+        <v>5.5344</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.8</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7276</v>
+        <v>-0.6625</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.6416</v>
+        <v>-10.6</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>2.12</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4866</v>
+        <v>1.6279</v>
       </c>
       <c r="J32" t="n">
-        <v>20.8124</v>
+        <v>22.7906</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.96</v>
       </c>
       <c r="I33" t="n">
-        <v>1.3152</v>
+        <v>1.4483</v>
       </c>
       <c r="J33" t="n">
-        <v>18.4128</v>
+        <v>20.2762</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.7</v>
       </c>
       <c r="I34" t="n">
-        <v>1.032</v>
+        <v>1.1476</v>
       </c>
       <c r="J34" t="n">
-        <v>14.448</v>
+        <v>16.0664</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.36</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.713</v>
       </c>
       <c r="J35" t="n">
-        <v>8.8424</v>
+        <v>9.981999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.17</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3689</v>
+        <v>0.4131</v>
       </c>
       <c r="J36" t="n">
-        <v>5.1646</v>
+        <v>5.7834</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.72</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2171</v>
+        <v>-0.2511</v>
       </c>
       <c r="J37" t="n">
-        <v>-3.0394</v>
+        <v>-3.5154</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.64</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3065</v>
+        <v>-0.3351</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.291</v>
+        <v>-4.6914</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.44</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4998</v>
+        <v>-0.5158</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.9972</v>
+        <v>-7.2212</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.41</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5286</v>
+        <v>-0.5423</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.4004</v>
+        <v>-7.5922</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.27</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-0.6694</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.3492</v>
+        <v>-9.371600000000001</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.23</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5231</v>
+        <v>0.5767</v>
       </c>
       <c r="J42" t="n">
-        <v>15.693</v>
+        <v>17.301</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.21</v>
       </c>
       <c r="I43" t="n">
-        <v>0.494</v>
+        <v>0.5442</v>
       </c>
       <c r="J43" t="n">
-        <v>14.82</v>
+        <v>16.326</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.09</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2944</v>
+        <v>0.2979</v>
       </c>
       <c r="J44" t="n">
-        <v>8.832000000000001</v>
+        <v>8.936999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.02</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0706</v>
+        <v>0.0838</v>
       </c>
       <c r="J45" t="n">
-        <v>2.118</v>
+        <v>2.514</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.99</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0798</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>-2.394</v>
+        <v>-2.304</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.26</v>
       </c>
       <c r="I47" t="n">
-        <v>0.453</v>
+        <v>0.5027</v>
       </c>
       <c r="J47" t="n">
-        <v>13.59</v>
+        <v>15.081</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.12</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2787</v>
+        <v>0.2852</v>
       </c>
       <c r="J48" t="n">
-        <v>8.361000000000001</v>
+        <v>8.555999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.09</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2188</v>
+        <v>0.2276</v>
       </c>
       <c r="J49" t="n">
-        <v>6.564</v>
+        <v>6.828</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.87</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1705</v>
+        <v>-0.183</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.115</v>
+        <v>-5.49</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.82</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2225</v>
+        <v>-0.2353</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.675</v>
+        <v>-7.059</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.79</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2017</v>
+        <v>1.3156</v>
       </c>
       <c r="J52" t="n">
-        <v>21.6306</v>
+        <v>23.6808</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.4</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7222</v>
+        <v>0.8032</v>
       </c>
       <c r="J53" t="n">
-        <v>12.9996</v>
+        <v>14.4576</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.15</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3834</v>
+        <v>0.4192</v>
       </c>
       <c r="J54" t="n">
-        <v>6.9012</v>
+        <v>7.5456</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3679</v>
+        <v>0.3962</v>
       </c>
       <c r="J55" t="n">
-        <v>6.6222</v>
+        <v>7.1316</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2383</v>
+        <v>-0.2203</v>
       </c>
       <c r="J56" t="n">
-        <v>-4.2894</v>
+        <v>-3.9654</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.99</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0459</v>
+        <v>0.0176</v>
       </c>
       <c r="J57" t="n">
-        <v>0.8262</v>
+        <v>0.3168</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.83</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1768</v>
+        <v>-0.1977</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.1824</v>
+        <v>-3.5586</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.8</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2079</v>
+        <v>-0.2285</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.7422</v>
+        <v>-4.113</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3957</v>
+        <v>-0.4108</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.1226</v>
+        <v>-7.3944</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.48</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.5163</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.136799999999999</v>
+        <v>-9.2934</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.45</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.8864</v>
       </c>
       <c r="J62" t="n">
-        <v>19.2456</v>
+        <v>21.2736</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.4</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7368</v>
+        <v>0.8159</v>
       </c>
       <c r="J63" t="n">
-        <v>17.6832</v>
+        <v>19.5816</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.24</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5218</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="J64" t="n">
-        <v>12.5232</v>
+        <v>13.8984</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.02</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0459</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="J65" t="n">
-        <v>1.1016</v>
+        <v>1.5984</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.92</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3459</v>
+        <v>-0.3266</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.301600000000001</v>
+        <v>-7.8384</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.36</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5704</v>
+        <v>0.6331</v>
       </c>
       <c r="J67" t="n">
-        <v>13.6896</v>
+        <v>15.1944</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.09</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2347</v>
+        <v>0.2391</v>
       </c>
       <c r="J68" t="n">
-        <v>5.6328</v>
+        <v>5.7384</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0.005</v>
+        <v>0.0035</v>
       </c>
       <c r="J69" t="n">
-        <v>0.12</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.8</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.235</v>
+        <v>-0.2493</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.64</v>
+        <v>-5.9832</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.58</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4439</v>
+        <v>-0.4518</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.6536</v>
+        <v>-10.8432</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.85</v>
       </c>
       <c r="I72" t="n">
-        <v>1.299</v>
+        <v>1.4136</v>
       </c>
       <c r="J72" t="n">
-        <v>27.279</v>
+        <v>29.6856</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.49</v>
       </c>
       <c r="I73" t="n">
-        <v>0.853</v>
+        <v>0.9415</v>
       </c>
       <c r="J73" t="n">
-        <v>17.913</v>
+        <v>19.7715</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.16</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4089</v>
+        <v>0.4502</v>
       </c>
       <c r="J74" t="n">
-        <v>8.5869</v>
+        <v>9.4542</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.82</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.625</v>
+        <v>-0.5803</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.125</v>
+        <v>-12.1863</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.72</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.8776</v>
+        <v>-0.8037</v>
       </c>
       <c r="J76" t="n">
-        <v>-18.4296</v>
+        <v>-16.8777</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.34</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5464</v>
+        <v>0.6068</v>
       </c>
       <c r="J77" t="n">
-        <v>11.4744</v>
+        <v>12.7428</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.14</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3286</v>
+        <v>0.3323</v>
       </c>
       <c r="J78" t="n">
-        <v>6.9006</v>
+        <v>6.9783</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.13</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3114</v>
+        <v>0.3137</v>
       </c>
       <c r="J79" t="n">
-        <v>6.5394</v>
+        <v>6.5877</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.74</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2957</v>
+        <v>-0.3086</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.2097</v>
+        <v>-6.4806</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.55</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4726</v>
+        <v>-0.4789</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.9246</v>
+        <v>-10.0569</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.5</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8854</v>
+        <v>0.9725</v>
       </c>
       <c r="J82" t="n">
-        <v>26.562</v>
+        <v>29.175</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.47</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8461</v>
+        <v>0.9304</v>
       </c>
       <c r="J83" t="n">
-        <v>25.383</v>
+        <v>27.912</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.11</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3388</v>
+        <v>0.3458</v>
       </c>
       <c r="J84" t="n">
-        <v>10.164</v>
+        <v>10.374</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.85</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5264</v>
+        <v>-0.4954</v>
       </c>
       <c r="J85" t="n">
-        <v>-15.792</v>
+        <v>-14.862</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.74</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.8109</v>
+        <v>-0.7481</v>
       </c>
       <c r="J86" t="n">
-        <v>-24.327</v>
+        <v>-22.443</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.39</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5773</v>
+        <v>0.6455</v>
       </c>
       <c r="J87" t="n">
-        <v>17.319</v>
+        <v>19.365</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.16</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3413</v>
+        <v>0.3527</v>
       </c>
       <c r="J88" t="n">
-        <v>10.239</v>
+        <v>10.581</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.97</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0559</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.677</v>
+        <v>-1.881</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.96</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0693</v>
+        <v>-0.0772</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.079</v>
+        <v>-2.316</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.82</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2256</v>
+        <v>-0.2377</v>
       </c>
       <c r="J91" t="n">
-        <v>-6.768</v>
+        <v>-7.131</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.76</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9127999999999999</v>
+        <v>1.019</v>
       </c>
       <c r="J92" t="n">
-        <v>21.9072</v>
+        <v>24.456</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.99</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0287</v>
+        <v>-0.0315</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.6888</v>
+        <v>-0.756</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.96</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0722</v>
+        <v>-0.0794</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.7328</v>
+        <v>-1.9056</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.88</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1659</v>
+        <v>-0.1769</v>
       </c>
       <c r="J95" t="n">
-        <v>-3.9816</v>
+        <v>-4.2456</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.85</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1978</v>
+        <v>-0.2091</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.7472</v>
+        <v>-5.0184</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.28</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6107</v>
+        <v>0.67</v>
       </c>
       <c r="J97" t="n">
-        <v>14.6568</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.11</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3514</v>
+        <v>0.3586</v>
       </c>
       <c r="J98" t="n">
-        <v>8.4336</v>
+        <v>8.606400000000001</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.03</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1224</v>
+        <v>0.1303</v>
       </c>
       <c r="J99" t="n">
-        <v>2.9376</v>
+        <v>3.1272</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.92</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.302</v>
+        <v>-0.2959</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.248</v>
+        <v>-7.1016</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.87</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4459</v>
+        <v>-0.4279</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.7016</v>
+        <v>-10.2696</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.51</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5228</v>
+        <v>0.5954</v>
       </c>
       <c r="J102" t="n">
-        <v>11.5016</v>
+        <v>13.0988</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.3</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3805</v>
+        <v>0.4223</v>
       </c>
       <c r="J103" t="n">
-        <v>8.371</v>
+        <v>9.2906</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.04</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0704</v>
+        <v>0.0835</v>
       </c>
       <c r="J104" t="n">
-        <v>1.5488</v>
+        <v>1.837</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.9</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1468</v>
+        <v>-0.1567</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.2296</v>
+        <v>-3.4474</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2214</v>
+        <v>-0.2322</v>
       </c>
       <c r="J106" t="n">
-        <v>-4.8708</v>
+        <v>-5.1084</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.15</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2856</v>
+        <v>0.2873</v>
       </c>
       <c r="J107" t="n">
-        <v>6.2832</v>
+        <v>6.3206</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0424</v>
+        <v>0.0439</v>
       </c>
       <c r="J108" t="n">
-        <v>0.9328</v>
+        <v>0.9658</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.97</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0426</v>
+        <v>-0.0526</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.9372</v>
+        <v>-1.1572</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.91</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1147</v>
+        <v>-0.129</v>
       </c>
       <c r="J110" t="n">
-        <v>-2.5234</v>
+        <v>-2.838</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.54</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4749</v>
+        <v>-0.4822</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.4478</v>
+        <v>-10.6084</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.42</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.7035</v>
       </c>
       <c r="J112" t="n">
-        <v>18.3744</v>
+        <v>20.4015</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.09</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2376</v>
+        <v>0.2412</v>
       </c>
       <c r="J113" t="n">
-        <v>6.8904</v>
+        <v>6.9948</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.79</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2438</v>
+        <v>-0.2582</v>
       </c>
       <c r="J114" t="n">
-        <v>-7.0702</v>
+        <v>-7.4878</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.76</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2733</v>
+        <v>-0.2873</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.9257</v>
+        <v>-8.3317</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.72</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.312</v>
+        <v>-0.3251</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.048</v>
+        <v>-9.427899999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.63</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0481</v>
+        <v>1.1464</v>
       </c>
       <c r="J117" t="n">
-        <v>30.3949</v>
+        <v>33.2456</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3137</v>
+        <v>0.3184</v>
       </c>
       <c r="J118" t="n">
-        <v>9.097300000000001</v>
+        <v>9.233599999999999</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.08</v>
       </c>
       <c r="I119" t="n">
-        <v>0.2572</v>
+        <v>0.2652</v>
       </c>
       <c r="J119" t="n">
-        <v>7.4588</v>
+        <v>7.6908</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.99</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0902</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.6158</v>
+        <v>-2.4389</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2693</v>
+        <v>-0.2584</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.8097</v>
+        <v>-7.4936</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>2.13</v>
       </c>
       <c r="I122" t="n">
-        <v>1.8338</v>
+        <v>1.8854</v>
       </c>
       <c r="J122" t="n">
-        <v>42.1774</v>
+        <v>43.3642</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.49</v>
       </c>
       <c r="I123" t="n">
-        <v>1.1149</v>
+        <v>1.0783</v>
       </c>
       <c r="J123" t="n">
-        <v>25.6427</v>
+        <v>24.8009</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.97</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1972</v>
+        <v>-0.1822</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.5356</v>
+        <v>-4.1906</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5306</v>
+        <v>-0.493</v>
       </c>
       <c r="J125" t="n">
-        <v>-12.2038</v>
+        <v>-11.339</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5306</v>
+        <v>-0.493</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.2038</v>
+        <v>-11.339</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.23</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5013</v>
       </c>
       <c r="J127" t="n">
-        <v>11.8818</v>
+        <v>11.5299</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.11</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2848</v>
+        <v>0.2851</v>
       </c>
       <c r="J128" t="n">
-        <v>6.5504</v>
+        <v>6.5573</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0828</v>
+        <v>-0.095</v>
       </c>
       <c r="J129" t="n">
-        <v>-1.9044</v>
+        <v>-2.185</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.79</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2416</v>
+        <v>-0.2565</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.5568</v>
+        <v>-5.8995</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.62</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.404</v>
+        <v>-0.4142</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.292</v>
+        <v>-9.5266</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.78</v>
       </c>
       <c r="I132" t="n">
-        <v>1.4206</v>
+        <v>1.4124</v>
       </c>
       <c r="J132" t="n">
-        <v>24.1502</v>
+        <v>24.0108</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.51</v>
       </c>
       <c r="I133" t="n">
-        <v>1.1074</v>
+        <v>1.0769</v>
       </c>
       <c r="J133" t="n">
-        <v>18.8258</v>
+        <v>18.3073</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.43</v>
       </c>
       <c r="I134" t="n">
-        <v>1.0073</v>
+        <v>0.9614</v>
       </c>
       <c r="J134" t="n">
-        <v>17.1241</v>
+        <v>16.3438</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.36</v>
       </c>
       <c r="I135" t="n">
-        <v>0.8742</v>
+        <v>0.8341</v>
       </c>
       <c r="J135" t="n">
-        <v>14.8614</v>
+        <v>14.1797</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.3</v>
       </c>
       <c r="I136" t="n">
-        <v>0.7409</v>
+        <v>0.7169</v>
       </c>
       <c r="J136" t="n">
-        <v>12.5953</v>
+        <v>12.1873</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.09</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3432</v>
+        <v>0.319</v>
       </c>
       <c r="J137" t="n">
-        <v>5.8344</v>
+        <v>5.423</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.87</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1304</v>
+        <v>-0.1521</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.2168</v>
+        <v>-2.5857</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.77</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2359</v>
+        <v>-0.2564</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.0103</v>
+        <v>-4.3588</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.49</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4965</v>
+        <v>-0.5062</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.4405</v>
+        <v>-8.605399999999999</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.42</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5615</v>
+        <v>-0.5669</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.545500000000001</v>
+        <v>-9.6373</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.57</v>
       </c>
       <c r="I142" t="n">
-        <v>1.2096</v>
+        <v>1.181</v>
       </c>
       <c r="J142" t="n">
-        <v>20.5632</v>
+        <v>20.077</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.48</v>
       </c>
       <c r="I143" t="n">
-        <v>1.0976</v>
+        <v>1.0602</v>
       </c>
       <c r="J143" t="n">
-        <v>18.6592</v>
+        <v>18.0234</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.14</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3918</v>
+        <v>0.3966</v>
       </c>
       <c r="J144" t="n">
-        <v>6.6606</v>
+        <v>6.7422</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.14</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3918</v>
+        <v>0.3966</v>
       </c>
       <c r="J145" t="n">
-        <v>6.6606</v>
+        <v>6.7422</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.1</v>
       </c>
       <c r="I146" t="n">
-        <v>0.2823</v>
+        <v>0.2962</v>
       </c>
       <c r="J146" t="n">
-        <v>4.7991</v>
+        <v>5.0354</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.29</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6657</v>
+        <v>0.6303</v>
       </c>
       <c r="J147" t="n">
-        <v>11.3169</v>
+        <v>10.7151</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.06</v>
       </c>
       <c r="I148" t="n">
-        <v>0.204</v>
+        <v>0.2009</v>
       </c>
       <c r="J148" t="n">
-        <v>3.468</v>
+        <v>3.4153</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.74</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2805</v>
+        <v>-0.2968</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.7685</v>
+        <v>-5.0456</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.65</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3662</v>
+        <v>-0.3797</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.2254</v>
+        <v>-6.4549</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4499</v>
+        <v>-0.4596</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.6483</v>
+        <v>-7.8132</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.32</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5561</v>
+        <v>0.536</v>
       </c>
       <c r="J152" t="n">
-        <v>11.122</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2109</v>
+        <v>-0.2284</v>
       </c>
       <c r="J153" t="n">
-        <v>-4.218</v>
+        <v>-4.568</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.77</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2501</v>
+        <v>-0.2672</v>
       </c>
       <c r="J154" t="n">
-        <v>-5.002</v>
+        <v>-5.344</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.75</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2695</v>
+        <v>-0.2863</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.39</v>
+        <v>-5.726</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.6</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4116</v>
+        <v>-0.4234</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.231999999999999</v>
+        <v>-8.468</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.96</v>
       </c>
       <c r="I157" t="n">
-        <v>1.0571</v>
+        <v>1.0442</v>
       </c>
       <c r="J157" t="n">
-        <v>21.142</v>
+        <v>20.884</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.33</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4293</v>
+        <v>0.4429</v>
       </c>
       <c r="J158" t="n">
-        <v>8.586</v>
+        <v>8.858000000000001</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.06</v>
       </c>
       <c r="I159" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1068</v>
       </c>
       <c r="J159" t="n">
-        <v>1.778</v>
+        <v>2.136</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.96</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0864</v>
+        <v>-0.0905</v>
       </c>
       <c r="J160" t="n">
-        <v>-1.728</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.84</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2221</v>
+        <v>-0.2305</v>
       </c>
       <c r="J161" t="n">
-        <v>-4.442</v>
+        <v>-4.61</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.94</v>
       </c>
       <c r="I162" t="n">
-        <v>1.6015</v>
+        <v>1.603</v>
       </c>
       <c r="J162" t="n">
-        <v>25.624</v>
+        <v>25.648</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.59</v>
       </c>
       <c r="I163" t="n">
-        <v>1.2011</v>
+        <v>1.1783</v>
       </c>
       <c r="J163" t="n">
-        <v>19.2176</v>
+        <v>18.8528</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.53</v>
       </c>
       <c r="I164" t="n">
-        <v>1.1308</v>
+        <v>1.1024</v>
       </c>
       <c r="J164" t="n">
-        <v>18.0928</v>
+        <v>17.6384</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.36</v>
       </c>
       <c r="I165" t="n">
-        <v>0.8742</v>
+        <v>0.8341</v>
       </c>
       <c r="J165" t="n">
-        <v>13.9872</v>
+        <v>13.3456</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.96</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.278</v>
+        <v>-0.2482</v>
       </c>
       <c r="J166" t="n">
-        <v>-4.448</v>
+        <v>-3.9712</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.77</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.2164</v>
+        <v>-0.2413</v>
       </c>
       <c r="J167" t="n">
-        <v>-3.4624</v>
+        <v>-3.8608</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.72</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.268</v>
+        <v>-0.2911</v>
       </c>
       <c r="J168" t="n">
-        <v>-4.288</v>
+        <v>-4.6576</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.61</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3699</v>
+        <v>-0.3892</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.9184</v>
+        <v>-6.2272</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.55</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4252</v>
+        <v>-0.4417</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.8032</v>
+        <v>-7.0672</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.54</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4345</v>
+        <v>-0.4505</v>
       </c>
       <c r="J171" t="n">
-        <v>-6.952</v>
+        <v>-7.208</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.51</v>
       </c>
       <c r="I172" t="n">
-        <v>1.1658</v>
+        <v>1.1282</v>
       </c>
       <c r="J172" t="n">
-        <v>33.8082</v>
+        <v>32.7178</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.32</v>
       </c>
       <c r="I173" t="n">
-        <v>0.8534</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="J173" t="n">
-        <v>24.7486</v>
+        <v>23.2841</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.6166</v>
+        <v>0.594</v>
       </c>
       <c r="J174" t="n">
-        <v>17.8814</v>
+        <v>17.226</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.92</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3331</v>
+        <v>-0.3176</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.6599</v>
+        <v>-9.2104</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6384</v>
+        <v>-0.5947</v>
       </c>
       <c r="J176" t="n">
-        <v>-18.5136</v>
+        <v>-17.2463</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.51</v>
       </c>
       <c r="I177" t="n">
-        <v>0.99</v>
+        <v>0.9349</v>
       </c>
       <c r="J177" t="n">
-        <v>28.71</v>
+        <v>27.1121</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.98</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0316</v>
+        <v>-0.0394</v>
       </c>
       <c r="J178" t="n">
-        <v>-0.9164</v>
+        <v>-1.1426</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.95</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.0706</v>
+        <v>-2.3954</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.71</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3202</v>
+        <v>-0.3333</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.2858</v>
+        <v>-9.665699999999999</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.57</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4507</v>
+        <v>-0.4586</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.0703</v>
+        <v>-13.2994</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.21</v>
       </c>
       <c r="I182" t="n">
-        <v>0.3663</v>
+        <v>0.3655</v>
       </c>
       <c r="J182" t="n">
-        <v>8.7912</v>
+        <v>8.772</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.16</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2936</v>
+        <v>0.2965</v>
       </c>
       <c r="J183" t="n">
-        <v>7.0464</v>
+        <v>7.116</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.95</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0711</v>
+        <v>-0.0824</v>
       </c>
       <c r="J184" t="n">
-        <v>-1.7064</v>
+        <v>-1.9776</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.87</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.16</v>
+        <v>-0.1749</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.84</v>
+        <v>-4.1976</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.51</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5046</v>
+        <v>-0.5099</v>
       </c>
       <c r="J186" t="n">
-        <v>-12.1104</v>
+        <v>-12.2376</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.33</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4556</v>
+        <v>0.4629</v>
       </c>
       <c r="J187" t="n">
-        <v>10.9344</v>
+        <v>11.1096</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.31</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4317</v>
+        <v>0.4402</v>
       </c>
       <c r="J188" t="n">
-        <v>10.3608</v>
+        <v>10.5648</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.18</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2706</v>
+        <v>0.285</v>
       </c>
       <c r="J189" t="n">
-        <v>6.4944</v>
+        <v>6.84</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.85</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1971</v>
+        <v>-0.2086</v>
       </c>
       <c r="J190" t="n">
-        <v>-4.7304</v>
+        <v>-5.0064</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.74</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3069</v>
+        <v>-0.3174</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.3656</v>
+        <v>-7.6176</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.96</v>
       </c>
       <c r="I192" t="n">
-        <v>1.6096</v>
+        <v>1.6138</v>
       </c>
       <c r="J192" t="n">
-        <v>25.7536</v>
+        <v>25.8208</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.65</v>
       </c>
       <c r="I193" t="n">
-        <v>1.2618</v>
+        <v>1.2453</v>
       </c>
       <c r="J193" t="n">
-        <v>20.1888</v>
+        <v>19.9248</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.58</v>
       </c>
       <c r="I194" t="n">
-        <v>1.182</v>
+        <v>1.1594</v>
       </c>
       <c r="J194" t="n">
-        <v>18.912</v>
+        <v>18.5504</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.33</v>
       </c>
       <c r="I195" t="n">
-        <v>0.7951</v>
+        <v>0.767</v>
       </c>
       <c r="J195" t="n">
-        <v>12.7216</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.2</v>
       </c>
       <c r="I196" t="n">
-        <v>0.4905</v>
+        <v>0.4969</v>
       </c>
       <c r="J196" t="n">
-        <v>7.848</v>
+        <v>7.9504</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.19</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5855</v>
+        <v>0.5389</v>
       </c>
       <c r="J197" t="n">
-        <v>9.368</v>
+        <v>8.622400000000001</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.03</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2139</v>
+        <v>0.1895</v>
       </c>
       <c r="J198" t="n">
-        <v>3.4224</v>
+        <v>3.032</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.52</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4637</v>
+        <v>-0.4762</v>
       </c>
       <c r="J199" t="n">
-        <v>-7.4192</v>
+        <v>-7.6192</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.47</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5105</v>
+        <v>-0.52</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.167999999999999</v>
+        <v>-8.32</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.28</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6876</v>
+        <v>-0.6839</v>
       </c>
       <c r="J201" t="n">
-        <v>-11.0016</v>
+        <v>-10.9424</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.05</v>
       </c>
       <c r="I202" t="n">
-        <v>0.1971</v>
+        <v>0.19</v>
       </c>
       <c r="J202" t="n">
-        <v>3.5478</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.01</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0883</v>
+        <v>0.0801</v>
       </c>
       <c r="J203" t="n">
-        <v>1.5894</v>
+        <v>1.4418</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.71</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3038</v>
+        <v>-0.3205</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.4684</v>
+        <v>-5.769</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3229</v>
+        <v>-0.339</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.8122</v>
+        <v>-6.102</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.64</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3701</v>
+        <v>-0.3844</v>
       </c>
       <c r="J206" t="n">
-        <v>-6.6618</v>
+        <v>-6.9192</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.79</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4552</v>
+        <v>1.4449</v>
       </c>
       <c r="J207" t="n">
-        <v>26.1936</v>
+        <v>26.0082</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.4</v>
       </c>
       <c r="I208" t="n">
-        <v>0.97</v>
+        <v>0.9195</v>
       </c>
       <c r="J208" t="n">
-        <v>17.46</v>
+        <v>16.551</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.29</v>
       </c>
       <c r="I209" t="n">
-        <v>0.74</v>
+        <v>0.7119</v>
       </c>
       <c r="J209" t="n">
-        <v>13.32</v>
+        <v>12.8142</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.26</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6711</v>
+        <v>0.6509</v>
       </c>
       <c r="J210" t="n">
-        <v>12.0798</v>
+        <v>11.7162</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.09</v>
       </c>
       <c r="I211" t="n">
-        <v>0.2354</v>
+        <v>0.2569</v>
       </c>
       <c r="J211" t="n">
-        <v>4.2372</v>
+        <v>4.6242</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.34</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6642</v>
       </c>
       <c r="J212" t="n">
-        <v>15.916</v>
+        <v>15.2766</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.17</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3873</v>
+        <v>0.385</v>
       </c>
       <c r="J213" t="n">
-        <v>8.9079</v>
+        <v>8.855</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.96</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.062</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="J214" t="n">
-        <v>-1.426</v>
+        <v>-1.6445</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.82</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2172</v>
+        <v>-0.2311</v>
       </c>
       <c r="J215" t="n">
-        <v>-4.9956</v>
+        <v>-5.3153</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.64</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3909</v>
+        <v>-0.4007</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.9907</v>
+        <v>-9.216100000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.29</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8056</v>
+        <v>0.7571</v>
       </c>
       <c r="J217" t="n">
-        <v>18.5288</v>
+        <v>17.4133</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.2</v>
       </c>
       <c r="I218" t="n">
-        <v>0.585</v>
+        <v>0.5622</v>
       </c>
       <c r="J218" t="n">
-        <v>13.455</v>
+        <v>12.9306</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.12</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3777</v>
+        <v>0.3747</v>
       </c>
       <c r="J219" t="n">
-        <v>8.687099999999999</v>
+        <v>8.6181</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.99</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0761</v>
+        <v>-0.0743</v>
       </c>
       <c r="J220" t="n">
-        <v>-1.7503</v>
+        <v>-1.7089</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.87</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4607</v>
+        <v>-0.4382</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.5961</v>
+        <v>-10.0786</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.89</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9819</v>
+        <v>0.9654</v>
       </c>
       <c r="J222" t="n">
-        <v>17.6742</v>
+        <v>17.3772</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.77</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8711</v>
+        <v>0.8592</v>
       </c>
       <c r="J223" t="n">
-        <v>15.6798</v>
+        <v>15.4656</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.23</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3017</v>
+        <v>0.3224</v>
       </c>
       <c r="J224" t="n">
-        <v>5.4306</v>
+        <v>5.8032</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.01</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0128</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="J225" t="n">
-        <v>-0.2304</v>
+        <v>-0.0108</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1237</v>
+        <v>-0.1268</v>
       </c>
       <c r="J226" t="n">
-        <v>-2.2266</v>
+        <v>-2.2824</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.22</v>
       </c>
       <c r="I227" t="n">
-        <v>0.419</v>
+        <v>0.408</v>
       </c>
       <c r="J227" t="n">
-        <v>7.542</v>
+        <v>7.344</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.96</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0439</v>
+        <v>-0.0577</v>
       </c>
       <c r="J228" t="n">
-        <v>-0.7902</v>
+        <v>-1.0386</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0699</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="J229" t="n">
-        <v>-1.2582</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.61</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4004</v>
+        <v>-0.413</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.2072</v>
+        <v>-7.434</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.45</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5476</v>
+        <v>-0.552</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.8568</v>
+        <v>-9.936</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.03</v>
       </c>
       <c r="I232" t="n">
-        <v>0.1967</v>
+        <v>0.1768</v>
       </c>
       <c r="J232" t="n">
-        <v>3.5406</v>
+        <v>3.1824</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.79</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.2152</v>
+        <v>-0.2363</v>
       </c>
       <c r="J233" t="n">
-        <v>-3.8736</v>
+        <v>-4.2534</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.71</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2908</v>
+        <v>-0.3105</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.2344</v>
+        <v>-5.589</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.55</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4399</v>
+        <v>-0.4531</v>
       </c>
       <c r="J235" t="n">
-        <v>-7.9182</v>
+        <v>-8.155799999999999</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.54</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4492</v>
+        <v>-0.4619</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.085599999999999</v>
+        <v>-8.3142</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.8</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4698</v>
+        <v>1.4598</v>
       </c>
       <c r="J237" t="n">
-        <v>26.4564</v>
+        <v>26.2764</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.51</v>
       </c>
       <c r="I238" t="n">
-        <v>1.123</v>
+        <v>1.0905</v>
       </c>
       <c r="J238" t="n">
-        <v>20.214</v>
+        <v>19.629</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.23</v>
       </c>
       <c r="I239" t="n">
-        <v>0.6028</v>
+        <v>0.5896</v>
       </c>
       <c r="J239" t="n">
-        <v>10.8504</v>
+        <v>10.6128</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.17</v>
       </c>
       <c r="I240" t="n">
-        <v>0.4546</v>
+        <v>0.4567</v>
       </c>
       <c r="J240" t="n">
-        <v>8.1828</v>
+        <v>8.220599999999999</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.06</v>
       </c>
       <c r="I241" t="n">
-        <v>0.1478</v>
+        <v>0.1743</v>
       </c>
       <c r="J241" t="n">
-        <v>2.6604</v>
+        <v>3.1374</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.36</v>
       </c>
       <c r="I242" t="n">
-        <v>0.7409</v>
+        <v>0.7059</v>
       </c>
       <c r="J242" t="n">
-        <v>17.0407</v>
+        <v>16.2357</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.33</v>
       </c>
       <c r="I243" t="n">
-        <v>0.6888</v>
+        <v>0.659</v>
       </c>
       <c r="J243" t="n">
-        <v>15.8424</v>
+        <v>15.157</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.82</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2134</v>
+        <v>-0.2281</v>
       </c>
       <c r="J244" t="n">
-        <v>-4.9082</v>
+        <v>-5.2463</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.66</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3686</v>
+        <v>-0.3799</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.4778</v>
+        <v>-8.7377</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.6</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4243</v>
+        <v>-0.4333</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.758900000000001</v>
+        <v>-9.9659</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.78</v>
       </c>
       <c r="I247" t="n">
-        <v>1.4977</v>
+        <v>1.4807</v>
       </c>
       <c r="J247" t="n">
-        <v>34.4471</v>
+        <v>34.0561</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.21</v>
       </c>
       <c r="I248" t="n">
-        <v>0.587</v>
+        <v>0.5687</v>
       </c>
       <c r="J248" t="n">
-        <v>13.501</v>
+        <v>13.0801</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.03</v>
       </c>
       <c r="I249" t="n">
-        <v>0.0895</v>
+        <v>0.1076</v>
       </c>
       <c r="J249" t="n">
-        <v>2.0585</v>
+        <v>2.4748</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.97</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1769</v>
+        <v>-0.168</v>
       </c>
       <c r="J250" t="n">
-        <v>-4.0687</v>
+        <v>-3.864</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.91</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3692</v>
+        <v>-0.3496</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.4916</v>
+        <v>-8.040800000000001</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.56</v>
       </c>
       <c r="I252" t="n">
-        <v>1.2091</v>
+        <v>1.1783</v>
       </c>
       <c r="J252" t="n">
-        <v>24.182</v>
+        <v>23.566</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.25</v>
       </c>
       <c r="I253" t="n">
-        <v>0.6708</v>
+        <v>0.6459</v>
       </c>
       <c r="J253" t="n">
-        <v>13.416</v>
+        <v>12.918</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.22</v>
       </c>
       <c r="I254" t="n">
-        <v>0.6025</v>
+        <v>0.5845</v>
       </c>
       <c r="J254" t="n">
-        <v>12.05</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.21</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5789</v>
+        <v>0.5633</v>
       </c>
       <c r="J255" t="n">
-        <v>11.578</v>
+        <v>11.266</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.93</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3223</v>
+        <v>-0.303</v>
       </c>
       <c r="J256" t="n">
-        <v>-6.446</v>
+        <v>-6.06</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.15</v>
       </c>
       <c r="I257" t="n">
-        <v>0.3686</v>
+        <v>0.3635</v>
       </c>
       <c r="J257" t="n">
-        <v>7.372</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.1</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2674</v>
+        <v>0.2677</v>
       </c>
       <c r="J258" t="n">
-        <v>5.348</v>
+        <v>5.354</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.06</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1803</v>
+        <v>0.1836</v>
       </c>
       <c r="J259" t="n">
-        <v>3.606</v>
+        <v>3.672</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.71</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3182</v>
+        <v>-0.3317</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.364</v>
+        <v>-6.634</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.62</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4028</v>
+        <v>-0.4133</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.055999999999999</v>
+        <v>-8.266</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.72</v>
       </c>
       <c r="I262" t="n">
-        <v>1.4335</v>
+        <v>1.4118</v>
       </c>
       <c r="J262" t="n">
-        <v>34.404</v>
+        <v>33.8832</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.35</v>
       </c>
       <c r="I263" t="n">
-        <v>0.9232</v>
+        <v>0.8643</v>
       </c>
       <c r="J263" t="n">
-        <v>22.1568</v>
+        <v>20.7432</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.97</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1697</v>
+        <v>-0.1629</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.0728</v>
+        <v>-3.9096</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2703</v>
+        <v>-0.2591</v>
       </c>
       <c r="J265" t="n">
-        <v>-6.4872</v>
+        <v>-6.2184</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.78</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.7147</v>
+        <v>-0.6626</v>
       </c>
       <c r="J266" t="n">
-        <v>-17.1528</v>
+        <v>-15.9024</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.22</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4949</v>
+        <v>0.482</v>
       </c>
       <c r="J267" t="n">
-        <v>11.8776</v>
+        <v>11.568</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.2</v>
       </c>
       <c r="I268" t="n">
-        <v>0.4577</v>
+        <v>0.4477</v>
       </c>
       <c r="J268" t="n">
-        <v>10.9848</v>
+        <v>10.7448</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.89</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1393</v>
+        <v>-0.1536</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.3432</v>
+        <v>-3.6864</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.88</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.15</v>
+        <v>-0.1646</v>
       </c>
       <c r="J270" t="n">
-        <v>-3.6</v>
+        <v>-3.9504</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.54</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4782</v>
+        <v>-0.4847</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.4768</v>
+        <v>-11.6328</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.17</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4649</v>
+        <v>0.4421</v>
       </c>
       <c r="J272" t="n">
-        <v>8.3682</v>
+        <v>7.9578</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1</v>
       </c>
       <c r="I273" t="n">
-        <v>0.0533</v>
+        <v>0.0387</v>
       </c>
       <c r="J273" t="n">
-        <v>0.9594</v>
+        <v>0.6966</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.96</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.0383</v>
+        <v>-0.0533</v>
       </c>
       <c r="J274" t="n">
-        <v>-0.6894</v>
+        <v>-0.9594</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.55</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4523</v>
+        <v>-0.4629</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.141400000000001</v>
+        <v>-8.3322</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.36</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.626</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="J276" t="n">
-        <v>-11.268</v>
+        <v>-11.259</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.56</v>
       </c>
       <c r="I277" t="n">
-        <v>1.1836</v>
+        <v>1.1558</v>
       </c>
       <c r="J277" t="n">
-        <v>21.3048</v>
+        <v>20.8044</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.48</v>
       </c>
       <c r="I278" t="n">
-        <v>1.0859</v>
+        <v>1.0494</v>
       </c>
       <c r="J278" t="n">
-        <v>19.5462</v>
+        <v>18.8892</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.39</v>
       </c>
       <c r="I279" t="n">
-        <v>0.9532</v>
+        <v>0.9025</v>
       </c>
       <c r="J279" t="n">
-        <v>17.1576</v>
+        <v>16.245</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.21</v>
       </c>
       <c r="I280" t="n">
-        <v>0.554</v>
+        <v>0.5462</v>
       </c>
       <c r="J280" t="n">
-        <v>9.972</v>
+        <v>9.8316</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>1.14</v>
       </c>
       <c r="I281" t="n">
-        <v>0.3761</v>
+        <v>0.3856</v>
       </c>
       <c r="J281" t="n">
-        <v>6.7698</v>
+        <v>6.9408</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.22</v>
       </c>
       <c r="I282" t="n">
-        <v>0.5075</v>
+        <v>0.4912</v>
       </c>
       <c r="J282" t="n">
-        <v>11.165</v>
+        <v>10.8064</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.11</v>
       </c>
       <c r="I283" t="n">
-        <v>0.2923</v>
+        <v>0.2906</v>
       </c>
       <c r="J283" t="n">
-        <v>6.4306</v>
+        <v>6.3932</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.02</v>
       </c>
       <c r="I284" t="n">
-        <v>0.0849</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="J284" t="n">
-        <v>1.8678</v>
+        <v>1.914</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.72</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3071</v>
+        <v>-0.3212</v>
       </c>
       <c r="J285" t="n">
-        <v>-6.7562</v>
+        <v>-7.0664</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.51</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5021</v>
+        <v>-0.5079</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.0462</v>
+        <v>-11.1738</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.5</v>
       </c>
       <c r="I287" t="n">
-        <v>1.1496</v>
+        <v>1.1115</v>
       </c>
       <c r="J287" t="n">
-        <v>25.2912</v>
+        <v>24.453</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.31</v>
       </c>
       <c r="I288" t="n">
-        <v>0.8262</v>
+        <v>0.7799</v>
       </c>
       <c r="J288" t="n">
-        <v>18.1764</v>
+        <v>17.1578</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.2</v>
       </c>
       <c r="I289" t="n">
-        <v>0.5654</v>
+        <v>0.5487</v>
       </c>
       <c r="J289" t="n">
-        <v>12.4388</v>
+        <v>12.0714</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.93</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3058</v>
+        <v>-0.2914</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.7276</v>
+        <v>-6.4108</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.9</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3954</v>
+        <v>-0.3744</v>
       </c>
       <c r="J291" t="n">
-        <v>-8.6988</v>
+        <v>-8.236800000000001</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.81</v>
       </c>
       <c r="I292" t="n">
-        <v>1.5094</v>
+        <v>1.4969</v>
       </c>
       <c r="J292" t="n">
-        <v>28.6786</v>
+        <v>28.4411</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.26</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6905</v>
+        <v>0.6641</v>
       </c>
       <c r="J293" t="n">
-        <v>13.1195</v>
+        <v>12.6179</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.22</v>
       </c>
       <c r="I294" t="n">
-        <v>0.5991</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="J294" t="n">
-        <v>11.3829</v>
+        <v>11.0618</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.06</v>
       </c>
       <c r="I295" t="n">
-        <v>0.171</v>
+        <v>0.1906</v>
       </c>
       <c r="J295" t="n">
-        <v>3.249</v>
+        <v>3.6214</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.92</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3576</v>
+        <v>-0.3348</v>
       </c>
       <c r="J296" t="n">
-        <v>-6.7944</v>
+        <v>-6.3612</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.7</v>
       </c>
       <c r="I297" t="n">
-        <v>1.1806</v>
+        <v>1.1522</v>
       </c>
       <c r="J297" t="n">
-        <v>22.4314</v>
+        <v>21.8918</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.86</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1717</v>
+        <v>-0.1864</v>
       </c>
       <c r="J298" t="n">
-        <v>-3.2623</v>
+        <v>-3.5416</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.8</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.2331</v>
+        <v>-0.2478</v>
       </c>
       <c r="J299" t="n">
-        <v>-4.4289</v>
+        <v>-4.7082</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.74</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2921</v>
+        <v>-0.3058</v>
       </c>
       <c r="J300" t="n">
-        <v>-5.5499</v>
+        <v>-5.8102</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.65</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3775</v>
+        <v>-0.3886</v>
       </c>
       <c r="J301" t="n">
-        <v>-7.1725</v>
+        <v>-7.3834</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.78</v>
       </c>
       <c r="I302" t="n">
-        <v>1.0289</v>
+        <v>0.9907</v>
       </c>
       <c r="J302" t="n">
-        <v>24.6936</v>
+        <v>23.7768</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.91</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.127</v>
+        <v>-0.1385</v>
       </c>
       <c r="J303" t="n">
-        <v>-3.048</v>
+        <v>-3.324</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.85</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1921</v>
+        <v>-0.2047</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.6104</v>
+        <v>-4.9128</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.83</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2128</v>
+        <v>-0.2254</v>
       </c>
       <c r="J305" t="n">
-        <v>-5.1072</v>
+        <v>-5.4096</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2331</v>
+        <v>-0.2457</v>
       </c>
       <c r="J306" t="n">
-        <v>-5.5944</v>
+        <v>-5.8968</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.4</v>
       </c>
       <c r="I307" t="n">
-        <v>0.5359</v>
+        <v>0.5389</v>
       </c>
       <c r="J307" t="n">
-        <v>12.8616</v>
+        <v>12.9336</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.33</v>
       </c>
       <c r="I308" t="n">
-        <v>0.4538</v>
+        <v>0.4615</v>
       </c>
       <c r="J308" t="n">
-        <v>10.8912</v>
+        <v>11.076</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.13</v>
       </c>
       <c r="I309" t="n">
-        <v>0.2038</v>
+        <v>0.2193</v>
       </c>
       <c r="J309" t="n">
-        <v>4.8912</v>
+        <v>5.2632</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.02</v>
       </c>
       <c r="I310" t="n">
-        <v>0.0378</v>
+        <v>0.0477</v>
       </c>
       <c r="J310" t="n">
-        <v>0.9072</v>
+        <v>1.1448</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.57</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4649</v>
+        <v>-0.4699</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.1576</v>
+        <v>-11.2776</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.73</v>
       </c>
       <c r="I312" t="n">
-        <v>1.4348</v>
+        <v>1.4149</v>
       </c>
       <c r="J312" t="n">
-        <v>34.4352</v>
+        <v>33.9576</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.36</v>
       </c>
       <c r="I313" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.8762</v>
       </c>
       <c r="J313" t="n">
-        <v>22.416</v>
+        <v>21.0288</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.1</v>
       </c>
       <c r="I314" t="n">
-        <v>0.3062</v>
+        <v>0.3128</v>
       </c>
       <c r="J314" t="n">
-        <v>7.3488</v>
+        <v>7.5072</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.9</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3995</v>
+        <v>-0.3773</v>
       </c>
       <c r="J315" t="n">
-        <v>-9.587999999999999</v>
+        <v>-9.055199999999999</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.83</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5928</v>
+        <v>-0.5526</v>
       </c>
       <c r="J316" t="n">
-        <v>-14.2272</v>
+        <v>-13.2624</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.16</v>
       </c>
       <c r="I317" t="n">
-        <v>0.376</v>
+        <v>0.3729</v>
       </c>
       <c r="J317" t="n">
-        <v>9.023999999999999</v>
+        <v>8.9496</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.15</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3567</v>
+        <v>0.3547</v>
       </c>
       <c r="J318" t="n">
-        <v>8.5608</v>
+        <v>8.5128</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.12</v>
       </c>
       <c r="I319" t="n">
-        <v>0.2974</v>
+        <v>0.2988</v>
       </c>
       <c r="J319" t="n">
-        <v>7.1376</v>
+        <v>7.1712</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.9</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1301</v>
+        <v>-0.1437</v>
       </c>
       <c r="J320" t="n">
-        <v>-3.1224</v>
+        <v>-3.4488</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.48</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5337</v>
+        <v>-0.537</v>
       </c>
       <c r="J321" t="n">
-        <v>-12.8088</v>
+        <v>-12.888</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/8250/event_8250_evp_summary.xlsx
+++ b/database/event/8250/event_8250_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.9367</v>
+        <v>8.201499999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.6199</v>
+        <v>2.7073</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9887</v>
+        <v>3.0496</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9367</v>
+        <v>8.201499999999999</v>
       </c>
       <c r="F2" t="n">
         <v>3.7489</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6104</v>
+        <v>6.69</v>
       </c>
       <c r="C3" t="n">
-        <v>2.1821</v>
+        <v>2.2083</v>
       </c>
       <c r="D3" t="n">
-        <v>2.385</v>
+        <v>2.3745</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6104</v>
+        <v>6.69</v>
       </c>
       <c r="F3" t="n">
         <v>2.6538</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3069</v>
+        <v>6.4653</v>
       </c>
       <c r="C4" t="n">
-        <v>2.0819</v>
+        <v>2.1342</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2468</v>
+        <v>2.2741</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3069</v>
+        <v>6.4653</v>
       </c>
       <c r="F4" t="n">
         <v>1.2028</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.4523</v>
+        <v>5.6461</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7998</v>
+        <v>1.8637</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8578</v>
+        <v>1.9082</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4523</v>
+        <v>5.6461</v>
       </c>
       <c r="F5" t="n">
-        <v>3.848</v>
+        <v>3.517</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6043</v>
+        <v>1.9327</v>
       </c>
       <c r="H5" t="n">
-        <v>7.8018</v>
+        <v>6.7097</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2129</v>
+        <v>3.6232</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6043</v>
+        <v>1.9327</v>
       </c>
       <c r="K5" t="n">
         <v>84</v>
@@ -667,7 +667,7 @@
         <v>110</v>
       </c>
       <c r="M5" t="n">
-        <v>5.817200000000001</v>
+        <v>5.5559</v>
       </c>
       <c r="N5" t="n">
         <v>194</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.4497</v>
+        <v>5.6095</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7989</v>
+        <v>1.8517</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8566</v>
+        <v>1.8918</v>
       </c>
       <c r="E6" t="n">
-        <v>5.4497</v>
+        <v>5.6095</v>
       </c>
       <c r="F6" t="n">
-        <v>3.517</v>
+        <v>3.848</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9327</v>
+        <v>1.6043</v>
       </c>
       <c r="H6" t="n">
-        <v>6.7097</v>
+        <v>7.8018</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6232</v>
+        <v>4.2129</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9327</v>
+        <v>1.6043</v>
       </c>
       <c r="K6" t="n">
         <v>84</v>
@@ -713,7 +713,7 @@
         <v>110</v>
       </c>
       <c r="M6" t="n">
-        <v>5.5559</v>
+        <v>5.817200000000001</v>
       </c>
       <c r="N6" t="n">
         <v>194</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.3766</v>
+        <v>5.365</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7748</v>
+        <v>1.771</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8233</v>
+        <v>1.7826</v>
       </c>
       <c r="E7" t="n">
-        <v>5.3766</v>
+        <v>5.365</v>
       </c>
       <c r="F7" t="n">
         <v>2.496</v>
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.1439</v>
+        <v>4.2127</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3679</v>
+        <v>1.3906</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2622</v>
+        <v>1.2679</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1439</v>
+        <v>4.2127</v>
       </c>
       <c r="F8" t="n">
         <v>2.4103</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2355</v>
+        <v>3.2465</v>
       </c>
       <c r="C9" t="n">
-        <v>1.068</v>
+        <v>1.0717</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8487</v>
+        <v>0.8363</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2355</v>
+        <v>3.2465</v>
       </c>
       <c r="F9" t="n">
         <v>2.5279</v>
@@ -860,139 +860,139 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0777</v>
+        <v>3.0604</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0159</v>
+        <v>1.0102</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7768</v>
+        <v>0.7532</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0777</v>
+        <v>3.0604</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4192</v>
+        <v>2.6834</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6585</v>
+        <v>0.3509</v>
       </c>
       <c r="H10" t="n">
-        <v>3.0876</v>
+        <v>3.1481</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6673</v>
+        <v>3.1481</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6585</v>
+        <v>0.3509</v>
       </c>
       <c r="K10" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="L10" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3258</v>
+        <v>3.499</v>
       </c>
       <c r="N10" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0343</v>
+        <v>2.9729</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0016</v>
+        <v>0.9813</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7571</v>
+        <v>0.7141</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0343</v>
+        <v>2.9729</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6834</v>
+        <v>2.3948</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3509</v>
+        <v>0.5372</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1481</v>
+        <v>2.5165</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1481</v>
+        <v>2.5813</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3509</v>
+        <v>0.5372</v>
       </c>
       <c r="K11" t="n">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L11" t="n">
-        <v>117</v>
+        <v>75</v>
       </c>
       <c r="M11" t="n">
-        <v>3.499</v>
+        <v>3.1185</v>
       </c>
       <c r="N11" t="n">
-        <v>214</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.932</v>
+        <v>2.9245</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9678</v>
+        <v>0.9654</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7105</v>
+        <v>0.6925</v>
       </c>
       <c r="E12" t="n">
-        <v>2.932</v>
+        <v>2.9245</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3948</v>
+        <v>2.4192</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5372</v>
+        <v>0.6585</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5165</v>
+        <v>3.0876</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5813</v>
+        <v>1.6673</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5372</v>
+        <v>0.6585</v>
       </c>
       <c r="K12" t="n">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="L12" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1185</v>
+        <v>2.3258</v>
       </c>
       <c r="N12" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7391</v>
+        <v>2.7914</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9042</v>
+        <v>0.9214</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6227</v>
+        <v>0.633</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7391</v>
+        <v>2.7914</v>
       </c>
       <c r="F13" t="n">
         <v>1.3013</v>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4756</v>
+        <v>2.3615</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8172</v>
+        <v>0.7795</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5027</v>
+        <v>0.441</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4756</v>
+        <v>2.3615</v>
       </c>
       <c r="F14" t="n">
         <v>2.9787</v>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1502</v>
+        <v>2.3234</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7098</v>
+        <v>0.7669</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3546</v>
+        <v>0.424</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1502</v>
+        <v>2.3234</v>
       </c>
       <c r="F15" t="n">
         <v>1.3395</v>
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7682</v>
+        <v>1.9666</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5837</v>
+        <v>0.6492</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1807</v>
+        <v>0.2646</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7682</v>
+        <v>1.9666</v>
       </c>
       <c r="F16" t="n">
         <v>1.1018</v>
@@ -1182,127 +1182,127 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>dem0n</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5522</v>
+        <v>1.6481</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5124</v>
+        <v>0.544</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0824</v>
+        <v>0.1223</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5522</v>
+        <v>1.6481</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4669</v>
+        <v>1.5307</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0853</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4669</v>
+        <v>1.5307</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4669</v>
+        <v>1.5307</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0853</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="L17" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5522</v>
+        <v>1.5307</v>
       </c>
       <c r="N17" t="n">
-        <v>214</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dem0n</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5307</v>
+        <v>1.6289</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5053</v>
+        <v>0.5377</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0726</v>
+        <v>0.1138</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5307</v>
+        <v>1.6289</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5307</v>
+        <v>1.4669</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.0853</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5307</v>
+        <v>1.4669</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5307</v>
+        <v>1.4669</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.0853</v>
       </c>
       <c r="K18" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5307</v>
+        <v>1.5522</v>
       </c>
       <c r="N18" t="n">
-        <v>108</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4887</v>
+        <v>1.5907</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4914</v>
+        <v>0.5251</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0535</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4887</v>
+        <v>1.5907</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3941</v>
+        <v>1.146</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0946</v>
+        <v>0.3369</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3941</v>
+        <v>1.146</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3941</v>
+        <v>1.146</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0946</v>
+        <v>0.3369</v>
       </c>
       <c r="K19" t="n">
         <v>81</v>
@@ -1311,7 +1311,7 @@
         <v>51</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4887</v>
+        <v>1.4829</v>
       </c>
       <c r="N19" t="n">
         <v>132</v>
@@ -1320,35 +1320,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4829</v>
+        <v>1.5104</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4895</v>
+        <v>0.4986</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0508</v>
+        <v>0.0608</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4829</v>
+        <v>1.5104</v>
       </c>
       <c r="F20" t="n">
-        <v>1.146</v>
+        <v>1.3941</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3369</v>
+        <v>0.0946</v>
       </c>
       <c r="H20" t="n">
-        <v>1.146</v>
+        <v>1.3941</v>
       </c>
       <c r="I20" t="n">
-        <v>1.146</v>
+        <v>1.3941</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3369</v>
+        <v>0.0946</v>
       </c>
       <c r="K20" t="n">
         <v>81</v>
@@ -1357,7 +1357,7 @@
         <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4829</v>
+        <v>1.4887</v>
       </c>
       <c r="N20" t="n">
         <v>132</v>
@@ -1366,311 +1366,311 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3117</v>
+        <v>1.4082</v>
       </c>
       <c r="C21" t="n">
-        <v>0.433</v>
+        <v>0.4648</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0271</v>
+        <v>0.0152</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3117</v>
+        <v>1.4082</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8533</v>
+        <v>0.927</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5416</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8533</v>
+        <v>0.927</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8533</v>
+        <v>0.927</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5416</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="L21" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3117</v>
+        <v>0.927</v>
       </c>
       <c r="N21" t="n">
-        <v>132</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Neityu</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3048</v>
+        <v>1.3612</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4307</v>
+        <v>0.4493</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0302</v>
+        <v>-0.0058</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3048</v>
+        <v>1.3612</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5451</v>
+        <v>1.8533</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2403</v>
+        <v>-0.5416</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5451</v>
+        <v>1.8533</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5451</v>
+        <v>1.8533</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2403</v>
+        <v>-0.5416</v>
       </c>
       <c r="K22" t="n">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="L22" t="n">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3048</v>
+        <v>1.3117</v>
       </c>
       <c r="N22" t="n">
-        <v>214</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>Krabeni</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1798</v>
+        <v>1.3443</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3894</v>
+        <v>0.4437</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0871</v>
+        <v>-0.0134</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1798</v>
+        <v>1.3443</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1798</v>
+        <v>1.0705</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1798</v>
+        <v>1.0705</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1798</v>
+        <v>1.0705</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1798</v>
+        <v>1.0705</v>
       </c>
       <c r="N23" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1005</v>
+        <v>1.3209</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3633</v>
+        <v>0.436</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1232</v>
+        <v>-0.0238</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1005</v>
+        <v>1.3209</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6139</v>
+        <v>1.1798</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4866</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6139</v>
+        <v>1.1798</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6297</v>
+        <v>1.1798</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4866</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="L24" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1163</v>
+        <v>1.1798</v>
       </c>
       <c r="N24" t="n">
-        <v>184</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Krabeni</t>
+          <t>Neityu</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0705</v>
+        <v>1.1321</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3534</v>
+        <v>0.3737</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1369</v>
+        <v>-0.1081</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0705</v>
+        <v>1.1321</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0705</v>
+        <v>1.5451</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.2403</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0705</v>
+        <v>1.5451</v>
       </c>
       <c r="I25" t="n">
-        <v>1.0705</v>
+        <v>1.5451</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.2403</v>
       </c>
       <c r="K25" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0705</v>
+        <v>1.3048</v>
       </c>
       <c r="N25" t="n">
-        <v>108</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.927</v>
+        <v>1.0923</v>
       </c>
       <c r="C26" t="n">
-        <v>0.306</v>
+        <v>0.3606</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2022</v>
+        <v>-0.1259</v>
       </c>
       <c r="E26" t="n">
-        <v>0.927</v>
+        <v>1.0923</v>
       </c>
       <c r="F26" t="n">
-        <v>0.927</v>
+        <v>0.6139</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.4866</v>
       </c>
       <c r="H26" t="n">
-        <v>0.927</v>
+        <v>0.6139</v>
       </c>
       <c r="I26" t="n">
-        <v>0.927</v>
+        <v>0.6297</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.4866</v>
       </c>
       <c r="K26" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M26" t="n">
-        <v>0.927</v>
+        <v>1.1163</v>
       </c>
       <c r="N26" t="n">
-        <v>112</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>jcobbb</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6675</v>
+        <v>0.6957</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2203</v>
+        <v>0.2296</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3203</v>
+        <v>-0.3031</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6675</v>
+        <v>0.6957</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1787</v>
+        <v>-0.0113</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.5112</v>
+        <v>0.6442</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1787</v>
+        <v>-0.0113</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1787</v>
+        <v>-0.0113</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.5112</v>
+        <v>0.6442</v>
       </c>
       <c r="K27" t="n">
         <v>97</v>
@@ -1679,7 +1679,7 @@
         <v>117</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6675000000000001</v>
+        <v>0.6329</v>
       </c>
       <c r="N27" t="n">
         <v>214</v>
@@ -1692,16 +1692,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6737</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2158</v>
+        <v>0.2224</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3266</v>
+        <v>-0.3129</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6737</v>
       </c>
       <c r="F28" t="n">
         <v>-0.7294</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6329</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2089</v>
+        <v>0.2208</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3361</v>
+        <v>-0.315</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6329</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0113</v>
+        <v>0.4715</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6442</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0113</v>
+        <v>0.4715</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0113</v>
+        <v>0.4715</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6442</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="L29" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.6329</v>
+        <v>0.4715</v>
       </c>
       <c r="N29" t="n">
-        <v>214</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>jcobbb</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4715</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1556</v>
+        <v>0.1842</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4096</v>
+        <v>-0.3646</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4715</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4715</v>
+        <v>1.1787</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.5112</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4715</v>
+        <v>1.1787</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4715</v>
+        <v>1.1787</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.5112</v>
       </c>
       <c r="K30" t="n">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M30" t="n">
-        <v>0.4715</v>
+        <v>0.6675000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>112</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31">
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2733</v>
+        <v>0.2671</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0902</v>
+        <v>0.0882</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4998</v>
+        <v>-0.4945</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2733</v>
+        <v>0.2671</v>
       </c>
       <c r="F31" t="n">
         <v>0.2733</v>
@@ -1876,16 +1876,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.2126</v>
+        <v>0.1105</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0702</v>
+        <v>0.0365</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5274</v>
+        <v>-0.5645</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2126</v>
+        <v>0.1105</v>
       </c>
       <c r="F32" t="n">
         <v>-0.064</v>
@@ -1922,16 +1922,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.0384</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0303</v>
+        <v>0.0127</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5824</v>
+        <v>-0.5967</v>
       </c>
       <c r="E33" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.0384</v>
       </c>
       <c r="F33" t="n">
         <v>1.4544</v>
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.2878</v>
+        <v>-0.6239</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.095</v>
+        <v>-0.2059</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7552</v>
+        <v>-0.8925</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.2878</v>
+        <v>-0.6239</v>
       </c>
       <c r="F34" t="n">
         <v>-0.8174</v>
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0014</v>
+        <v>-1.1311</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3306</v>
+        <v>-0.3734</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0801</v>
+        <v>-1.1191</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0014</v>
+        <v>-1.1311</v>
       </c>
       <c r="F35" t="n">
         <v>-0.3019</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>hypex</t>
+          <t>cmtry</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0277</v>
+        <v>-1.2981</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3392</v>
+        <v>-0.4285</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.092</v>
+        <v>-1.1937</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0277</v>
+        <v>-1.2981</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2029</v>
+        <v>-1.047</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.2306</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2029</v>
+        <v>-1.047</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2029</v>
+        <v>-1.047</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.2306</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="L36" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0277</v>
+        <v>-1.047</v>
       </c>
       <c r="N36" t="n">
-        <v>194</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cmtry</t>
+          <t>hypex</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.047</v>
+        <v>-1.3138</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3456</v>
+        <v>-0.4337</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1008</v>
+        <v>-1.2007</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.047</v>
+        <v>-1.3138</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.047</v>
+        <v>0.2029</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-1.2306</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.047</v>
+        <v>0.2029</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.047</v>
+        <v>0.2029</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-1.2306</v>
       </c>
       <c r="K37" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.047</v>
+        <v>-1.0277</v>
       </c>
       <c r="N37" t="n">
-        <v>108</v>
+        <v>194</v>
       </c>
     </row>
     <row r="38">
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0886</v>
+        <v>-1.3508</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3593</v>
+        <v>-0.4459</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1198</v>
+        <v>-1.2172</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0886</v>
+        <v>-1.3508</v>
       </c>
       <c r="F38" t="n">
         <v>-1.0886</v>
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1414</v>
+        <v>-1.518</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3768</v>
+        <v>-0.5011</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1438</v>
+        <v>-1.2919</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1414</v>
+        <v>-1.518</v>
       </c>
       <c r="F39" t="n">
         <v>-1.1414</v>
@@ -2244,16 +2244,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2245</v>
+        <v>-1.6288</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4042</v>
+        <v>-0.5377</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1816</v>
+        <v>-1.3414</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2245</v>
+        <v>-1.6288</v>
       </c>
       <c r="F40" t="n">
         <v>-1.2245</v>
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4442</v>
+        <v>-1.6438</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4767</v>
+        <v>-0.5426</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2816</v>
+        <v>-1.3481</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4442</v>
+        <v>-1.6438</v>
       </c>
       <c r="F41" t="n">
         <v>-0.9208</v>

--- a/database/event/8250/event_8250_evp_summary.xlsx
+++ b/database/event/8250/event_8250_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.201499999999999</v>
+        <v>8.263299999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.7073</v>
+        <v>2.7277</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0496</v>
+        <v>3.1585</v>
       </c>
       <c r="E2" t="n">
-        <v>8.201499999999999</v>
+        <v>8.263299999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7489</v>
+        <v>3.6843</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1878</v>
+        <v>4.3142</v>
       </c>
       <c r="H2" t="n">
-        <v>7.4749</v>
+        <v>7.3897</v>
       </c>
       <c r="I2" t="n">
-        <v>4.0364</v>
+        <v>4.1491</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1878</v>
+        <v>4.3142</v>
       </c>
       <c r="K2" t="n">
         <v>136</v>
@@ -529,7 +529,7 @@
         <v>112</v>
       </c>
       <c r="M2" t="n">
-        <v>8.2242</v>
+        <v>8.4633</v>
       </c>
       <c r="N2" t="n">
         <v>248</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.69</v>
+        <v>6.669</v>
       </c>
       <c r="C3" t="n">
-        <v>2.2083</v>
+        <v>2.2014</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3745</v>
+        <v>2.4323</v>
       </c>
       <c r="E3" t="n">
-        <v>6.69</v>
+        <v>6.669</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6538</v>
+        <v>2.6948</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9566</v>
+        <v>3.8946</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8615</v>
+        <v>3.675</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0852</v>
+        <v>2.0634</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9566</v>
+        <v>3.8946</v>
       </c>
       <c r="K3" t="n">
         <v>136</v>
@@ -575,7 +575,7 @@
         <v>112</v>
       </c>
       <c r="M3" t="n">
-        <v>6.0418</v>
+        <v>5.958</v>
       </c>
       <c r="N3" t="n">
         <v>248</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4653</v>
+        <v>6.6337</v>
       </c>
       <c r="C4" t="n">
-        <v>2.1342</v>
+        <v>2.1897</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2741</v>
+        <v>2.4162</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4653</v>
+        <v>6.6337</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2028</v>
+        <v>1.3415</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1041</v>
+        <v>5.1338</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2028</v>
+        <v>1.3415</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6495</v>
+        <v>0.7532</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1041</v>
+        <v>5.1338</v>
       </c>
       <c r="K4" t="n">
         <v>136</v>
@@ -621,7 +621,7 @@
         <v>112</v>
       </c>
       <c r="M4" t="n">
-        <v>5.7536</v>
+        <v>5.887</v>
       </c>
       <c r="N4" t="n">
         <v>248</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6461</v>
+        <v>5.5156</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8637</v>
+        <v>1.8207</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9082</v>
+        <v>1.9068</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6461</v>
+        <v>5.5156</v>
       </c>
       <c r="F5" t="n">
-        <v>3.517</v>
+        <v>3.4877</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9327</v>
+        <v>1.8315</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7097</v>
+        <v>6.6517</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6232</v>
+        <v>3.7347</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9327</v>
+        <v>1.8315</v>
       </c>
       <c r="K5" t="n">
         <v>84</v>
@@ -667,7 +667,7 @@
         <v>110</v>
       </c>
       <c r="M5" t="n">
-        <v>5.5559</v>
+        <v>5.5662</v>
       </c>
       <c r="N5" t="n">
         <v>194</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.6095</v>
+        <v>5.4573</v>
       </c>
       <c r="C6" t="n">
-        <v>1.8517</v>
+        <v>1.8014</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8918</v>
+        <v>1.8803</v>
       </c>
       <c r="E6" t="n">
-        <v>5.6095</v>
+        <v>5.4573</v>
       </c>
       <c r="F6" t="n">
-        <v>3.848</v>
+        <v>2.6411</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6043</v>
+        <v>2.8278</v>
       </c>
       <c r="H6" t="n">
-        <v>7.8018</v>
+        <v>3.4732</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2129</v>
+        <v>1.9501</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6043</v>
+        <v>2.8278</v>
       </c>
       <c r="K6" t="n">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="L6" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M6" t="n">
-        <v>5.817200000000001</v>
+        <v>4.7779</v>
       </c>
       <c r="N6" t="n">
-        <v>194</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.365</v>
+        <v>5.4349</v>
       </c>
       <c r="C7" t="n">
-        <v>1.771</v>
+        <v>1.794</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7826</v>
+        <v>1.8701</v>
       </c>
       <c r="E7" t="n">
-        <v>5.365</v>
+        <v>5.4349</v>
       </c>
       <c r="F7" t="n">
-        <v>2.496</v>
+        <v>3.7267</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8806</v>
+        <v>1.551</v>
       </c>
       <c r="H7" t="n">
-        <v>3.341</v>
+        <v>7.549</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8041</v>
+        <v>4.2385</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8806</v>
+        <v>1.551</v>
       </c>
       <c r="K7" t="n">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="L7" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M7" t="n">
-        <v>4.684699999999999</v>
+        <v>5.7895</v>
       </c>
       <c r="N7" t="n">
-        <v>248</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.2127</v>
+        <v>4.1512</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3906</v>
+        <v>1.3703</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2679</v>
+        <v>1.2853</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2127</v>
+        <v>4.1512</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4103</v>
+        <v>2.4839</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7336</v>
+        <v>1.5985</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0584</v>
+        <v>2.883</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6515</v>
+        <v>1.6187</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7336</v>
+        <v>1.5985</v>
       </c>
       <c r="K8" t="n">
         <v>84</v>
@@ -805,7 +805,7 @@
         <v>110</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3851</v>
+        <v>3.2172</v>
       </c>
       <c r="N8" t="n">
         <v>194</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2465</v>
+        <v>3.1637</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0717</v>
+        <v>1.0443</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8363</v>
+        <v>0.8354</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2465</v>
+        <v>3.1637</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5279</v>
+        <v>2.4869</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7076</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8079</v>
+        <v>2.7492</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8803</v>
+        <v>2.8226</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7076</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>109</v>
@@ -851,7 +851,7 @@
         <v>75</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5879</v>
+        <v>3.4884</v>
       </c>
       <c r="N9" t="n">
         <v>184</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0604</v>
+        <v>3.1085</v>
       </c>
       <c r="C10" t="n">
-        <v>1.0102</v>
+        <v>1.0261</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7532</v>
+        <v>0.8103</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0604</v>
+        <v>3.1085</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6834</v>
+        <v>2.6486</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3509</v>
+        <v>0.4338</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1481</v>
+        <v>3.1197</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1481</v>
+        <v>3.1197</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3509</v>
+        <v>0.4338</v>
       </c>
       <c r="K10" t="n">
         <v>97</v>
@@ -897,7 +897,7 @@
         <v>117</v>
       </c>
       <c r="M10" t="n">
-        <v>3.499</v>
+        <v>3.5535</v>
       </c>
       <c r="N10" t="n">
         <v>214</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9729</v>
+        <v>3.0732</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9813</v>
+        <v>1.0144</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7141</v>
+        <v>0.7942</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9729</v>
+        <v>3.0732</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3948</v>
+        <v>2.5384</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5372</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5165</v>
+        <v>3.0878</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5813</v>
+        <v>1.7337</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5372</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="L11" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1185</v>
+        <v>2.4217</v>
       </c>
       <c r="N11" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9245</v>
+        <v>2.8997</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9654</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6925</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9245</v>
+        <v>2.8997</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4192</v>
+        <v>2.3249</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6585</v>
+        <v>0.5339</v>
       </c>
       <c r="H12" t="n">
-        <v>3.0876</v>
+        <v>2.3779</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6673</v>
+        <v>2.4415</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6585</v>
+        <v>0.5339</v>
       </c>
       <c r="K12" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="L12" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3258</v>
+        <v>2.9754</v>
       </c>
       <c r="N12" t="n">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7914</v>
+        <v>2.7924</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9214</v>
+        <v>0.9218</v>
       </c>
       <c r="D13" t="n">
-        <v>0.633</v>
+        <v>0.6663</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7914</v>
+        <v>2.7924</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3013</v>
+        <v>1.2916</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4378</v>
+        <v>1.4485</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3013</v>
+        <v>1.2916</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3013</v>
+        <v>1.2916</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4378</v>
+        <v>1.4485</v>
       </c>
       <c r="K13" t="n">
         <v>99</v>
@@ -1035,7 +1035,7 @@
         <v>95</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7391</v>
+        <v>2.7401</v>
       </c>
       <c r="N13" t="n">
         <v>194</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3615</v>
+        <v>2.3989</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7795</v>
+        <v>0.7919</v>
       </c>
       <c r="D14" t="n">
-        <v>0.441</v>
+        <v>0.487</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3615</v>
+        <v>2.3989</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9787</v>
+        <v>1.3919</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5031</v>
+        <v>0.8338</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9338</v>
+        <v>1.3919</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6642</v>
+        <v>1.3919</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5031</v>
+        <v>0.8338</v>
       </c>
       <c r="K14" t="n">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="L14" t="n">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1611</v>
+        <v>2.2257</v>
       </c>
       <c r="N14" t="n">
-        <v>248</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3234</v>
+        <v>2.2947</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7669</v>
+        <v>0.7575</v>
       </c>
       <c r="D15" t="n">
-        <v>0.424</v>
+        <v>0.4396</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3234</v>
+        <v>2.2947</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3395</v>
+        <v>2.9631</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8107</v>
+        <v>-0.5543</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3395</v>
+        <v>4.6822</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3395</v>
+        <v>2.6289</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8107</v>
+        <v>-0.5543</v>
       </c>
       <c r="K15" t="n">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="L15" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1502</v>
+        <v>2.0746</v>
       </c>
       <c r="N15" t="n">
-        <v>194</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9666</v>
+        <v>1.7539</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6492</v>
+        <v>0.579</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2646</v>
+        <v>0.1932</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9666</v>
+        <v>1.7539</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1018</v>
+        <v>0.9978</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6664</v>
+        <v>0.5577</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1018</v>
+        <v>0.9978</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1018</v>
+        <v>0.9978</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6664</v>
+        <v>0.5577</v>
       </c>
       <c r="K16" t="n">
         <v>81</v>
@@ -1173,7 +1173,7 @@
         <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7682</v>
+        <v>1.5555</v>
       </c>
       <c r="N16" t="n">
         <v>132</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dem0n</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6481</v>
+        <v>1.6471</v>
       </c>
       <c r="C17" t="n">
-        <v>0.544</v>
+        <v>0.5437</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1223</v>
+        <v>0.1445</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6481</v>
+        <v>1.6471</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5307</v>
+        <v>1.5464</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5307</v>
+        <v>1.5464</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5307</v>
+        <v>1.5464</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="K17" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5307</v>
+        <v>1.5704</v>
       </c>
       <c r="N17" t="n">
-        <v>108</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>dem0n</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6289</v>
+        <v>1.5394</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5377</v>
+        <v>0.5081</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1138</v>
+        <v>0.0955</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6289</v>
+        <v>1.5394</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4669</v>
+        <v>1.422</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0853</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4669</v>
+        <v>1.422</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4669</v>
+        <v>1.422</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0853</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="L18" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5522</v>
+        <v>1.422</v>
       </c>
       <c r="N18" t="n">
-        <v>214</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5907</v>
+        <v>1.4821</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5251</v>
+        <v>0.4892</v>
       </c>
       <c r="D19" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0694</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5907</v>
+        <v>1.4821</v>
       </c>
       <c r="F19" t="n">
-        <v>1.146</v>
+        <v>1.0535</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3369</v>
+        <v>0.3209</v>
       </c>
       <c r="H19" t="n">
-        <v>1.146</v>
+        <v>1.0535</v>
       </c>
       <c r="I19" t="n">
-        <v>1.146</v>
+        <v>1.0535</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3369</v>
+        <v>0.3209</v>
       </c>
       <c r="K19" t="n">
         <v>81</v>
@@ -1311,7 +1311,7 @@
         <v>51</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4829</v>
+        <v>1.3744</v>
       </c>
       <c r="N19" t="n">
         <v>132</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5104</v>
+        <v>1.4504</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4986</v>
+        <v>0.4788</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0608</v>
+        <v>0.0549</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5104</v>
+        <v>1.4504</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3941</v>
+        <v>1.3673</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0946</v>
+        <v>0.0614</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3941</v>
+        <v>1.3673</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3941</v>
+        <v>1.3673</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0946</v>
+        <v>0.0614</v>
       </c>
       <c r="K20" t="n">
         <v>81</v>
@@ -1357,7 +1357,7 @@
         <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4887</v>
+        <v>1.4287</v>
       </c>
       <c r="N20" t="n">
         <v>132</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4082</v>
+        <v>1.3511</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4648</v>
+        <v>0.446</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0152</v>
+        <v>0.0097</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4082</v>
+        <v>1.3511</v>
       </c>
       <c r="F21" t="n">
-        <v>0.927</v>
+        <v>1.8281</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.5265</v>
       </c>
       <c r="H21" t="n">
-        <v>0.927</v>
+        <v>1.8281</v>
       </c>
       <c r="I21" t="n">
-        <v>0.927</v>
+        <v>1.8281</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.5265</v>
       </c>
       <c r="K21" t="n">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>0.927</v>
+        <v>1.3016</v>
       </c>
       <c r="N21" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3612</v>
+        <v>1.2796</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4493</v>
+        <v>0.4224</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0058</v>
+        <v>-0.0229</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3612</v>
+        <v>1.2796</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8533</v>
+        <v>0.7984</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5416</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.8533</v>
+        <v>0.7984</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8533</v>
+        <v>0.7984</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5416</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="L22" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3117</v>
+        <v>0.7984</v>
       </c>
       <c r="N22" t="n">
-        <v>132</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3443</v>
+        <v>1.1821</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4437</v>
+        <v>0.3902</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0134</v>
+        <v>-0.0673</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3443</v>
+        <v>1.1821</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0705</v>
+        <v>0.9083</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0705</v>
+        <v>0.9083</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0705</v>
+        <v>0.9083</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0705</v>
+        <v>0.9083</v>
       </c>
       <c r="N23" t="n">
         <v>108</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3209</v>
+        <v>1.1676</v>
       </c>
       <c r="C24" t="n">
-        <v>0.436</v>
+        <v>0.3854</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0238</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3209</v>
+        <v>1.1676</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1798</v>
+        <v>1.0265</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1798</v>
+        <v>1.0265</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1798</v>
+        <v>1.0265</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1798</v>
+        <v>1.0265</v>
       </c>
       <c r="N24" t="n">
         <v>112</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.1321</v>
+        <v>1.0599</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3737</v>
+        <v>0.3499</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1081</v>
+        <v>-0.123</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1321</v>
+        <v>1.0599</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5451</v>
+        <v>1.4758</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2403</v>
+        <v>-0.2432</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5451</v>
+        <v>1.4758</v>
       </c>
       <c r="I25" t="n">
-        <v>1.5451</v>
+        <v>1.4758</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2403</v>
+        <v>-0.2432</v>
       </c>
       <c r="K25" t="n">
         <v>97</v>
@@ -1587,7 +1587,7 @@
         <v>117</v>
       </c>
       <c r="M25" t="n">
-        <v>1.3048</v>
+        <v>1.2326</v>
       </c>
       <c r="N25" t="n">
         <v>214</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.0923</v>
+        <v>1.0424</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3606</v>
+        <v>0.3441</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1259</v>
+        <v>-0.1309</v>
       </c>
       <c r="E26" t="n">
-        <v>1.0923</v>
+        <v>1.0424</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6139</v>
+        <v>0.6555</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4866</v>
+        <v>0.3951</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6139</v>
+        <v>0.6555</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6297</v>
+        <v>0.673</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4866</v>
+        <v>0.3951</v>
       </c>
       <c r="K26" t="n">
         <v>109</v>
@@ -1633,7 +1633,7 @@
         <v>75</v>
       </c>
       <c r="M26" t="n">
-        <v>1.1163</v>
+        <v>1.0681</v>
       </c>
       <c r="N26" t="n">
         <v>184</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6957</v>
+        <v>0.61</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2296</v>
+        <v>0.2014</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3031</v>
+        <v>-0.3279</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6957</v>
+        <v>0.61</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0113</v>
+        <v>-0.0452</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6442</v>
+        <v>0.5925</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0113</v>
+        <v>-0.0452</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0113</v>
+        <v>-0.0452</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6442</v>
+        <v>0.5925</v>
       </c>
       <c r="K27" t="n">
         <v>97</v>
@@ -1679,7 +1679,7 @@
         <v>117</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6329</v>
+        <v>0.5473</v>
       </c>
       <c r="N27" t="n">
         <v>214</v>
@@ -1688,47 +1688,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>jcobbb</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6737</v>
+        <v>0.5505</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2224</v>
+        <v>0.1817</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3129</v>
+        <v>-0.355</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6737</v>
+        <v>0.5505</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.7294</v>
+        <v>1.1437</v>
       </c>
       <c r="G28" t="n">
-        <v>1.3831</v>
+        <v>-0.4837</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.7294</v>
+        <v>1.1437</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.7294</v>
+        <v>1.1437</v>
       </c>
       <c r="J28" t="n">
-        <v>1.3831</v>
+        <v>-0.4837</v>
       </c>
       <c r="K28" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L28" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6599999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.5426</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2208</v>
+        <v>0.1791</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.315</v>
+        <v>-0.3586</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.5426</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4715</v>
+        <v>0.3452</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4715</v>
+        <v>0.3452</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4715</v>
+        <v>0.3452</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4715</v>
+        <v>0.3452</v>
       </c>
       <c r="N29" t="n">
         <v>112</v>
@@ -1780,47 +1780,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>jcobbb</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1842</v>
+        <v>0.1755</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3646</v>
+        <v>-0.3635</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1787</v>
+        <v>-0.7894</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.5112</v>
+        <v>1.3012</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1787</v>
+        <v>-0.7894</v>
       </c>
       <c r="I30" t="n">
-        <v>1.1787</v>
+        <v>-0.7894</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.5112</v>
+        <v>1.3012</v>
       </c>
       <c r="K30" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L30" t="n">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6675000000000001</v>
+        <v>0.5117999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>214</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2671</v>
+        <v>0.1963</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0882</v>
+        <v>0.0648</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4945</v>
+        <v>-0.5164</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2671</v>
+        <v>0.1963</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2733</v>
+        <v>0.2025</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2733</v>
+        <v>0.2025</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2733</v>
+        <v>0.2025</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2733</v>
+        <v>0.2025</v>
       </c>
       <c r="N31" t="n">
         <v>108</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.1105</v>
+        <v>0.0341</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0365</v>
+        <v>0.0113</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5645</v>
+        <v>-0.5903</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1105</v>
+        <v>0.0341</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.064</v>
+        <v>-0.1298</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2766</v>
+        <v>0.266</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.064</v>
+        <v>-0.1298</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.1333</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2766</v>
+        <v>0.266</v>
       </c>
       <c r="K32" t="n">
         <v>109</v>
@@ -1909,7 +1909,7 @@
         <v>75</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2109</v>
+        <v>0.1327</v>
       </c>
       <c r="N32" t="n">
         <v>184</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0384</v>
+        <v>-0.0659</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0127</v>
+        <v>-0.0218</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5967</v>
+        <v>-0.6358</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0384</v>
+        <v>-0.0659</v>
       </c>
       <c r="F33" t="n">
-        <v>1.4544</v>
+        <v>1.368</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.3626</v>
+        <v>-1.3805</v>
       </c>
       <c r="H33" t="n">
-        <v>1.4544</v>
+        <v>1.368</v>
       </c>
       <c r="I33" t="n">
-        <v>1.4544</v>
+        <v>1.368</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.3626</v>
+        <v>-1.3805</v>
       </c>
       <c r="K33" t="n">
         <v>99</v>
@@ -1955,7 +1955,7 @@
         <v>95</v>
       </c>
       <c r="M33" t="n">
-        <v>0.09179999999999988</v>
+        <v>-0.01249999999999996</v>
       </c>
       <c r="N33" t="n">
         <v>194</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6239</v>
+        <v>-0.6509</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2059</v>
+        <v>-0.2149</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8925</v>
+        <v>-0.9023</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6239</v>
+        <v>-0.6509</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8174</v>
+        <v>-0.8286</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5296</v>
+        <v>0.5138</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8174</v>
+        <v>-0.8286</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8174</v>
+        <v>-0.8286</v>
       </c>
       <c r="J34" t="n">
-        <v>0.5296</v>
+        <v>0.5138</v>
       </c>
       <c r="K34" t="n">
         <v>81</v>
@@ -2001,7 +2001,7 @@
         <v>51</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2878000000000001</v>
+        <v>-0.3148</v>
       </c>
       <c r="N34" t="n">
         <v>132</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1311</v>
+        <v>-1.1241</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3734</v>
+        <v>-0.3711</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1191</v>
+        <v>-1.1179</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1311</v>
+        <v>-1.1241</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3019</v>
+        <v>-0.3549</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.6995</v>
+        <v>-0.6395</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3019</v>
+        <v>-0.3549</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3097</v>
+        <v>-0.3644</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.6995</v>
+        <v>-0.6395</v>
       </c>
       <c r="K35" t="n">
         <v>109</v>
@@ -2047,7 +2047,7 @@
         <v>75</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.0092</v>
+        <v>-1.0039</v>
       </c>
       <c r="N35" t="n">
         <v>184</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2981</v>
+        <v>-1.2935</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.4285</v>
+        <v>-0.427</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1937</v>
+        <v>-1.195</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2981</v>
+        <v>-1.2935</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.047</v>
+        <v>-1.0424</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.047</v>
+        <v>-1.0424</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.047</v>
+        <v>-1.0424</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.047</v>
+        <v>-1.0424</v>
       </c>
       <c r="N36" t="n">
         <v>108</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3138</v>
+        <v>-1.3016</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.4337</v>
+        <v>-0.4297</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2007</v>
+        <v>-1.1987</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3138</v>
+        <v>-1.3016</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2029</v>
+        <v>0.2653</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.2306</v>
+        <v>-1.2808</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2029</v>
+        <v>0.2653</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2029</v>
+        <v>0.2653</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.2306</v>
+        <v>-1.2808</v>
       </c>
       <c r="K37" t="n">
         <v>99</v>
@@ -2139,7 +2139,7 @@
         <v>95</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0277</v>
+        <v>-1.0155</v>
       </c>
       <c r="N37" t="n">
         <v>194</v>
@@ -2148,124 +2148,124 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>coolio</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3508</v>
+        <v>-1.3839</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4459</v>
+        <v>-0.4568</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2172</v>
+        <v>-1.2362</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3508</v>
+        <v>-1.3839</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0886</v>
+        <v>-0.6873</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.497</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0886</v>
+        <v>-0.6873</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0886</v>
+        <v>-0.3859</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.497</v>
       </c>
       <c r="K38" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0886</v>
+        <v>-0.8829</v>
       </c>
       <c r="N38" t="n">
-        <v>108</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>coolio</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.518</v>
+        <v>-1.3865</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5011</v>
+        <v>-0.4577</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2919</v>
+        <v>-1.2374</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.518</v>
+        <v>-1.3865</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1414</v>
+        <v>-1.1243</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1414</v>
+        <v>-1.1243</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1414</v>
+        <v>-1.1243</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1414</v>
+        <v>-1.1243</v>
       </c>
       <c r="N39" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.6288</v>
+        <v>-1.4925</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5377</v>
+        <v>-0.4927</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3414</v>
+        <v>-1.2857</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.6288</v>
+        <v>-1.4925</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2245</v>
+        <v>-1.1159</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2245</v>
+        <v>-1.1159</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2245</v>
+        <v>-1.1159</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2245</v>
+        <v>-1.1159</v>
       </c>
       <c r="N40" t="n">
         <v>112</v>
@@ -2286,47 +2286,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.6438</v>
+        <v>-1.5975</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5426</v>
+        <v>-0.5273</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3481</v>
+        <v>-1.3335</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.6438</v>
+        <v>-1.5975</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.9208</v>
+        <v>-1.1932</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5234</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.9208</v>
+        <v>-1.1932</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4972</v>
+        <v>-1.1932</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.5234</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="L41" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.0206</v>
+        <v>-1.1932</v>
       </c>
       <c r="N41" t="n">
-        <v>194</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.25</v>
       </c>
       <c r="I2" t="n">
-        <v>0.533</v>
+        <v>0.4752</v>
       </c>
       <c r="J2" t="n">
-        <v>14.924</v>
+        <v>13.3056</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2639</v>
+        <v>0.2161</v>
       </c>
       <c r="J3" t="n">
-        <v>7.3892</v>
+        <v>6.0508</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0693</v>
+        <v>-0.0565</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.9404</v>
+        <v>-1.582</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2372</v>
+        <v>-0.2171</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.6416</v>
+        <v>-6.0788</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.6</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4324</v>
+        <v>-0.425</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.1072</v>
+        <v>-11.9</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1195</v>
+        <v>1.1253</v>
       </c>
       <c r="J7" t="n">
-        <v>31.346</v>
+        <v>31.5084</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.38</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8958</v>
+        <v>0.881</v>
       </c>
       <c r="J8" t="n">
-        <v>25.0824</v>
+        <v>24.668</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.23</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6006</v>
+        <v>0.5714</v>
       </c>
       <c r="J9" t="n">
-        <v>16.8168</v>
+        <v>15.9992</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.536</v>
+        <v>0.5053</v>
       </c>
       <c r="J10" t="n">
-        <v>15.008</v>
+        <v>14.1484</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.07</v>
       </c>
       <c r="I11" t="n">
-        <v>0.216</v>
+        <v>0.1868</v>
       </c>
       <c r="J11" t="n">
-        <v>6.048</v>
+        <v>5.2304</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.67</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1064</v>
+        <v>1.0758</v>
       </c>
       <c r="J12" t="n">
-        <v>26.5536</v>
+        <v>25.8192</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.27</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5306</v>
+        <v>0.4711</v>
       </c>
       <c r="J13" t="n">
-        <v>12.7344</v>
+        <v>11.3064</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.11</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2598</v>
+        <v>0.2146</v>
       </c>
       <c r="J14" t="n">
-        <v>6.2352</v>
+        <v>5.1504</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.84</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2189</v>
+        <v>-0.1985</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.2536</v>
+        <v>-4.764</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.51</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.52</v>
+        <v>-0.5256</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.48</v>
+        <v>-12.6144</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.69</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5116</v>
+        <v>1.5499</v>
       </c>
       <c r="J17" t="n">
-        <v>36.2784</v>
+        <v>37.1976</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4671</v>
+        <v>0.4279</v>
       </c>
       <c r="J18" t="n">
-        <v>11.2104</v>
+        <v>10.2696</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.09</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2971</v>
+        <v>0.2619</v>
       </c>
       <c r="J19" t="n">
-        <v>7.1304</v>
+        <v>6.2856</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.98</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1193</v>
+        <v>-0.0924</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.8632</v>
+        <v>-2.2176</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.65</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9354</v>
+        <v>-0.9268999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-22.4496</v>
+        <v>-22.2456</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.35</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7558</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>12.0928</v>
+        <v>11.5248</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.79</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.244</v>
+        <v>-0.2263</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.904</v>
+        <v>-3.6208</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.75</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2818</v>
+        <v>-0.2642</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.5088</v>
+        <v>-4.2272</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.66</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3648</v>
+        <v>-0.3506</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.8368</v>
+        <v>-5.6096</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.48</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5234</v>
+        <v>-0.5258</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.3744</v>
+        <v>-8.412800000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>2.18</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J27" t="n">
-        <v>29.5248</v>
+        <v>31.7152</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.93</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7347</v>
+        <v>1.7696</v>
       </c>
       <c r="J28" t="n">
-        <v>27.7552</v>
+        <v>28.3136</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.25</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6169</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>9.8704</v>
+        <v>9.491199999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.13</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3459</v>
+        <v>0.313</v>
       </c>
       <c r="J30" t="n">
-        <v>5.5344</v>
+        <v>5.008</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.8</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6625</v>
+        <v>-0.6387</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.6</v>
+        <v>-10.2192</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>2.12</v>
       </c>
       <c r="I32" t="n">
-        <v>1.6279</v>
+        <v>1.6568</v>
       </c>
       <c r="J32" t="n">
-        <v>22.7906</v>
+        <v>23.1952</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.96</v>
       </c>
       <c r="I33" t="n">
-        <v>1.4483</v>
+        <v>1.4629</v>
       </c>
       <c r="J33" t="n">
-        <v>20.2762</v>
+        <v>20.4806</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.7</v>
       </c>
       <c r="I34" t="n">
-        <v>1.1476</v>
+        <v>1.1482</v>
       </c>
       <c r="J34" t="n">
-        <v>16.0664</v>
+        <v>16.0748</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.36</v>
       </c>
       <c r="I35" t="n">
-        <v>0.713</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>9.981999999999999</v>
+        <v>9.928800000000001</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.17</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4131</v>
+        <v>0.3794</v>
       </c>
       <c r="J36" t="n">
-        <v>5.7834</v>
+        <v>5.3116</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.72</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2511</v>
+        <v>-0.2327</v>
       </c>
       <c r="J37" t="n">
-        <v>-3.5154</v>
+        <v>-3.2578</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.64</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3351</v>
+        <v>-0.3259</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.6914</v>
+        <v>-4.5626</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.44</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5158</v>
+        <v>-0.5171</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.2212</v>
+        <v>-7.2394</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.41</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5423</v>
+        <v>-0.5458</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.5922</v>
+        <v>-7.6412</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.27</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6694</v>
+        <v>-0.6913</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.371600000000001</v>
+        <v>-9.6782</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.23</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5767</v>
+        <v>0.5655</v>
       </c>
       <c r="J42" t="n">
-        <v>17.301</v>
+        <v>16.965</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.21</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5442</v>
+        <v>0.5337</v>
       </c>
       <c r="J43" t="n">
-        <v>16.326</v>
+        <v>16.011</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.09</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2979</v>
+        <v>0.2623</v>
       </c>
       <c r="J44" t="n">
-        <v>8.936999999999999</v>
+        <v>7.869</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.02</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0838</v>
+        <v>0.0663</v>
       </c>
       <c r="J45" t="n">
-        <v>2.514</v>
+        <v>1.989</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.99</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0565</v>
       </c>
       <c r="J46" t="n">
-        <v>-2.304</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.26</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5027</v>
+        <v>0.4658</v>
       </c>
       <c r="J47" t="n">
-        <v>15.081</v>
+        <v>13.974</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.12</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2852</v>
+        <v>0.2363</v>
       </c>
       <c r="J48" t="n">
-        <v>8.555999999999999</v>
+        <v>7.089</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.09</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2276</v>
+        <v>0.1843</v>
       </c>
       <c r="J49" t="n">
-        <v>6.828</v>
+        <v>5.529</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.87</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.183</v>
+        <v>-0.1624</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.49</v>
+        <v>-4.872</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.82</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2353</v>
+        <v>-0.215</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.059</v>
+        <v>-6.45</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.79</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3156</v>
+        <v>1.3201</v>
       </c>
       <c r="J52" t="n">
-        <v>23.6808</v>
+        <v>23.7618</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.4</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8032</v>
+        <v>0.7895</v>
       </c>
       <c r="J53" t="n">
-        <v>14.4576</v>
+        <v>14.211</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.15</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4192</v>
+        <v>0.3881</v>
       </c>
       <c r="J54" t="n">
-        <v>7.5456</v>
+        <v>6.9858</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.14</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3962</v>
+        <v>0.364</v>
       </c>
       <c r="J55" t="n">
-        <v>7.1316</v>
+        <v>6.552</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2203</v>
+        <v>-0.1874</v>
       </c>
       <c r="J56" t="n">
-        <v>-3.9654</v>
+        <v>-3.3732</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.99</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0176</v>
+        <v>0.0273</v>
       </c>
       <c r="J57" t="n">
-        <v>0.3168</v>
+        <v>0.4914</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.83</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1977</v>
+        <v>-0.1821</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.5586</v>
+        <v>-3.2778</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.8</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2285</v>
+        <v>-0.2129</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.113</v>
+        <v>-3.8322</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.6</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4108</v>
+        <v>-0.4003</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.3944</v>
+        <v>-7.2054</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.48</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5163</v>
+        <v>-0.517</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.2934</v>
+        <v>-9.305999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.45</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8864</v>
+        <v>0.8712</v>
       </c>
       <c r="J62" t="n">
-        <v>21.2736</v>
+        <v>20.9088</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.4</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8159</v>
+        <v>0.8004</v>
       </c>
       <c r="J63" t="n">
-        <v>19.5816</v>
+        <v>19.2096</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.24</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.5707</v>
       </c>
       <c r="J64" t="n">
-        <v>13.8984</v>
+        <v>13.6968</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.02</v>
       </c>
       <c r="I65" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0505</v>
       </c>
       <c r="J65" t="n">
-        <v>1.5984</v>
+        <v>1.212</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.92</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3266</v>
+        <v>-0.2865</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.8384</v>
+        <v>-6.876</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.36</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6331</v>
+        <v>0.6047</v>
       </c>
       <c r="J67" t="n">
-        <v>15.1944</v>
+        <v>14.5128</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.09</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2391</v>
+        <v>0.1935</v>
       </c>
       <c r="J68" t="n">
-        <v>5.7384</v>
+        <v>4.644</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0035</v>
+        <v>0.0018</v>
       </c>
       <c r="J69" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0432</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.8</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2493</v>
+        <v>-0.2293</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.9832</v>
+        <v>-5.5032</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.58</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4518</v>
+        <v>-0.4469</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.8432</v>
+        <v>-10.7256</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.85</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4136</v>
+        <v>1.4298</v>
       </c>
       <c r="J72" t="n">
-        <v>29.6856</v>
+        <v>30.0258</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.49</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9415</v>
+        <v>0.9273</v>
       </c>
       <c r="J73" t="n">
-        <v>19.7715</v>
+        <v>19.4733</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.16</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4502</v>
+        <v>0.4214</v>
       </c>
       <c r="J74" t="n">
-        <v>9.4542</v>
+        <v>8.849399999999999</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.82</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5803</v>
+        <v>-0.5442</v>
       </c>
       <c r="J75" t="n">
-        <v>-12.1863</v>
+        <v>-11.4282</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.72</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.8037</v>
+        <v>-0.7839</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.8777</v>
+        <v>-16.4619</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.34</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6068</v>
+        <v>0.5793</v>
       </c>
       <c r="J77" t="n">
-        <v>12.7428</v>
+        <v>12.1653</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.14</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3323</v>
+        <v>0.2794</v>
       </c>
       <c r="J78" t="n">
-        <v>6.9783</v>
+        <v>5.8674</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.13</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3137</v>
+        <v>0.2621</v>
       </c>
       <c r="J79" t="n">
-        <v>6.5877</v>
+        <v>5.5041</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.74</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3086</v>
+        <v>-0.2911</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.4806</v>
+        <v>-6.1131</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.55</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4789</v>
+        <v>-0.4775</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.0569</v>
+        <v>-10.0275</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.5</v>
       </c>
       <c r="I82" t="n">
-        <v>0.9725</v>
+        <v>0.9598</v>
       </c>
       <c r="J82" t="n">
-        <v>29.175</v>
+        <v>28.794</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.47</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9304</v>
+        <v>0.9163</v>
       </c>
       <c r="J83" t="n">
-        <v>27.912</v>
+        <v>27.489</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.11</v>
       </c>
       <c r="I84" t="n">
-        <v>0.3458</v>
+        <v>0.3097</v>
       </c>
       <c r="J84" t="n">
-        <v>10.374</v>
+        <v>9.291</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.85</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4954</v>
+        <v>-0.4544</v>
       </c>
       <c r="J85" t="n">
-        <v>-14.862</v>
+        <v>-13.632</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.74</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7481</v>
+        <v>-0.7214</v>
       </c>
       <c r="J86" t="n">
-        <v>-22.443</v>
+        <v>-21.642</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.39</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6455</v>
+        <v>0.6142</v>
       </c>
       <c r="J87" t="n">
-        <v>19.365</v>
+        <v>18.426</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.16</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3527</v>
+        <v>0.2995</v>
       </c>
       <c r="J88" t="n">
-        <v>10.581</v>
+        <v>8.984999999999999</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.97</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.049</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.881</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.96</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0772</v>
+        <v>-0.0619</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.316</v>
+        <v>-1.857</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.82</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2377</v>
+        <v>-0.2176</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.131</v>
+        <v>-6.528</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.76</v>
       </c>
       <c r="I92" t="n">
-        <v>1.019</v>
+        <v>0.9829</v>
       </c>
       <c r="J92" t="n">
-        <v>24.456</v>
+        <v>23.5896</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.99</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0315</v>
+        <v>-0.0226</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.756</v>
+        <v>-0.5424</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.96</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0794</v>
+        <v>-0.0639</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.9056</v>
+        <v>-1.5336</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.88</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1769</v>
+        <v>-0.1564</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.2456</v>
+        <v>-3.7536</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.85</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2091</v>
+        <v>-0.1887</v>
       </c>
       <c r="J96" t="n">
-        <v>-5.0184</v>
+        <v>-4.5288</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.28</v>
       </c>
       <c r="I97" t="n">
-        <v>0.67</v>
+        <v>0.6551</v>
       </c>
       <c r="J97" t="n">
-        <v>16.08</v>
+        <v>15.7224</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.11</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3586</v>
+        <v>0.3176</v>
       </c>
       <c r="J98" t="n">
-        <v>8.606400000000001</v>
+        <v>7.6224</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.03</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1303</v>
+        <v>0.1051</v>
       </c>
       <c r="J99" t="n">
-        <v>3.1272</v>
+        <v>2.5224</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.92</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2959</v>
+        <v>-0.2549</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.1016</v>
+        <v>-6.1176</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.87</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4279</v>
+        <v>-0.3848</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.2696</v>
+        <v>-9.235200000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.51</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5954</v>
+        <v>0.5591</v>
       </c>
       <c r="J102" t="n">
-        <v>13.0988</v>
+        <v>12.3002</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.3</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4223</v>
+        <v>0.3589</v>
       </c>
       <c r="J103" t="n">
-        <v>9.2906</v>
+        <v>7.8958</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.04</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0835</v>
+        <v>0.0612</v>
       </c>
       <c r="J104" t="n">
-        <v>1.837</v>
+        <v>1.3464</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.9</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1567</v>
+        <v>-0.1368</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.4474</v>
+        <v>-3.0096</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.83</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2322</v>
+        <v>-0.2123</v>
       </c>
       <c r="J106" t="n">
-        <v>-5.1084</v>
+        <v>-4.6706</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.15</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2873</v>
+        <v>0.2752</v>
       </c>
       <c r="J107" t="n">
-        <v>6.3206</v>
+        <v>6.0544</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.01</v>
       </c>
       <c r="I108" t="n">
-        <v>0.0439</v>
+        <v>0.0336</v>
       </c>
       <c r="J108" t="n">
-        <v>0.9658</v>
+        <v>0.7392</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.97</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0526</v>
+        <v>-0.0423</v>
       </c>
       <c r="J109" t="n">
-        <v>-1.1572</v>
+        <v>-0.9306</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.91</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.129</v>
+        <v>-0.1117</v>
       </c>
       <c r="J110" t="n">
-        <v>-2.838</v>
+        <v>-2.4574</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.54</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4822</v>
+        <v>-0.4803</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.6084</v>
+        <v>-10.5666</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.42</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7035</v>
+        <v>0.6731</v>
       </c>
       <c r="J112" t="n">
-        <v>20.4015</v>
+        <v>19.5199</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.09</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2412</v>
+        <v>0.1954</v>
       </c>
       <c r="J113" t="n">
-        <v>6.9948</v>
+        <v>5.6666</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.79</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2582</v>
+        <v>-0.2385</v>
       </c>
       <c r="J114" t="n">
-        <v>-7.4878</v>
+        <v>-6.9165</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.76</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2873</v>
+        <v>-0.2686</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.3317</v>
+        <v>-7.7894</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.72</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3251</v>
+        <v>-0.3085</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.427899999999999</v>
+        <v>-8.9465</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.63</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1464</v>
+        <v>1.1424</v>
       </c>
       <c r="J117" t="n">
-        <v>33.2456</v>
+        <v>33.1296</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3184</v>
+        <v>0.2838</v>
       </c>
       <c r="J118" t="n">
-        <v>9.233599999999999</v>
+        <v>8.2302</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.08</v>
       </c>
       <c r="I119" t="n">
-        <v>0.2652</v>
+        <v>0.2328</v>
       </c>
       <c r="J119" t="n">
-        <v>7.6908</v>
+        <v>6.7512</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.99</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.4389</v>
+        <v>-1.8328</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2584</v>
+        <v>-0.2196</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.4936</v>
+        <v>-6.3684</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>2.13</v>
       </c>
       <c r="I122" t="n">
-        <v>1.8854</v>
+        <v>1.9637</v>
       </c>
       <c r="J122" t="n">
-        <v>43.3642</v>
+        <v>45.1651</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.49</v>
       </c>
       <c r="I123" t="n">
-        <v>1.0783</v>
+        <v>1.088</v>
       </c>
       <c r="J123" t="n">
-        <v>24.8009</v>
+        <v>25.024</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.97</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1822</v>
+        <v>-0.1517</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.1906</v>
+        <v>-3.4891</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.493</v>
+        <v>-0.455</v>
       </c>
       <c r="J125" t="n">
-        <v>-11.339</v>
+        <v>-10.465</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.86</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.493</v>
+        <v>-0.455</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.339</v>
+        <v>-10.465</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.23</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5013</v>
+        <v>0.4438</v>
       </c>
       <c r="J127" t="n">
-        <v>11.5299</v>
+        <v>10.2074</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.11</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2851</v>
+        <v>0.2356</v>
       </c>
       <c r="J128" t="n">
-        <v>6.5573</v>
+        <v>5.4188</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.095</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.185</v>
+        <v>-1.8331</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.79</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2565</v>
+        <v>-0.2368</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.8995</v>
+        <v>-5.4464</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.62</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4142</v>
+        <v>-0.4048</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.5266</v>
+        <v>-9.3104</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.78</v>
       </c>
       <c r="I132" t="n">
-        <v>1.4124</v>
+        <v>1.4386</v>
       </c>
       <c r="J132" t="n">
-        <v>24.0108</v>
+        <v>24.4562</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.51</v>
       </c>
       <c r="I133" t="n">
-        <v>1.0769</v>
+        <v>1.0925</v>
       </c>
       <c r="J133" t="n">
-        <v>18.3073</v>
+        <v>18.5725</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.43</v>
       </c>
       <c r="I134" t="n">
-        <v>0.9614</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="J134" t="n">
-        <v>16.3438</v>
+        <v>16.3744</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.36</v>
       </c>
       <c r="I135" t="n">
-        <v>0.8341</v>
+        <v>0.8244</v>
       </c>
       <c r="J135" t="n">
-        <v>14.1797</v>
+        <v>14.0148</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.3</v>
       </c>
       <c r="I136" t="n">
-        <v>0.7169</v>
+        <v>0.6992</v>
       </c>
       <c r="J136" t="n">
-        <v>12.1873</v>
+        <v>11.8864</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.09</v>
       </c>
       <c r="I137" t="n">
-        <v>0.319</v>
+        <v>0.2821</v>
       </c>
       <c r="J137" t="n">
-        <v>5.423</v>
+        <v>4.7957</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.87</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.1521</v>
+        <v>-0.1365</v>
       </c>
       <c r="J138" t="n">
-        <v>-2.5857</v>
+        <v>-2.3205</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.77</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2564</v>
+        <v>-0.2412</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.3588</v>
+        <v>-4.1004</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.49</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5062</v>
+        <v>-0.5054</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.605399999999999</v>
+        <v>-8.591799999999999</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.42</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5669</v>
+        <v>-0.5747</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.6373</v>
+        <v>-9.7699</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.57</v>
       </c>
       <c r="I142" t="n">
-        <v>1.181</v>
+        <v>1.1952</v>
       </c>
       <c r="J142" t="n">
-        <v>20.077</v>
+        <v>20.3184</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.48</v>
       </c>
       <c r="I143" t="n">
-        <v>1.0602</v>
+        <v>1.0682</v>
       </c>
       <c r="J143" t="n">
-        <v>18.0234</v>
+        <v>18.1594</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.14</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3966</v>
+        <v>0.3643</v>
       </c>
       <c r="J144" t="n">
-        <v>6.7422</v>
+        <v>6.1931</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.14</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3966</v>
+        <v>0.3643</v>
       </c>
       <c r="J145" t="n">
-        <v>6.7422</v>
+        <v>6.1931</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.1</v>
       </c>
       <c r="I146" t="n">
-        <v>0.2962</v>
+        <v>0.2647</v>
       </c>
       <c r="J146" t="n">
-        <v>5.0354</v>
+        <v>4.4999</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.29</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6303</v>
+        <v>0.5802</v>
       </c>
       <c r="J147" t="n">
-        <v>10.7151</v>
+        <v>9.8634</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.06</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2009</v>
+        <v>0.1608</v>
       </c>
       <c r="J148" t="n">
-        <v>3.4153</v>
+        <v>2.7336</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.74</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2968</v>
+        <v>-0.2788</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.0456</v>
+        <v>-4.7396</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.65</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3797</v>
+        <v>-0.3666</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.4549</v>
+        <v>-6.2322</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4596</v>
+        <v>-0.4543</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.8132</v>
+        <v>-7.7231</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.32</v>
       </c>
       <c r="I152" t="n">
-        <v>0.536</v>
+        <v>0.5608</v>
       </c>
       <c r="J152" t="n">
-        <v>10.72</v>
+        <v>11.216</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2284</v>
+        <v>-0.2095</v>
       </c>
       <c r="J153" t="n">
-        <v>-4.568</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.77</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2672</v>
+        <v>-0.2486</v>
       </c>
       <c r="J154" t="n">
-        <v>-5.344</v>
+        <v>-4.972</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.75</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2863</v>
+        <v>-0.2681</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.726</v>
+        <v>-5.362</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.6</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4234</v>
+        <v>-0.4141</v>
       </c>
       <c r="J156" t="n">
-        <v>-8.468</v>
+        <v>-8.282</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.96</v>
       </c>
       <c r="I157" t="n">
-        <v>1.0442</v>
+        <v>0.9999</v>
       </c>
       <c r="J157" t="n">
-        <v>20.884</v>
+        <v>19.998</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.33</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4429</v>
+        <v>0.3786</v>
       </c>
       <c r="J158" t="n">
-        <v>8.858000000000001</v>
+        <v>7.572</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.06</v>
       </c>
       <c r="I159" t="n">
-        <v>0.1068</v>
+        <v>0.0805</v>
       </c>
       <c r="J159" t="n">
-        <v>2.136</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.96</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.0905</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="J160" t="n">
-        <v>-1.81</v>
+        <v>-1.498</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.84</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2305</v>
+        <v>-0.2118</v>
       </c>
       <c r="J161" t="n">
-        <v>-4.61</v>
+        <v>-4.236</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.94</v>
       </c>
       <c r="I162" t="n">
-        <v>1.603</v>
+        <v>1.6423</v>
       </c>
       <c r="J162" t="n">
-        <v>25.648</v>
+        <v>26.2768</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.59</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1783</v>
+        <v>1.1961</v>
       </c>
       <c r="J163" t="n">
-        <v>18.8528</v>
+        <v>19.1376</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.53</v>
       </c>
       <c r="I164" t="n">
-        <v>1.1024</v>
+        <v>1.1193</v>
       </c>
       <c r="J164" t="n">
-        <v>17.6384</v>
+        <v>17.9088</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.36</v>
       </c>
       <c r="I165" t="n">
-        <v>0.8341</v>
+        <v>0.8244</v>
       </c>
       <c r="J165" t="n">
-        <v>13.3456</v>
+        <v>13.1904</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.96</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2482</v>
+        <v>-0.2205</v>
       </c>
       <c r="J166" t="n">
-        <v>-3.9712</v>
+        <v>-3.528</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.77</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.2413</v>
+        <v>-0.2271</v>
       </c>
       <c r="J167" t="n">
-        <v>-3.8608</v>
+        <v>-3.6336</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.72</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2911</v>
+        <v>-0.2789</v>
       </c>
       <c r="J168" t="n">
-        <v>-4.6576</v>
+        <v>-4.4624</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.61</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3892</v>
+        <v>-0.3794</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.2272</v>
+        <v>-6.0704</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.55</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4417</v>
+        <v>-0.4345</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.0672</v>
+        <v>-6.952</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.54</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4505</v>
+        <v>-0.444</v>
       </c>
       <c r="J171" t="n">
-        <v>-7.208</v>
+        <v>-7.104</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.51</v>
       </c>
       <c r="I172" t="n">
-        <v>1.1282</v>
+        <v>1.141</v>
       </c>
       <c r="J172" t="n">
-        <v>32.7178</v>
+        <v>33.089</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.32</v>
       </c>
       <c r="I173" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.7774</v>
       </c>
       <c r="J173" t="n">
-        <v>23.2841</v>
+        <v>22.5446</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.594</v>
+        <v>0.5585</v>
       </c>
       <c r="J174" t="n">
-        <v>17.226</v>
+        <v>16.1965</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.92</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3176</v>
+        <v>-0.2767</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.2104</v>
+        <v>-8.0243</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5947</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="J176" t="n">
-        <v>-17.2463</v>
+        <v>-16.182</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.51</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9349</v>
+        <v>0.899</v>
       </c>
       <c r="J177" t="n">
-        <v>27.1121</v>
+        <v>26.071</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.98</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0394</v>
+        <v>-0.0307</v>
       </c>
       <c r="J178" t="n">
-        <v>-1.1426</v>
+        <v>-0.8903</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.95</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.0684</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.3954</v>
+        <v>-1.9836</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.71</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3333</v>
+        <v>-0.3171</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.665699999999999</v>
+        <v>-9.1959</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.57</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4586</v>
+        <v>-0.4542</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.2994</v>
+        <v>-13.1718</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.21</v>
       </c>
       <c r="I182" t="n">
-        <v>0.3655</v>
+        <v>0.3599</v>
       </c>
       <c r="J182" t="n">
-        <v>8.772</v>
+        <v>8.637600000000001</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.16</v>
       </c>
       <c r="I183" t="n">
-        <v>0.2965</v>
+        <v>0.2845</v>
       </c>
       <c r="J183" t="n">
-        <v>7.116</v>
+        <v>6.828</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.95</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0824</v>
+        <v>-0.0683</v>
       </c>
       <c r="J184" t="n">
-        <v>-1.9776</v>
+        <v>-1.6392</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.87</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1749</v>
+        <v>-0.155</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.1976</v>
+        <v>-3.72</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.51</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5099</v>
+        <v>-0.5121</v>
       </c>
       <c r="J186" t="n">
-        <v>-12.2376</v>
+        <v>-12.2904</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.33</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4629</v>
+        <v>0.396</v>
       </c>
       <c r="J187" t="n">
-        <v>11.1096</v>
+        <v>9.504</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.31</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4402</v>
+        <v>0.3744</v>
       </c>
       <c r="J188" t="n">
-        <v>10.5648</v>
+        <v>8.9856</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.18</v>
       </c>
       <c r="I189" t="n">
-        <v>0.285</v>
+        <v>0.2313</v>
       </c>
       <c r="J189" t="n">
-        <v>6.84</v>
+        <v>5.5512</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.85</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2086</v>
+        <v>-0.1881</v>
       </c>
       <c r="J190" t="n">
-        <v>-5.0064</v>
+        <v>-4.5144</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.74</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3174</v>
+        <v>-0.3012</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.6176</v>
+        <v>-7.2288</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.96</v>
       </c>
       <c r="I192" t="n">
-        <v>1.6138</v>
+        <v>1.654</v>
       </c>
       <c r="J192" t="n">
-        <v>25.8208</v>
+        <v>26.464</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.65</v>
       </c>
       <c r="I193" t="n">
-        <v>1.2453</v>
+        <v>1.2664</v>
       </c>
       <c r="J193" t="n">
-        <v>19.9248</v>
+        <v>20.2624</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.58</v>
       </c>
       <c r="I194" t="n">
-        <v>1.1594</v>
+        <v>1.1791</v>
       </c>
       <c r="J194" t="n">
-        <v>18.5504</v>
+        <v>18.8656</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.33</v>
       </c>
       <c r="I195" t="n">
-        <v>0.767</v>
+        <v>0.754</v>
       </c>
       <c r="J195" t="n">
-        <v>12.272</v>
+        <v>12.064</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.2</v>
       </c>
       <c r="I196" t="n">
-        <v>0.4969</v>
+        <v>0.4676</v>
       </c>
       <c r="J196" t="n">
-        <v>7.9504</v>
+        <v>7.4816</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.19</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5389</v>
+        <v>0.5088</v>
       </c>
       <c r="J197" t="n">
-        <v>8.622400000000001</v>
+        <v>8.1408</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.03</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1895</v>
+        <v>0.1673</v>
       </c>
       <c r="J198" t="n">
-        <v>3.032</v>
+        <v>2.6768</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.52</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4762</v>
+        <v>-0.4718</v>
       </c>
       <c r="J199" t="n">
-        <v>-7.6192</v>
+        <v>-7.5488</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.47</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.52</v>
+        <v>-0.5208</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.32</v>
+        <v>-8.332800000000001</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.28</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6839</v>
+        <v>-0.7124</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.9424</v>
+        <v>-11.3984</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.05</v>
       </c>
       <c r="I202" t="n">
-        <v>0.19</v>
+        <v>0.1532</v>
       </c>
       <c r="J202" t="n">
-        <v>3.42</v>
+        <v>2.7576</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.01</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0801</v>
+        <v>0.0608</v>
       </c>
       <c r="J203" t="n">
-        <v>1.4418</v>
+        <v>1.0944</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.71</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3205</v>
+        <v>-0.3039</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.769</v>
+        <v>-5.4702</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.339</v>
+        <v>-0.3232</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.102</v>
+        <v>-5.8176</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.64</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3844</v>
+        <v>-0.3716</v>
       </c>
       <c r="J206" t="n">
-        <v>-6.9192</v>
+        <v>-6.6888</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.79</v>
       </c>
       <c r="I207" t="n">
-        <v>1.4449</v>
+        <v>1.4727</v>
       </c>
       <c r="J207" t="n">
-        <v>26.0082</v>
+        <v>26.5086</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.4</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9195</v>
+        <v>0.9111</v>
       </c>
       <c r="J208" t="n">
-        <v>16.551</v>
+        <v>16.3998</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.29</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7119</v>
+        <v>0.6909</v>
       </c>
       <c r="J209" t="n">
-        <v>12.8142</v>
+        <v>12.4362</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.26</v>
       </c>
       <c r="I210" t="n">
-        <v>0.6509</v>
+        <v>0.627</v>
       </c>
       <c r="J210" t="n">
-        <v>11.7162</v>
+        <v>11.286</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.09</v>
       </c>
       <c r="I211" t="n">
-        <v>0.2569</v>
+        <v>0.2256</v>
       </c>
       <c r="J211" t="n">
-        <v>4.6242</v>
+        <v>4.0608</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.34</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6642</v>
+        <v>0.6072</v>
       </c>
       <c r="J212" t="n">
-        <v>15.2766</v>
+        <v>13.9656</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.17</v>
       </c>
       <c r="I213" t="n">
-        <v>0.385</v>
+        <v>0.3293</v>
       </c>
       <c r="J213" t="n">
-        <v>8.855</v>
+        <v>7.5739</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.96</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.0576</v>
       </c>
       <c r="J214" t="n">
-        <v>-1.6445</v>
+        <v>-1.3248</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.82</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2311</v>
+        <v>-0.2107</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.3153</v>
+        <v>-4.8461</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.64</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4007</v>
+        <v>-0.3904</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.216100000000001</v>
+        <v>-8.979200000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.29</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7571</v>
+        <v>0.7274</v>
       </c>
       <c r="J217" t="n">
-        <v>17.4133</v>
+        <v>16.7302</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.2</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5622</v>
+        <v>0.5234</v>
       </c>
       <c r="J218" t="n">
-        <v>12.9306</v>
+        <v>12.0382</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.12</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3747</v>
+        <v>0.3357</v>
       </c>
       <c r="J219" t="n">
-        <v>8.6181</v>
+        <v>7.7211</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.99</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0743</v>
+        <v>-0.0542</v>
       </c>
       <c r="J220" t="n">
-        <v>-1.7089</v>
+        <v>-1.2466</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.87</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4382</v>
+        <v>-0.3955</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.0786</v>
+        <v>-9.096500000000001</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.89</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9654</v>
+        <v>0.9013</v>
       </c>
       <c r="J222" t="n">
-        <v>17.3772</v>
+        <v>16.2234</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.77</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8592</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="J223" t="n">
-        <v>15.4656</v>
+        <v>14.1984</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.23</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3224</v>
+        <v>0.2708</v>
       </c>
       <c r="J224" t="n">
-        <v>5.8032</v>
+        <v>4.8744</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.01</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0056</v>
       </c>
       <c r="J225" t="n">
-        <v>-0.0108</v>
+        <v>-0.1008</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1268</v>
+        <v>-0.1107</v>
       </c>
       <c r="J226" t="n">
-        <v>-2.2824</v>
+        <v>-1.9926</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.22</v>
       </c>
       <c r="I227" t="n">
-        <v>0.408</v>
+        <v>0.4129</v>
       </c>
       <c r="J227" t="n">
-        <v>7.344</v>
+        <v>7.4322</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.96</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0577</v>
+        <v>-0.0469</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.0386</v>
+        <v>-0.8442</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.0721</v>
       </c>
       <c r="J229" t="n">
-        <v>-1.53</v>
+        <v>-1.2978</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.61</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.413</v>
+        <v>-0.4027</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.434</v>
+        <v>-7.2486</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.45</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.552</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.936</v>
+        <v>-10.062</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.03</v>
       </c>
       <c r="I232" t="n">
-        <v>0.1768</v>
+        <v>0.1517</v>
       </c>
       <c r="J232" t="n">
-        <v>3.1824</v>
+        <v>2.7306</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.79</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.2363</v>
+        <v>-0.2211</v>
       </c>
       <c r="J233" t="n">
-        <v>-4.2534</v>
+        <v>-3.9798</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.71</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3105</v>
+        <v>-0.2958</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.589</v>
+        <v>-5.3244</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.55</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4531</v>
+        <v>-0.4464</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.155799999999999</v>
+        <v>-8.0352</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.54</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4619</v>
+        <v>-0.4561</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.3142</v>
+        <v>-8.2098</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.8</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4598</v>
+        <v>1.4887</v>
       </c>
       <c r="J237" t="n">
-        <v>26.2764</v>
+        <v>26.7966</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.51</v>
       </c>
       <c r="I238" t="n">
-        <v>1.0905</v>
+        <v>1.1031</v>
       </c>
       <c r="J238" t="n">
-        <v>19.629</v>
+        <v>19.8558</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.23</v>
       </c>
       <c r="I239" t="n">
-        <v>0.5896</v>
+        <v>0.5629</v>
       </c>
       <c r="J239" t="n">
-        <v>10.6128</v>
+        <v>10.1322</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.17</v>
       </c>
       <c r="I240" t="n">
-        <v>0.4567</v>
+        <v>0.426</v>
       </c>
       <c r="J240" t="n">
-        <v>8.220599999999999</v>
+        <v>7.668</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.06</v>
       </c>
       <c r="I241" t="n">
-        <v>0.1743</v>
+        <v>0.1459</v>
       </c>
       <c r="J241" t="n">
-        <v>3.1374</v>
+        <v>2.6262</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.36</v>
       </c>
       <c r="I242" t="n">
-        <v>0.7059</v>
+        <v>0.652</v>
       </c>
       <c r="J242" t="n">
-        <v>16.2357</v>
+        <v>14.996</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.33</v>
       </c>
       <c r="I243" t="n">
-        <v>0.659</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="J243" t="n">
-        <v>15.157</v>
+        <v>13.8759</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.82</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.2281</v>
+        <v>-0.2078</v>
       </c>
       <c r="J244" t="n">
-        <v>-5.2463</v>
+        <v>-4.7794</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.66</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3799</v>
+        <v>-0.3674</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.7377</v>
+        <v>-8.450200000000001</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.6</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4333</v>
+        <v>-0.4261</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.9659</v>
+        <v>-9.8003</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.78</v>
       </c>
       <c r="I247" t="n">
-        <v>1.4807</v>
+        <v>1.516</v>
       </c>
       <c r="J247" t="n">
-        <v>34.0561</v>
+        <v>34.868</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.21</v>
       </c>
       <c r="I248" t="n">
-        <v>0.5687</v>
+        <v>0.5339</v>
       </c>
       <c r="J248" t="n">
-        <v>13.0801</v>
+        <v>12.2797</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.03</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1076</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="J249" t="n">
-        <v>2.4748</v>
+        <v>2.001</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.97</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.168</v>
+        <v>-0.1365</v>
       </c>
       <c r="J250" t="n">
-        <v>-3.864</v>
+        <v>-3.1395</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.91</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3496</v>
+        <v>-0.3085</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.040800000000001</v>
+        <v>-7.0955</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.56</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1783</v>
+        <v>1.1923</v>
       </c>
       <c r="J252" t="n">
-        <v>23.566</v>
+        <v>23.846</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.25</v>
       </c>
       <c r="I253" t="n">
-        <v>0.6459</v>
+        <v>0.6159</v>
       </c>
       <c r="J253" t="n">
-        <v>12.918</v>
+        <v>12.318</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.22</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5845</v>
+        <v>0.5528</v>
       </c>
       <c r="J254" t="n">
-        <v>11.69</v>
+        <v>11.056</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.21</v>
       </c>
       <c r="I255" t="n">
-        <v>0.5633</v>
+        <v>0.5312</v>
       </c>
       <c r="J255" t="n">
-        <v>11.266</v>
+        <v>10.624</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.93</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.303</v>
+        <v>-0.2642</v>
       </c>
       <c r="J256" t="n">
-        <v>-6.06</v>
+        <v>-5.284</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.15</v>
       </c>
       <c r="I257" t="n">
-        <v>0.3635</v>
+        <v>0.3095</v>
       </c>
       <c r="J257" t="n">
-        <v>7.27</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.1</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2677</v>
+        <v>0.2197</v>
       </c>
       <c r="J258" t="n">
-        <v>5.354</v>
+        <v>4.394</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.06</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1836</v>
+        <v>0.144</v>
       </c>
       <c r="J259" t="n">
-        <v>3.672</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.71</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3317</v>
+        <v>-0.3154</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.634</v>
+        <v>-6.308</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.62</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4133</v>
+        <v>-0.4037</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.266</v>
+        <v>-8.074</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.72</v>
       </c>
       <c r="I262" t="n">
-        <v>1.4118</v>
+        <v>1.4421</v>
       </c>
       <c r="J262" t="n">
-        <v>33.8832</v>
+        <v>34.6104</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.35</v>
       </c>
       <c r="I263" t="n">
-        <v>0.8643</v>
+        <v>0.8433</v>
       </c>
       <c r="J263" t="n">
-        <v>20.7432</v>
+        <v>20.2392</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.97</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1629</v>
+        <v>-0.1313</v>
       </c>
       <c r="J264" t="n">
-        <v>-3.9096</v>
+        <v>-3.1512</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2591</v>
+        <v>-0.2204</v>
       </c>
       <c r="J265" t="n">
-        <v>-6.2184</v>
+        <v>-5.2896</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.78</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6626</v>
+        <v>-0.6299</v>
       </c>
       <c r="J266" t="n">
-        <v>-15.9024</v>
+        <v>-15.1176</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.22</v>
       </c>
       <c r="I267" t="n">
-        <v>0.482</v>
+        <v>0.4243</v>
       </c>
       <c r="J267" t="n">
-        <v>11.568</v>
+        <v>10.1832</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.2</v>
       </c>
       <c r="I268" t="n">
-        <v>0.4477</v>
+        <v>0.3905</v>
       </c>
       <c r="J268" t="n">
-        <v>10.7448</v>
+        <v>9.372</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.89</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1536</v>
+        <v>-0.1344</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.6864</v>
+        <v>-3.2256</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.88</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.1646</v>
+        <v>-0.145</v>
       </c>
       <c r="J270" t="n">
-        <v>-3.9504</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.54</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4847</v>
+        <v>-0.4836</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.6328</v>
+        <v>-11.6064</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.17</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4421</v>
+        <v>0.3931</v>
       </c>
       <c r="J272" t="n">
-        <v>7.9578</v>
+        <v>7.0758</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1</v>
       </c>
       <c r="I273" t="n">
-        <v>0.0387</v>
+        <v>0.033</v>
       </c>
       <c r="J273" t="n">
-        <v>0.6966</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.96</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.0533</v>
+        <v>-0.0426</v>
       </c>
       <c r="J274" t="n">
-        <v>-0.9594</v>
+        <v>-0.7668</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.55</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4629</v>
+        <v>-0.4576</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.3322</v>
+        <v>-8.236800000000001</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.36</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.6445</v>
       </c>
       <c r="J276" t="n">
-        <v>-11.259</v>
+        <v>-11.601</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.56</v>
       </c>
       <c r="I277" t="n">
-        <v>1.1558</v>
+        <v>1.1703</v>
       </c>
       <c r="J277" t="n">
-        <v>20.8044</v>
+        <v>21.0654</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.48</v>
       </c>
       <c r="I278" t="n">
-        <v>1.0494</v>
+        <v>1.058</v>
       </c>
       <c r="J278" t="n">
-        <v>18.8892</v>
+        <v>19.044</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.39</v>
       </c>
       <c r="I279" t="n">
-        <v>0.9025</v>
+        <v>0.8922</v>
       </c>
       <c r="J279" t="n">
-        <v>16.245</v>
+        <v>16.0596</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.21</v>
       </c>
       <c r="I280" t="n">
-        <v>0.5462</v>
+        <v>0.5179</v>
       </c>
       <c r="J280" t="n">
-        <v>9.8316</v>
+        <v>9.3222</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>1.14</v>
       </c>
       <c r="I281" t="n">
-        <v>0.3856</v>
+        <v>0.3538</v>
       </c>
       <c r="J281" t="n">
-        <v>6.9408</v>
+        <v>6.3684</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.22</v>
       </c>
       <c r="I282" t="n">
-        <v>0.4912</v>
+        <v>0.4346</v>
       </c>
       <c r="J282" t="n">
-        <v>10.8064</v>
+        <v>9.561199999999999</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.11</v>
       </c>
       <c r="I283" t="n">
-        <v>0.2906</v>
+        <v>0.2411</v>
       </c>
       <c r="J283" t="n">
-        <v>6.3932</v>
+        <v>5.3042</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.02</v>
       </c>
       <c r="I284" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0624</v>
       </c>
       <c r="J284" t="n">
-        <v>1.914</v>
+        <v>1.3728</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.72</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3212</v>
+        <v>-0.3042</v>
       </c>
       <c r="J285" t="n">
-        <v>-7.0664</v>
+        <v>-6.6924</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.51</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5079</v>
+        <v>-0.5095</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.1738</v>
+        <v>-11.209</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.5</v>
       </c>
       <c r="I287" t="n">
-        <v>1.1115</v>
+        <v>1.1234</v>
       </c>
       <c r="J287" t="n">
-        <v>24.453</v>
+        <v>24.7148</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.31</v>
       </c>
       <c r="I288" t="n">
-        <v>0.7799</v>
+        <v>0.7532</v>
       </c>
       <c r="J288" t="n">
-        <v>17.1578</v>
+        <v>16.5704</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.2</v>
       </c>
       <c r="I289" t="n">
-        <v>0.5487</v>
+        <v>0.5129</v>
       </c>
       <c r="J289" t="n">
-        <v>12.0714</v>
+        <v>11.2838</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.93</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2914</v>
+        <v>-0.2515</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.4108</v>
+        <v>-5.533</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.9</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3744</v>
+        <v>-0.3328</v>
       </c>
       <c r="J291" t="n">
-        <v>-8.236800000000001</v>
+        <v>-7.3216</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.81</v>
       </c>
       <c r="I292" t="n">
-        <v>1.4969</v>
+        <v>1.5307</v>
       </c>
       <c r="J292" t="n">
-        <v>28.4411</v>
+        <v>29.0833</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.26</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6641</v>
+        <v>0.6358</v>
       </c>
       <c r="J293" t="n">
-        <v>12.6179</v>
+        <v>12.0802</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.22</v>
       </c>
       <c r="I294" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.5515</v>
       </c>
       <c r="J294" t="n">
-        <v>11.0618</v>
+        <v>10.4785</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.06</v>
       </c>
       <c r="I295" t="n">
-        <v>0.1906</v>
+        <v>0.1628</v>
       </c>
       <c r="J295" t="n">
-        <v>3.6214</v>
+        <v>3.0932</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.92</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3348</v>
+        <v>-0.2957</v>
       </c>
       <c r="J296" t="n">
-        <v>-6.3612</v>
+        <v>-5.6183</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.7</v>
       </c>
       <c r="I297" t="n">
-        <v>1.1522</v>
+        <v>1.1515</v>
       </c>
       <c r="J297" t="n">
-        <v>21.8918</v>
+        <v>21.8785</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.86</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1864</v>
+        <v>-0.1662</v>
       </c>
       <c r="J298" t="n">
-        <v>-3.5416</v>
+        <v>-3.1578</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.8</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.2478</v>
+        <v>-0.2278</v>
       </c>
       <c r="J299" t="n">
-        <v>-4.7082</v>
+        <v>-4.3282</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.74</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3058</v>
+        <v>-0.288</v>
       </c>
       <c r="J300" t="n">
-        <v>-5.8102</v>
+        <v>-5.472</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.65</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3886</v>
+        <v>-0.3768</v>
       </c>
       <c r="J301" t="n">
-        <v>-7.3834</v>
+        <v>-7.1592</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.78</v>
       </c>
       <c r="I302" t="n">
-        <v>0.9907</v>
+        <v>1.091</v>
       </c>
       <c r="J302" t="n">
-        <v>23.7768</v>
+        <v>26.184</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.91</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.1385</v>
+        <v>-0.119</v>
       </c>
       <c r="J303" t="n">
-        <v>-3.324</v>
+        <v>-2.856</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.85</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2047</v>
+        <v>-0.184</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.9128</v>
+        <v>-4.416</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.83</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.2254</v>
+        <v>-0.205</v>
       </c>
       <c r="J305" t="n">
-        <v>-5.4096</v>
+        <v>-4.92</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2457</v>
+        <v>-0.2257</v>
       </c>
       <c r="J306" t="n">
-        <v>-5.8968</v>
+        <v>-5.4168</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.4</v>
       </c>
       <c r="I307" t="n">
-        <v>0.5389</v>
+        <v>0.4694</v>
       </c>
       <c r="J307" t="n">
-        <v>12.9336</v>
+        <v>11.2656</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.33</v>
       </c>
       <c r="I308" t="n">
-        <v>0.4615</v>
+        <v>0.3947</v>
       </c>
       <c r="J308" t="n">
-        <v>11.076</v>
+        <v>9.472799999999999</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.13</v>
       </c>
       <c r="I309" t="n">
-        <v>0.2193</v>
+        <v>0.1737</v>
       </c>
       <c r="J309" t="n">
-        <v>5.2632</v>
+        <v>4.1688</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.02</v>
       </c>
       <c r="I310" t="n">
-        <v>0.0477</v>
+        <v>0.0332</v>
       </c>
       <c r="J310" t="n">
-        <v>1.1448</v>
+        <v>0.7968</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.57</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4699</v>
+        <v>-0.4687</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.2776</v>
+        <v>-11.2488</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.73</v>
       </c>
       <c r="I312" t="n">
-        <v>1.4149</v>
+        <v>1.4442</v>
       </c>
       <c r="J312" t="n">
-        <v>33.9576</v>
+        <v>34.6608</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.36</v>
       </c>
       <c r="I313" t="n">
-        <v>0.8762</v>
+        <v>0.8568</v>
       </c>
       <c r="J313" t="n">
-        <v>21.0288</v>
+        <v>20.5632</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.1</v>
       </c>
       <c r="I314" t="n">
-        <v>0.3128</v>
+        <v>0.2796</v>
       </c>
       <c r="J314" t="n">
-        <v>7.5072</v>
+        <v>6.7104</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.9</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3773</v>
+        <v>-0.3359</v>
       </c>
       <c r="J315" t="n">
-        <v>-9.055199999999999</v>
+        <v>-8.0616</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.83</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5526</v>
+        <v>-0.5147</v>
       </c>
       <c r="J316" t="n">
-        <v>-13.2624</v>
+        <v>-12.3528</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.16</v>
       </c>
       <c r="I317" t="n">
-        <v>0.3729</v>
+        <v>0.3179</v>
       </c>
       <c r="J317" t="n">
-        <v>8.9496</v>
+        <v>7.6296</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.15</v>
       </c>
       <c r="I318" t="n">
-        <v>0.3547</v>
+        <v>0.3007</v>
       </c>
       <c r="J318" t="n">
-        <v>8.5128</v>
+        <v>7.2168</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.12</v>
       </c>
       <c r="I319" t="n">
-        <v>0.2988</v>
+        <v>0.2482</v>
       </c>
       <c r="J319" t="n">
-        <v>7.1712</v>
+        <v>5.9568</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.9</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1437</v>
+        <v>-0.1247</v>
       </c>
       <c r="J320" t="n">
-        <v>-3.4488</v>
+        <v>-2.9928</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.48</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.537</v>
+        <v>-0.5435</v>
       </c>
       <c r="J321" t="n">
-        <v>-12.888</v>
+        <v>-13.044</v>
       </c>
     </row>
   </sheetData>
